--- a/research/traditional_assets/database/data/egypt/egypt_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_retail_special_lines.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03149999999999999</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="E2">
-        <v>0.215</v>
+        <v>0.118</v>
       </c>
       <c r="G2">
-        <v>-0.01345291479820627</v>
+        <v>0.0818623124448367</v>
       </c>
       <c r="H2">
-        <v>-0.01345291479820627</v>
+        <v>0.0818623124448367</v>
       </c>
       <c r="I2">
-        <v>-0.0164424514200299</v>
+        <v>0.04101059135039717</v>
       </c>
       <c r="J2">
-        <v>-0.01457982997010463</v>
+        <v>0.03632366662463749</v>
       </c>
       <c r="K2">
-        <v>-8.730000000000002</v>
+        <v>3.16</v>
       </c>
       <c r="L2">
-        <v>-0.04349775784753364</v>
+        <v>0.01394527802294792</v>
       </c>
       <c r="M2">
-        <v>8.380000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="N2">
-        <v>0.08346613545816733</v>
+        <v>0.1028662420382166</v>
       </c>
       <c r="O2">
-        <v>-0.9599083619702174</v>
+        <v>3.066455696202532</v>
       </c>
       <c r="P2">
-        <v>8.380000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="Q2">
-        <v>0.08346613545816733</v>
+        <v>0.1028662420382166</v>
       </c>
       <c r="R2">
-        <v>-0.9599083619702174</v>
+        <v>3.066455696202532</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>78.41</v>
+        <v>71.14999999999999</v>
       </c>
       <c r="V2">
-        <v>0.7809760956175298</v>
+        <v>0.7553078556263269</v>
       </c>
       <c r="W2">
-        <v>0.2835196888672825</v>
+        <v>0.2766279021815333</v>
       </c>
       <c r="X2">
-        <v>0.3170429739597466</v>
+        <v>0.5129044662034664</v>
       </c>
       <c r="Y2">
-        <v>-0.03352328509246411</v>
+        <v>-0.2362765640219331</v>
       </c>
       <c r="Z2">
-        <v>0.8470641861093291</v>
+        <v>1.059423067932115</v>
       </c>
       <c r="AA2">
-        <v>0.6182737102201227</v>
+        <v>1.000130579680166</v>
       </c>
       <c r="AB2">
-        <v>0.1245243579387439</v>
+        <v>0.1937914813038705</v>
       </c>
       <c r="AC2">
-        <v>0.4937493522813787</v>
+        <v>0.8063390983762956</v>
       </c>
       <c r="AD2">
-        <v>251.9</v>
+        <v>254.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>251.9</v>
+        <v>254.5</v>
       </c>
       <c r="AG2">
-        <v>173.49</v>
+        <v>183.35</v>
       </c>
       <c r="AH2">
-        <v>0.7150156116945785</v>
+        <v>0.729853742472039</v>
       </c>
       <c r="AI2">
-        <v>0.7501488981536629</v>
+        <v>0.7693470374848851</v>
       </c>
       <c r="AJ2">
-        <v>0.6334294789879149</v>
+        <v>0.6606016933885787</v>
       </c>
       <c r="AK2">
-        <v>0.6740355103150861</v>
+        <v>0.7061428846524167</v>
       </c>
       <c r="AL2">
-        <v>14.4</v>
+        <v>10.7</v>
       </c>
       <c r="AM2">
-        <v>10.011</v>
+        <v>6.548999999999999</v>
       </c>
       <c r="AN2">
-        <v>40.43338683788122</v>
+        <v>14.09972299168975</v>
       </c>
       <c r="AO2">
-        <v>-0.2291666666666667</v>
+        <v>0.8685046728971962</v>
       </c>
       <c r="AP2">
-        <v>27.84751203852328</v>
+        <v>10.15789473684211</v>
       </c>
       <c r="AQ2">
-        <v>-0.3296373988612527</v>
+        <v>1.418995266452894</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.164</v>
+        <v>0.152</v>
       </c>
       <c r="E3">
-        <v>0.215</v>
+        <v>0.118</v>
       </c>
       <c r="G3">
-        <v>0.218436873747495</v>
+        <v>0.2505854800936768</v>
       </c>
       <c r="H3">
-        <v>0.218436873747495</v>
+        <v>0.2505854800936768</v>
       </c>
       <c r="I3">
-        <v>0.2444889779559118</v>
+        <v>0.2304449648711944</v>
       </c>
       <c r="J3">
-        <v>0.1890969438877755</v>
+        <v>0.1777718300434928</v>
       </c>
       <c r="K3">
-        <v>9.869999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L3">
-        <v>0.1977955911823647</v>
+        <v>0.2023419203747073</v>
       </c>
       <c r="M3">
-        <v>8.380000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="N3">
-        <v>0.1672654690618763</v>
+        <v>0.1719191919191919</v>
       </c>
       <c r="O3">
-        <v>0.8490374873353598</v>
+        <v>0.9849537037037036</v>
       </c>
       <c r="P3">
-        <v>8.380000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="Q3">
-        <v>0.1672654690618763</v>
+        <v>0.1719191919191919</v>
       </c>
       <c r="R3">
-        <v>0.8490374873353598</v>
+        <v>0.9849537037037036</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.91</v>
+        <v>6.55</v>
       </c>
       <c r="V3">
-        <v>0.1978043912175649</v>
+        <v>0.1323232323232323</v>
       </c>
       <c r="W3">
-        <v>0.815702479338843</v>
+        <v>0.6306569343065694</v>
       </c>
       <c r="X3">
-        <v>0.1177813821813773</v>
+        <v>0.1866694842042297</v>
       </c>
       <c r="Y3">
-        <v>0.6979210971574656</v>
+        <v>0.4439874501023398</v>
       </c>
       <c r="Z3">
-        <v>6.896075179657269</v>
+        <v>11.26649076517151</v>
       </c>
       <c r="AA3">
-        <v>1.304026741293532</v>
+        <v>2.00286468149265</v>
       </c>
       <c r="AB3">
-        <v>0.1177813821813773</v>
+        <v>0.1866694842042297</v>
       </c>
       <c r="AC3">
-        <v>1.186245359112155</v>
+        <v>1.81619519728842</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-9.91</v>
+        <v>-6.55</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,25 +815,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2465787509330679</v>
+        <v>-0.1525029103608847</v>
       </c>
       <c r="AK3">
-        <v>-2.422982885085575</v>
+        <v>-1.297029702970297</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.489</v>
+        <v>-0.301</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.7865079365079365</v>
+        <v>-0.6421568627450981</v>
       </c>
       <c r="AQ3">
-        <v>-24.94887525562372</v>
+        <v>-32.69102990033223</v>
       </c>
     </row>
     <row r="4">
@@ -853,115 +853,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.101</v>
+        <v>-0.0526</v>
       </c>
       <c r="G4">
-        <v>-0.09018567639257294</v>
+        <v>0.04268624252311038</v>
       </c>
       <c r="H4">
-        <v>-0.09018567639257294</v>
+        <v>0.04268624252311038</v>
       </c>
       <c r="I4">
-        <v>-0.1027851458885942</v>
+        <v>-0.002974442631865144</v>
       </c>
       <c r="J4">
-        <v>-0.1027851458885942</v>
+        <v>-0.002974442631865144</v>
       </c>
       <c r="K4">
-        <v>-18.6</v>
+        <v>-5.48</v>
       </c>
       <c r="L4">
-        <v>-0.123342175066313</v>
+        <v>-0.02979880369766177</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.18</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02639821029082774</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.2153284671532846</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>1.18</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02639821029082774</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0.2153284671532846</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>68.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="V4">
-        <v>1.361829025844931</v>
+        <v>1.445190156599552</v>
       </c>
       <c r="W4">
-        <v>-0.2486631016042781</v>
+        <v>-0.07740112994350283</v>
       </c>
       <c r="X4">
-        <v>0.5163045657381158</v>
+        <v>0.839139448202703</v>
       </c>
       <c r="Y4">
-        <v>-0.7649676673423939</v>
+        <v>-0.9165405781462058</v>
       </c>
       <c r="Z4">
-        <v>0.6565084893339138</v>
+        <v>0.8752974773917181</v>
       </c>
       <c r="AA4">
-        <v>-0.06747932085328689</v>
+        <v>-0.002603522132317944</v>
       </c>
       <c r="AB4">
-        <v>0.1312673336961105</v>
+        <v>0.2009134784035112</v>
       </c>
       <c r="AC4">
-        <v>-0.1987466545493974</v>
+        <v>-0.2035170005358291</v>
       </c>
       <c r="AD4">
-        <v>251.9</v>
+        <v>254.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>251.9</v>
+        <v>254.5</v>
       </c>
       <c r="AG4">
-        <v>183.4</v>
+        <v>189.9</v>
       </c>
       <c r="AH4">
-        <v>0.8335539377895435</v>
+        <v>0.8506016042780749</v>
       </c>
       <c r="AI4">
-        <v>0.7827843380981976</v>
+        <v>0.7973057644110276</v>
       </c>
       <c r="AJ4">
-        <v>0.7847667950363715</v>
+        <v>0.809462915601023</v>
       </c>
       <c r="AK4">
-        <v>0.7240426371891038</v>
+        <v>0.7458758837391987</v>
       </c>
       <c r="AL4">
-        <v>14.4</v>
+        <v>10.7</v>
       </c>
       <c r="AM4">
-        <v>10.5</v>
+        <v>6.85</v>
       </c>
       <c r="AN4">
-        <v>-39.5447409733124</v>
+        <v>32.4203821656051</v>
       </c>
       <c r="AO4">
-        <v>-1.076388888888889</v>
+        <v>-0.05112149532710281</v>
       </c>
       <c r="AP4">
-        <v>-28.79120879120879</v>
+        <v>24.19108280254777</v>
       </c>
       <c r="AQ4">
-        <v>-1.476190476190476</v>
+        <v>-0.07985401459854016</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_retail_special_lines.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="case_aivc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04969999999999999</v>
+        <v>0.07685</v>
       </c>
       <c r="E2">
-        <v>0.118</v>
+        <v>0.261</v>
       </c>
       <c r="G2">
-        <v>0.0818623124448367</v>
+        <v>0.160210605490786</v>
       </c>
       <c r="H2">
-        <v>0.0818623124448367</v>
+        <v>0.160210605490786</v>
       </c>
       <c r="I2">
-        <v>0.04101059135039717</v>
+        <v>0.128995863106431</v>
       </c>
       <c r="J2">
-        <v>0.03632366662463749</v>
+        <v>0.08151706316951558</v>
       </c>
       <c r="K2">
-        <v>3.16</v>
+        <v>10.41</v>
       </c>
       <c r="L2">
-        <v>0.01394527802294792</v>
+        <v>0.03915005641218504</v>
       </c>
       <c r="M2">
-        <v>9.69</v>
+        <v>9.641999999999999</v>
       </c>
       <c r="N2">
-        <v>0.1028662420382166</v>
+        <v>0.07462848297213623</v>
       </c>
       <c r="O2">
-        <v>3.066455696202532</v>
+        <v>0.9262247838616714</v>
       </c>
       <c r="P2">
-        <v>9.69</v>
+        <v>9.641999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.1028662420382166</v>
+        <v>0.07462848297213623</v>
       </c>
       <c r="R2">
-        <v>3.066455696202532</v>
+        <v>0.9262247838616714</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>71.14999999999999</v>
+        <v>19.46</v>
       </c>
       <c r="V2">
-        <v>0.7553078556263269</v>
+        <v>0.1506191950464396</v>
       </c>
       <c r="W2">
-        <v>0.2766279021815333</v>
+        <v>0.31654502877305</v>
       </c>
       <c r="X2">
-        <v>0.5129044662034664</v>
+        <v>0.5382009936636114</v>
       </c>
       <c r="Y2">
-        <v>-0.2362765640219331</v>
+        <v>-0.2216559648905614</v>
       </c>
       <c r="Z2">
-        <v>1.059423067932115</v>
+        <v>1.082187655165116</v>
       </c>
       <c r="AA2">
-        <v>1.000130579680166</v>
+        <v>0.8353668813576094</v>
       </c>
       <c r="AB2">
-        <v>0.1937914813038705</v>
+        <v>0.2016804511890571</v>
       </c>
       <c r="AC2">
-        <v>0.8063390983762956</v>
+        <v>0.6336864301685523</v>
       </c>
       <c r="AD2">
-        <v>254.5</v>
+        <v>190.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>254.5</v>
+        <v>190.9</v>
       </c>
       <c r="AG2">
-        <v>183.35</v>
+        <v>171.44</v>
       </c>
       <c r="AH2">
-        <v>0.729853742472039</v>
+        <v>0.5963761324586067</v>
       </c>
       <c r="AI2">
-        <v>0.7693470374848851</v>
+        <v>0.8310116663764583</v>
       </c>
       <c r="AJ2">
-        <v>0.6606016933885787</v>
+        <v>0.5702501330494945</v>
       </c>
       <c r="AK2">
-        <v>0.7061428846524167</v>
+        <v>0.8153714448777704</v>
       </c>
       <c r="AL2">
-        <v>10.7</v>
+        <v>21.8</v>
       </c>
       <c r="AM2">
-        <v>6.548999999999999</v>
+        <v>20.21</v>
       </c>
       <c r="AN2">
-        <v>14.09972299168975</v>
+        <v>4.481220657276995</v>
       </c>
       <c r="AO2">
-        <v>0.8685046728971962</v>
+        <v>1.573394495412844</v>
       </c>
       <c r="AP2">
-        <v>10.15789473684211</v>
+        <v>4.024413145539905</v>
       </c>
       <c r="AQ2">
-        <v>1.418995266452894</v>
+        <v>1.697179614052449</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.152</v>
+        <v>0.174</v>
       </c>
       <c r="E3">
-        <v>0.118</v>
+        <v>0.261</v>
       </c>
       <c r="G3">
-        <v>0.2505854800936768</v>
+        <v>0.2555066079295154</v>
       </c>
       <c r="H3">
-        <v>0.2505854800936768</v>
+        <v>0.2555066079295154</v>
       </c>
       <c r="I3">
-        <v>0.2304449648711944</v>
+        <v>0.3149779735682819</v>
       </c>
       <c r="J3">
-        <v>0.1777718300434928</v>
+        <v>0.2406025294869973</v>
       </c>
       <c r="K3">
-        <v>8.640000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="L3">
-        <v>0.2023419203747073</v>
+        <v>0.2599118942731278</v>
       </c>
       <c r="M3">
-        <v>8.51</v>
+        <v>9.52</v>
       </c>
       <c r="N3">
-        <v>0.1719191919191919</v>
+        <v>0.09834710743801653</v>
       </c>
       <c r="O3">
-        <v>0.9849537037037036</v>
+        <v>0.8067796610169491</v>
       </c>
       <c r="P3">
-        <v>8.51</v>
+        <v>9.52</v>
       </c>
       <c r="Q3">
-        <v>0.1719191919191919</v>
+        <v>0.09834710743801653</v>
       </c>
       <c r="R3">
-        <v>0.9849537037037036</v>
+        <v>0.8067796610169491</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +772,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.55</v>
+        <v>8.16</v>
       </c>
       <c r="V3">
-        <v>0.1323232323232323</v>
+        <v>0.08429752066115703</v>
       </c>
       <c r="W3">
-        <v>0.6306569343065694</v>
+        <v>0.6592178770949721</v>
       </c>
       <c r="X3">
-        <v>0.1866694842042297</v>
+        <v>0.1909107622388137</v>
       </c>
       <c r="Y3">
-        <v>0.4439874501023398</v>
+        <v>0.4683071148561584</v>
       </c>
       <c r="Z3">
-        <v>11.26649076517151</v>
+        <v>6.770056665672533</v>
       </c>
       <c r="AA3">
-        <v>2.00286468149265</v>
+        <v>1.628892758531118</v>
       </c>
       <c r="AB3">
-        <v>0.1866694842042297</v>
+        <v>0.1909107622388137</v>
       </c>
       <c r="AC3">
-        <v>1.81619519728842</v>
+        <v>1.437981996292305</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-6.55</v>
+        <v>-8.16</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,25 +817,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1525029103608847</v>
+        <v>-0.09205776173285199</v>
       </c>
       <c r="AK3">
-        <v>-1.297029702970297</v>
+        <v>-4.636363636363637</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.301</v>
+        <v>-0.42</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.6421568627450981</v>
+        <v>-0.5589041095890411</v>
       </c>
       <c r="AQ3">
-        <v>-32.69102990033223</v>
+        <v>-34.04761904761905</v>
       </c>
     </row>
     <row r="4">
@@ -853,43 +855,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0526</v>
+        <v>-0.0203</v>
       </c>
       <c r="G4">
-        <v>0.04268624252311038</v>
+        <v>0.1405895691609977</v>
       </c>
       <c r="H4">
-        <v>0.04268624252311038</v>
+        <v>0.1405895691609977</v>
       </c>
       <c r="I4">
-        <v>-0.002974442631865144</v>
+        <v>0.09070294784580499</v>
       </c>
       <c r="J4">
-        <v>-0.002974442631865144</v>
+        <v>0.04535147392290249</v>
       </c>
       <c r="K4">
-        <v>-5.48</v>
+        <v>-1.39</v>
       </c>
       <c r="L4">
-        <v>-0.02979880369766177</v>
+        <v>-0.006303854875283447</v>
       </c>
       <c r="M4">
-        <v>1.18</v>
+        <v>0.122</v>
       </c>
       <c r="N4">
-        <v>0.02639821029082774</v>
+        <v>0.003765432098765432</v>
       </c>
       <c r="O4">
-        <v>-0.2153284671532846</v>
+        <v>-0.08776978417266187</v>
       </c>
       <c r="P4">
-        <v>1.18</v>
+        <v>0.122</v>
       </c>
       <c r="Q4">
-        <v>0.02639821029082774</v>
+        <v>0.003765432098765432</v>
       </c>
       <c r="R4">
-        <v>-0.2153284671532846</v>
+        <v>-0.08776978417266187</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +900,8845 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>64.59999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="V4">
-        <v>1.445190156599552</v>
+        <v>0.3487654320987655</v>
       </c>
       <c r="W4">
-        <v>-0.07740112994350283</v>
+        <v>-0.02612781954887218</v>
       </c>
       <c r="X4">
-        <v>0.839139448202703</v>
+        <v>0.8854912250884091</v>
       </c>
       <c r="Y4">
-        <v>-0.9165405781462058</v>
+        <v>-0.9116190446372813</v>
       </c>
       <c r="Z4">
-        <v>0.8752974773917181</v>
+        <v>0.9225941422594144</v>
       </c>
       <c r="AA4">
-        <v>-0.002603522132317944</v>
+        <v>0.04184100418410042</v>
       </c>
       <c r="AB4">
-        <v>0.2009134784035112</v>
+        <v>0.2124501401393005</v>
       </c>
       <c r="AC4">
-        <v>-0.2035170005358291</v>
+        <v>-0.1706091359552001</v>
       </c>
       <c r="AD4">
-        <v>254.5</v>
+        <v>190.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>254.5</v>
+        <v>190.9</v>
       </c>
       <c r="AG4">
-        <v>189.9</v>
+        <v>179.6</v>
       </c>
       <c r="AH4">
-        <v>0.8506016042780749</v>
+        <v>0.8549037169726825</v>
       </c>
       <c r="AI4">
-        <v>0.7973057644110276</v>
+        <v>0.8685168334849863</v>
       </c>
       <c r="AJ4">
-        <v>0.809462915601023</v>
+        <v>0.8471698113207546</v>
       </c>
       <c r="AK4">
-        <v>0.7458758837391987</v>
+        <v>0.8613908872901679</v>
       </c>
       <c r="AL4">
-        <v>10.7</v>
+        <v>21.8</v>
       </c>
       <c r="AM4">
-        <v>6.85</v>
+        <v>20.63</v>
       </c>
       <c r="AN4">
-        <v>32.4203821656051</v>
+        <v>6.817857142857143</v>
       </c>
       <c r="AO4">
-        <v>-0.05112149532710281</v>
+        <v>0.9174311926605504</v>
       </c>
       <c r="AP4">
-        <v>24.19108280254777</v>
+        <v>6.414285714285714</v>
       </c>
       <c r="AQ4">
-        <v>-0.07985401459854016</v>
+        <v>0.9694619486185166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Al Arafa for Investment and Consultancies Company (S.A.E) (CASE:AIVC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CASE:AIVC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retail (Special Lines)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.91743119266055</v>
+      </c>
+      <c r="F2">
+        <v>3.50129758088348</v>
+      </c>
+      <c r="G2">
+        <v>6.81785714285714</v>
+      </c>
+      <c r="H2">
+        <v>7.018</v>
+      </c>
+      <c r="I2">
+        <v>0.854903716972683</v>
+      </c>
+      <c r="J2">
+        <v>0.88</v>
+      </c>
+      <c r="K2">
+        <v>32.4</v>
+      </c>
+      <c r="L2">
+        <v>106.55885868464</v>
+      </c>
+      <c r="M2">
+        <v>212</v>
+      </c>
+      <c r="N2">
+        <v>291.76285868464</v>
+      </c>
+      <c r="O2">
+        <v>190.9</v>
+      </c>
+      <c r="P2">
+        <v>196.504</v>
+      </c>
+      <c r="Q2">
+        <v>0.2124501401393</v>
+      </c>
+      <c r="R2">
+        <v>0.164977231315529</v>
+      </c>
+      <c r="S2">
+        <v>0.0982200136209604</v>
+      </c>
+      <c r="T2">
+        <v>0.043555</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.8854912250884091</v>
+      </c>
+      <c r="X2">
+        <v>1.0554069276294</v>
+      </c>
+      <c r="Y2">
+        <v>5.43910961708025</v>
+      </c>
+      <c r="Z2">
+        <v>6.5306411038831</v>
+      </c>
+      <c r="AA2">
+        <v>190.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.1267355014464005</v>
+      </c>
+      <c r="AC2">
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="AD2">
+        <v>190.9</v>
+      </c>
+      <c r="AE2">
+        <v>21.8</v>
+      </c>
+      <c r="AF2">
+        <v>8</v>
+      </c>
+      <c r="AG2">
+        <v>28</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>32.4</v>
+      </c>
+      <c r="AK2">
+        <v>0.1556672478946873</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.225</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>10.87</v>
+      </c>
+      <c r="AR2">
+        <v>21.8</v>
+      </c>
+      <c r="AS2">
+        <v>190.9</v>
+      </c>
+      <c r="AT2">
+        <v>11.3</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1909107622388137</v>
+      </c>
+      <c r="C2">
+        <v>253.3198884529554</v>
+      </c>
+      <c r="D2">
+        <v>242.0198884529553</v>
+      </c>
+      <c r="E2">
+        <v>-190.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>11.3</v>
+      </c>
+      <c r="H2">
+        <v>32.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="O2">
+        <v>8.700000000000001</v>
+      </c>
+      <c r="P2">
+        <v>29.96666666666667</v>
+      </c>
+      <c r="Q2">
+        <v>37.96666666666667</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1909107622388137</v>
+      </c>
+      <c r="T2">
+        <v>0.9771532823765233</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.225</v>
+      </c>
+      <c r="W2">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1905269380237763</v>
+      </c>
+      <c r="C3">
+        <v>251.6991270898039</v>
+      </c>
+      <c r="D3">
+        <v>242.6321270898039</v>
+      </c>
+      <c r="E3">
+        <v>-188.667</v>
+      </c>
+      <c r="F3">
+        <v>2.233</v>
+      </c>
+      <c r="G3">
+        <v>11.3</v>
+      </c>
+      <c r="H3">
+        <v>32.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+      <c r="L3">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M3">
+        <v>0.09981510000000002</v>
+      </c>
+      <c r="N3">
+        <v>38.56685156666667</v>
+      </c>
+      <c r="O3">
+        <v>8.677541602500002</v>
+      </c>
+      <c r="P3">
+        <v>29.88930996416667</v>
+      </c>
+      <c r="Q3">
+        <v>37.88930996416667</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1921015283068448</v>
+      </c>
+      <c r="T3">
+        <v>0.9848027146375515</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.225</v>
+      </c>
+      <c r="W3">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>387.3829377185082</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.190143113808739</v>
+      </c>
+      <c r="C4">
+        <v>250.0814711472862</v>
+      </c>
+      <c r="D4">
+        <v>243.2474711472862</v>
+      </c>
+      <c r="E4">
+        <v>-186.434</v>
+      </c>
+      <c r="F4">
+        <v>4.466</v>
+      </c>
+      <c r="G4">
+        <v>11.3</v>
+      </c>
+      <c r="H4">
+        <v>32.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K4">
+        <v>8</v>
+      </c>
+      <c r="L4">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M4">
+        <v>0.1996302</v>
+      </c>
+      <c r="N4">
+        <v>38.46703646666667</v>
+      </c>
+      <c r="O4">
+        <v>8.655083205</v>
+      </c>
+      <c r="P4">
+        <v>29.81195326166667</v>
+      </c>
+      <c r="Q4">
+        <v>37.81195326166667</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1933165957232031</v>
+      </c>
+      <c r="T4">
+        <v>0.9926082577610499</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.225</v>
+      </c>
+      <c r="W4">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>193.6914688592541</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1897592895937017</v>
+      </c>
+      <c r="C5">
+        <v>248.4669443126291</v>
+      </c>
+      <c r="D5">
+        <v>243.8659443126291</v>
+      </c>
+      <c r="E5">
+        <v>-184.201</v>
+      </c>
+      <c r="F5">
+        <v>6.699</v>
+      </c>
+      <c r="G5">
+        <v>11.3</v>
+      </c>
+      <c r="H5">
+        <v>32.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M5">
+        <v>0.2994453</v>
+      </c>
+      <c r="N5">
+        <v>38.36722136666667</v>
+      </c>
+      <c r="O5">
+        <v>8.632624807500001</v>
+      </c>
+      <c r="P5">
+        <v>29.73459655916667</v>
+      </c>
+      <c r="Q5">
+        <v>37.73459655916667</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1945567160759811</v>
+      </c>
+      <c r="T5">
+        <v>1.000574739918022</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.225</v>
+      </c>
+      <c r="W5">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>129.1276459061694</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1893754653786643</v>
+      </c>
+      <c r="C6">
+        <v>246.8555705145787</v>
+      </c>
+      <c r="D6">
+        <v>244.4875705145787</v>
+      </c>
+      <c r="E6">
+        <v>-181.968</v>
+      </c>
+      <c r="F6">
+        <v>8.932</v>
+      </c>
+      <c r="G6">
+        <v>11.3</v>
+      </c>
+      <c r="H6">
+        <v>32.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M6">
+        <v>0.3992604000000001</v>
+      </c>
+      <c r="N6">
+        <v>38.26740626666667</v>
+      </c>
+      <c r="O6">
+        <v>8.610166410000001</v>
+      </c>
+      <c r="P6">
+        <v>29.65723985666667</v>
+      </c>
+      <c r="Q6">
+        <v>37.65723985666666</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.195822672269442</v>
+      </c>
+      <c r="T6">
+        <v>1.008707190453265</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.225</v>
+      </c>
+      <c r="W6">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>96.84573442962703</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.188991641163627</v>
+      </c>
+      <c r="C7">
+        <v>245.247373926487</v>
+      </c>
+      <c r="D7">
+        <v>245.112373926487</v>
+      </c>
+      <c r="E7">
+        <v>-179.735</v>
+      </c>
+      <c r="F7">
+        <v>11.165</v>
+      </c>
+      <c r="G7">
+        <v>11.3</v>
+      </c>
+      <c r="H7">
+        <v>32.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M7">
+        <v>0.4990755000000001</v>
+      </c>
+      <c r="N7">
+        <v>38.16759116666667</v>
+      </c>
+      <c r="O7">
+        <v>8.5877080125</v>
+      </c>
+      <c r="P7">
+        <v>29.57988315416667</v>
+      </c>
+      <c r="Q7">
+        <v>37.57988315416667</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.197115280172239</v>
+      </c>
+      <c r="T7">
+        <v>1.017010850473461</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.225</v>
+      </c>
+      <c r="W7">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>77.47658754370163</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1886078169485897</v>
+      </c>
+      <c r="C8">
+        <v>243.6423789694452</v>
+      </c>
+      <c r="D8">
+        <v>245.7403789694452</v>
+      </c>
+      <c r="E8">
+        <v>-177.502</v>
+      </c>
+      <c r="F8">
+        <v>13.398</v>
+      </c>
+      <c r="G8">
+        <v>11.3</v>
+      </c>
+      <c r="H8">
+        <v>32.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K8">
+        <v>8</v>
+      </c>
+      <c r="L8">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M8">
+        <v>0.5988906000000001</v>
+      </c>
+      <c r="N8">
+        <v>38.06777606666667</v>
+      </c>
+      <c r="O8">
+        <v>8.565249615000003</v>
+      </c>
+      <c r="P8">
+        <v>29.50252645166667</v>
+      </c>
+      <c r="Q8">
+        <v>37.50252645166667</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1984353903708401</v>
+      </c>
+      <c r="T8">
+        <v>1.025491184111107</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.225</v>
+      </c>
+      <c r="W8">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>64.5638229530847</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1882239927335523</v>
+      </c>
+      <c r="C9">
+        <v>242.0406103154654</v>
+      </c>
+      <c r="D9">
+        <v>246.3716103154655</v>
+      </c>
+      <c r="E9">
+        <v>-175.269</v>
+      </c>
+      <c r="F9">
+        <v>15.631</v>
+      </c>
+      <c r="G9">
+        <v>11.3</v>
+      </c>
+      <c r="H9">
+        <v>32.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K9">
+        <v>8</v>
+      </c>
+      <c r="L9">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M9">
+        <v>0.6987057000000001</v>
+      </c>
+      <c r="N9">
+        <v>37.96796096666667</v>
+      </c>
+      <c r="O9">
+        <v>8.542791217500001</v>
+      </c>
+      <c r="P9">
+        <v>29.42516974916667</v>
+      </c>
+      <c r="Q9">
+        <v>37.42516974916667</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1997838900360778</v>
+      </c>
+      <c r="T9">
+        <v>1.034153890515154</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.225</v>
+      </c>
+      <c r="W9">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>55.3404196740726</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.187840168518515</v>
+      </c>
+      <c r="C10">
+        <v>240.442092890712</v>
+      </c>
+      <c r="D10">
+        <v>247.006092890712</v>
+      </c>
+      <c r="E10">
+        <v>-173.036</v>
+      </c>
+      <c r="F10">
+        <v>17.864</v>
+      </c>
+      <c r="G10">
+        <v>11.3</v>
+      </c>
+      <c r="H10">
+        <v>32.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K10">
+        <v>8</v>
+      </c>
+      <c r="L10">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M10">
+        <v>0.7985208000000001</v>
+      </c>
+      <c r="N10">
+        <v>37.86814586666667</v>
+      </c>
+      <c r="O10">
+        <v>8.520332820000002</v>
+      </c>
+      <c r="P10">
+        <v>29.34781304666667</v>
+      </c>
+      <c r="Q10">
+        <v>37.34781304666667</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2011617049114294</v>
+      </c>
+      <c r="T10">
+        <v>1.043004916623637</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.225</v>
+      </c>
+      <c r="W10">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>48.42286721481352</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1874563443034777</v>
+      </c>
+      <c r="C11">
+        <v>238.8468518787824</v>
+      </c>
+      <c r="D11">
+        <v>247.6438518787824</v>
+      </c>
+      <c r="E11">
+        <v>-170.803</v>
+      </c>
+      <c r="F11">
+        <v>20.097</v>
+      </c>
+      <c r="G11">
+        <v>11.3</v>
+      </c>
+      <c r="H11">
+        <v>32.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K11">
+        <v>8</v>
+      </c>
+      <c r="L11">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M11">
+        <v>0.8983359000000001</v>
+      </c>
+      <c r="N11">
+        <v>37.76833076666667</v>
+      </c>
+      <c r="O11">
+        <v>8.497874422500001</v>
+      </c>
+      <c r="P11">
+        <v>29.27045634416667</v>
+      </c>
+      <c r="Q11">
+        <v>37.27045634416667</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2025698014323931</v>
+      </c>
+      <c r="T11">
+        <v>1.05205047077846</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.225</v>
+      </c>
+      <c r="W11">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>43.0425486353898</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1870725200884404</v>
+      </c>
+      <c r="C12">
+        <v>237.2549127240387</v>
+      </c>
+      <c r="D12">
+        <v>248.2849127240388</v>
+      </c>
+      <c r="E12">
+        <v>-168.57</v>
+      </c>
+      <c r="F12">
+        <v>22.33</v>
+      </c>
+      <c r="G12">
+        <v>11.3</v>
+      </c>
+      <c r="H12">
+        <v>32.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K12">
+        <v>8</v>
+      </c>
+      <c r="L12">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M12">
+        <v>0.9981510000000001</v>
+      </c>
+      <c r="N12">
+        <v>37.66851566666667</v>
+      </c>
+      <c r="O12">
+        <v>8.475416025000001</v>
+      </c>
+      <c r="P12">
+        <v>29.19309964166667</v>
+      </c>
+      <c r="Q12">
+        <v>37.19309964166667</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2040091889871559</v>
+      </c>
+      <c r="T12">
+        <v>1.061297037247835</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.225</v>
+      </c>
+      <c r="W12">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>38.73829377185082</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.186688695873403</v>
+      </c>
+      <c r="C13">
+        <v>235.6663011349928</v>
+      </c>
+      <c r="D13">
+        <v>248.9293011349927</v>
+      </c>
+      <c r="E13">
+        <v>-166.337</v>
+      </c>
+      <c r="F13">
+        <v>24.563</v>
+      </c>
+      <c r="G13">
+        <v>11.3</v>
+      </c>
+      <c r="H13">
+        <v>32.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K13">
+        <v>8</v>
+      </c>
+      <c r="L13">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M13">
+        <v>1.0979661</v>
+      </c>
+      <c r="N13">
+        <v>37.56870056666667</v>
+      </c>
+      <c r="O13">
+        <v>8.452957627500002</v>
+      </c>
+      <c r="P13">
+        <v>29.11574293916667</v>
+      </c>
+      <c r="Q13">
+        <v>37.11574293916667</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2054809223296663</v>
+      </c>
+      <c r="T13">
+        <v>1.070751391727758</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.225</v>
+      </c>
+      <c r="W13">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>35.21663070168255</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1863048716583657</v>
+      </c>
+      <c r="C14">
+        <v>234.0810430877414</v>
+      </c>
+      <c r="D14">
+        <v>249.5770430877414</v>
+      </c>
+      <c r="E14">
+        <v>-164.104</v>
+      </c>
+      <c r="F14">
+        <v>26.796</v>
+      </c>
+      <c r="G14">
+        <v>11.3</v>
+      </c>
+      <c r="H14">
+        <v>32.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K14">
+        <v>8</v>
+      </c>
+      <c r="L14">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M14">
+        <v>1.1977812</v>
+      </c>
+      <c r="N14">
+        <v>37.46888546666667</v>
+      </c>
+      <c r="O14">
+        <v>8.430499230000001</v>
+      </c>
+      <c r="P14">
+        <v>29.03838623666667</v>
+      </c>
+      <c r="Q14">
+        <v>37.03838623666667</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2069861041572338</v>
+      </c>
+      <c r="T14">
+        <v>1.080420617900406</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.225</v>
+      </c>
+      <c r="W14">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>32.28191147654235</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1859210474433284</v>
+      </c>
+      <c r="C15">
+        <v>232.4991648294581</v>
+      </c>
+      <c r="D15">
+        <v>250.2281648294581</v>
+      </c>
+      <c r="E15">
+        <v>-161.871</v>
+      </c>
+      <c r="F15">
+        <v>29.029</v>
+      </c>
+      <c r="G15">
+        <v>11.3</v>
+      </c>
+      <c r="H15">
+        <v>32.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K15">
+        <v>8</v>
+      </c>
+      <c r="L15">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M15">
+        <v>1.2975963</v>
+      </c>
+      <c r="N15">
+        <v>37.36907036666667</v>
+      </c>
+      <c r="O15">
+        <v>8.408040832500001</v>
+      </c>
+      <c r="P15">
+        <v>28.96102953416667</v>
+      </c>
+      <c r="Q15">
+        <v>36.96102953416667</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2085258878658947</v>
+      </c>
+      <c r="T15">
+        <v>1.090312125134494</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.225</v>
+      </c>
+      <c r="W15">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>29.79868751680831</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.185537223228291</v>
+      </c>
+      <c r="C16">
+        <v>230.9206928819379</v>
+      </c>
+      <c r="D16">
+        <v>250.8826928819379</v>
+      </c>
+      <c r="E16">
+        <v>-159.638</v>
+      </c>
+      <c r="F16">
+        <v>31.262</v>
+      </c>
+      <c r="G16">
+        <v>11.3</v>
+      </c>
+      <c r="H16">
+        <v>32.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K16">
+        <v>8</v>
+      </c>
+      <c r="L16">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M16">
+        <v>1.3974114</v>
+      </c>
+      <c r="N16">
+        <v>37.26925526666667</v>
+      </c>
+      <c r="O16">
+        <v>8.385582435</v>
+      </c>
+      <c r="P16">
+        <v>28.88367283166667</v>
+      </c>
+      <c r="Q16">
+        <v>36.88367283166667</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2101014804980128</v>
+      </c>
+      <c r="T16">
+        <v>1.100433667420538</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.225</v>
+      </c>
+      <c r="W16">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>27.6702098370363</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1851533990132537</v>
+      </c>
+      <c r="C17">
+        <v>229.3456540451982</v>
+      </c>
+      <c r="D17">
+        <v>251.5406540451982</v>
+      </c>
+      <c r="E17">
+        <v>-157.405</v>
+      </c>
+      <c r="F17">
+        <v>33.495</v>
+      </c>
+      <c r="G17">
+        <v>11.3</v>
+      </c>
+      <c r="H17">
+        <v>32.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K17">
+        <v>8</v>
+      </c>
+      <c r="L17">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M17">
+        <v>1.4972265</v>
+      </c>
+      <c r="N17">
+        <v>37.16944016666667</v>
+      </c>
+      <c r="O17">
+        <v>8.363124037500002</v>
+      </c>
+      <c r="P17">
+        <v>28.80631612916667</v>
+      </c>
+      <c r="Q17">
+        <v>36.80631612916667</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2117141458979455</v>
+      </c>
+      <c r="T17">
+        <v>1.110793363642724</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.225</v>
+      </c>
+      <c r="W17">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>25.82552918123389</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1847695747982164</v>
+      </c>
+      <c r="C18">
+        <v>227.7740754011372</v>
+      </c>
+      <c r="D18">
+        <v>252.2020754011372</v>
+      </c>
+      <c r="E18">
+        <v>-155.172</v>
+      </c>
+      <c r="F18">
+        <v>35.728</v>
+      </c>
+      <c r="G18">
+        <v>11.3</v>
+      </c>
+      <c r="H18">
+        <v>32.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K18">
+        <v>8</v>
+      </c>
+      <c r="L18">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M18">
+        <v>1.5970416</v>
+      </c>
+      <c r="N18">
+        <v>37.06962506666667</v>
+      </c>
+      <c r="O18">
+        <v>8.340665640000003</v>
+      </c>
+      <c r="P18">
+        <v>28.72895942666667</v>
+      </c>
+      <c r="Q18">
+        <v>36.72895942666667</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2133652080931147</v>
+      </c>
+      <c r="T18">
+        <v>1.121399719298772</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.225</v>
+      </c>
+      <c r="W18">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>24.21143360740676</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.184385750583179</v>
+      </c>
+      <c r="C19">
+        <v>226.2059843172493</v>
+      </c>
+      <c r="D19">
+        <v>252.8669843172493</v>
+      </c>
+      <c r="E19">
+        <v>-152.939</v>
+      </c>
+      <c r="F19">
+        <v>37.96100000000001</v>
+      </c>
+      <c r="G19">
+        <v>11.3</v>
+      </c>
+      <c r="H19">
+        <v>32.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K19">
+        <v>8</v>
+      </c>
+      <c r="L19">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M19">
+        <v>1.6968567</v>
+      </c>
+      <c r="N19">
+        <v>36.96980996666667</v>
+      </c>
+      <c r="O19">
+        <v>8.318207242500002</v>
+      </c>
+      <c r="P19">
+        <v>28.65160272416667</v>
+      </c>
+      <c r="Q19">
+        <v>36.65160272416667</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2150560549194928</v>
+      </c>
+      <c r="T19">
+        <v>1.132261649789905</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.225</v>
+      </c>
+      <c r="W19">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>22.78723163050048</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1840019263681417</v>
+      </c>
+      <c r="C20">
+        <v>224.6414084503998</v>
+      </c>
+      <c r="D20">
+        <v>253.5354084503998</v>
+      </c>
+      <c r="E20">
+        <v>-150.706</v>
+      </c>
+      <c r="F20">
+        <v>40.194</v>
+      </c>
+      <c r="G20">
+        <v>11.3</v>
+      </c>
+      <c r="H20">
+        <v>32.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K20">
+        <v>8</v>
+      </c>
+      <c r="L20">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M20">
+        <v>1.7966718</v>
+      </c>
+      <c r="N20">
+        <v>36.86999486666667</v>
+      </c>
+      <c r="O20">
+        <v>8.295748845000002</v>
+      </c>
+      <c r="P20">
+        <v>28.57424602166667</v>
+      </c>
+      <c r="Q20">
+        <v>36.57424602166667</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2167881419123679</v>
+      </c>
+      <c r="T20">
+        <v>1.143388505414968</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.225</v>
+      </c>
+      <c r="W20">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>21.5212743176949</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1836181021531044</v>
+      </c>
+      <c r="C21">
+        <v>223.0803757506602</v>
+      </c>
+      <c r="D21">
+        <v>254.2073757506602</v>
+      </c>
+      <c r="E21">
+        <v>-148.473</v>
+      </c>
+      <c r="F21">
+        <v>42.427</v>
+      </c>
+      <c r="G21">
+        <v>11.3</v>
+      </c>
+      <c r="H21">
+        <v>32.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K21">
+        <v>8</v>
+      </c>
+      <c r="L21">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M21">
+        <v>1.8964869</v>
+      </c>
+      <c r="N21">
+        <v>36.77017976666667</v>
+      </c>
+      <c r="O21">
+        <v>8.273290447500001</v>
+      </c>
+      <c r="P21">
+        <v>28.49688931916667</v>
+      </c>
+      <c r="Q21">
+        <v>36.49688931916667</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.218562996485314</v>
+      </c>
+      <c r="T21">
+        <v>1.154790098215959</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.225</v>
+      </c>
+      <c r="W21">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>20.38857566939517</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1832342779380671</v>
+      </c>
+      <c r="C22">
+        <v>221.5229144652029</v>
+      </c>
+      <c r="D22">
+        <v>254.882914465203</v>
+      </c>
+      <c r="E22">
+        <v>-146.24</v>
+      </c>
+      <c r="F22">
+        <v>44.66</v>
+      </c>
+      <c r="G22">
+        <v>11.3</v>
+      </c>
+      <c r="H22">
+        <v>32.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K22">
+        <v>8</v>
+      </c>
+      <c r="L22">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M22">
+        <v>1.996302</v>
+      </c>
+      <c r="N22">
+        <v>36.67036466666667</v>
+      </c>
+      <c r="O22">
+        <v>8.250832050000001</v>
+      </c>
+      <c r="P22">
+        <v>28.41953261666667</v>
+      </c>
+      <c r="Q22">
+        <v>36.41953261666667</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2203822224225838</v>
+      </c>
+      <c r="T22">
+        <v>1.166476730836975</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.225</v>
+      </c>
+      <c r="W22">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>19.36914688592541</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1828504537230297</v>
+      </c>
+      <c r="C23">
+        <v>219.9690531422608</v>
+      </c>
+      <c r="D23">
+        <v>255.5620531422608</v>
+      </c>
+      <c r="E23">
+        <v>-144.007</v>
+      </c>
+      <c r="F23">
+        <v>46.893</v>
+      </c>
+      <c r="G23">
+        <v>11.3</v>
+      </c>
+      <c r="H23">
+        <v>32.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K23">
+        <v>8</v>
+      </c>
+      <c r="L23">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M23">
+        <v>2.0961171</v>
+      </c>
+      <c r="N23">
+        <v>36.57054956666667</v>
+      </c>
+      <c r="O23">
+        <v>8.228373652500002</v>
+      </c>
+      <c r="P23">
+        <v>28.34217591416667</v>
+      </c>
+      <c r="Q23">
+        <v>36.34217591416667</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2222475047126958</v>
+      </c>
+      <c r="T23">
+        <v>1.178459227574978</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.225</v>
+      </c>
+      <c r="W23">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>18.4468065580242</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1824666295079924</v>
+      </c>
+      <c r="C24">
+        <v>218.4188206351475</v>
+      </c>
+      <c r="D24">
+        <v>256.2448206351474</v>
+      </c>
+      <c r="E24">
+        <v>-141.774</v>
+      </c>
+      <c r="F24">
+        <v>49.126</v>
+      </c>
+      <c r="G24">
+        <v>11.3</v>
+      </c>
+      <c r="H24">
+        <v>32.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K24">
+        <v>8</v>
+      </c>
+      <c r="L24">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M24">
+        <v>2.195932200000001</v>
+      </c>
+      <c r="N24">
+        <v>36.47073446666667</v>
+      </c>
+      <c r="O24">
+        <v>8.205915255000001</v>
+      </c>
+      <c r="P24">
+        <v>28.26481921166667</v>
+      </c>
+      <c r="Q24">
+        <v>36.26481921166667</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2241606147538364</v>
+      </c>
+      <c r="T24">
+        <v>1.190748967819084</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.225</v>
+      </c>
+      <c r="W24">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>17.60831535084128</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1820828052929551</v>
+      </c>
+      <c r="C25">
+        <v>216.8722461063446</v>
+      </c>
+      <c r="D25">
+        <v>256.9312461063446</v>
+      </c>
+      <c r="E25">
+        <v>-139.541</v>
+      </c>
+      <c r="F25">
+        <v>51.359</v>
+      </c>
+      <c r="G25">
+        <v>11.3</v>
+      </c>
+      <c r="H25">
+        <v>32.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K25">
+        <v>8</v>
+      </c>
+      <c r="L25">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M25">
+        <v>2.2957473</v>
+      </c>
+      <c r="N25">
+        <v>36.37091936666667</v>
+      </c>
+      <c r="O25">
+        <v>8.183456857500001</v>
+      </c>
+      <c r="P25">
+        <v>28.18746250916667</v>
+      </c>
+      <c r="Q25">
+        <v>36.18746250916666</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2261234159648767</v>
+      </c>
+      <c r="T25">
+        <v>1.203357922095504</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.225</v>
+      </c>
+      <c r="W25">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>16.84273642254383</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1816989810779177</v>
+      </c>
+      <c r="C26">
+        <v>215.3293590316535</v>
+      </c>
+      <c r="D26">
+        <v>257.6213590316535</v>
+      </c>
+      <c r="E26">
+        <v>-137.308</v>
+      </c>
+      <c r="F26">
+        <v>53.592</v>
+      </c>
+      <c r="G26">
+        <v>11.3</v>
+      </c>
+      <c r="H26">
+        <v>32.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K26">
+        <v>8</v>
+      </c>
+      <c r="L26">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M26">
+        <v>2.3955624</v>
+      </c>
+      <c r="N26">
+        <v>36.27110426666667</v>
+      </c>
+      <c r="O26">
+        <v>8.16099846</v>
+      </c>
+      <c r="P26">
+        <v>28.11010580666667</v>
+      </c>
+      <c r="Q26">
+        <v>36.11010580666667</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2281378698393654</v>
+      </c>
+      <c r="T26">
+        <v>1.216298690958146</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.225</v>
+      </c>
+      <c r="W26">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>16.14095573827117</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1813151568628804</v>
+      </c>
+      <c r="C27">
+        <v>213.7901892044141</v>
+      </c>
+      <c r="D27">
+        <v>258.3151892044141</v>
+      </c>
+      <c r="E27">
+        <v>-135.075</v>
+      </c>
+      <c r="F27">
+        <v>55.825</v>
+      </c>
+      <c r="G27">
+        <v>11.3</v>
+      </c>
+      <c r="H27">
+        <v>32.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K27">
+        <v>8</v>
+      </c>
+      <c r="L27">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M27">
+        <v>2.4953775</v>
+      </c>
+      <c r="N27">
+        <v>36.17128916666667</v>
+      </c>
+      <c r="O27">
+        <v>8.138540062500001</v>
+      </c>
+      <c r="P27">
+        <v>28.03274910416667</v>
+      </c>
+      <c r="Q27">
+        <v>36.03274910416667</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2302060424838405</v>
+      </c>
+      <c r="T27">
+        <v>1.229584546990458</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.225</v>
+      </c>
+      <c r="W27">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>15.49531750874032</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1809313326478431</v>
+      </c>
+      <c r="C28">
+        <v>212.254766739793</v>
+      </c>
+      <c r="D28">
+        <v>259.0127667397929</v>
+      </c>
+      <c r="E28">
+        <v>-132.842</v>
+      </c>
+      <c r="F28">
+        <v>58.05800000000001</v>
+      </c>
+      <c r="G28">
+        <v>11.3</v>
+      </c>
+      <c r="H28">
+        <v>32.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K28">
+        <v>8</v>
+      </c>
+      <c r="L28">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M28">
+        <v>2.595192600000001</v>
+      </c>
+      <c r="N28">
+        <v>36.07147406666667</v>
+      </c>
+      <c r="O28">
+        <v>8.116081665000001</v>
+      </c>
+      <c r="P28">
+        <v>27.95539240166666</v>
+      </c>
+      <c r="Q28">
+        <v>35.95539240166666</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2323301116862745</v>
+      </c>
+      <c r="T28">
+        <v>1.243229480212834</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.225</v>
+      </c>
+      <c r="W28">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>14.89934375840416</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1805475084328057</v>
+      </c>
+      <c r="C29">
+        <v>210.7231220791405</v>
+      </c>
+      <c r="D29">
+        <v>259.7141220791405</v>
+      </c>
+      <c r="E29">
+        <v>-130.609</v>
+      </c>
+      <c r="F29">
+        <v>60.291</v>
+      </c>
+      <c r="G29">
+        <v>11.3</v>
+      </c>
+      <c r="H29">
+        <v>32.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K29">
+        <v>8</v>
+      </c>
+      <c r="L29">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M29">
+        <v>2.695007700000001</v>
+      </c>
+      <c r="N29">
+        <v>35.97165896666667</v>
+      </c>
+      <c r="O29">
+        <v>8.093623267500002</v>
+      </c>
+      <c r="P29">
+        <v>27.87803569916667</v>
+      </c>
+      <c r="Q29">
+        <v>35.87803569916667</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2345123745654873</v>
+      </c>
+      <c r="T29">
+        <v>1.257248247222123</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.225</v>
+      </c>
+      <c r="W29">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>14.3475162117966</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1801636842177684</v>
+      </c>
+      <c r="C30">
+        <v>209.1952859944185</v>
+      </c>
+      <c r="D30">
+        <v>260.4192859944185</v>
+      </c>
+      <c r="E30">
+        <v>-128.376</v>
+      </c>
+      <c r="F30">
+        <v>62.52400000000001</v>
+      </c>
+      <c r="G30">
+        <v>11.3</v>
+      </c>
+      <c r="H30">
+        <v>32.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K30">
+        <v>8</v>
+      </c>
+      <c r="L30">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M30">
+        <v>2.7948228</v>
+      </c>
+      <c r="N30">
+        <v>35.87184386666667</v>
+      </c>
+      <c r="O30">
+        <v>8.071164870000002</v>
+      </c>
+      <c r="P30">
+        <v>27.80067899666667</v>
+      </c>
+      <c r="Q30">
+        <v>35.80067899666667</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2367552558580117</v>
+      </c>
+      <c r="T30">
+        <v>1.271656424426114</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.225</v>
+      </c>
+      <c r="W30">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>13.83510491851815</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1797798600027311</v>
+      </c>
+      <c r="C31">
+        <v>207.6712895927017</v>
+      </c>
+      <c r="D31">
+        <v>261.1282895927017</v>
+      </c>
+      <c r="E31">
+        <v>-126.143</v>
+      </c>
+      <c r="F31">
+        <v>64.75700000000001</v>
+      </c>
+      <c r="G31">
+        <v>11.3</v>
+      </c>
+      <c r="H31">
+        <v>32.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K31">
+        <v>8</v>
+      </c>
+      <c r="L31">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M31">
+        <v>2.894637900000001</v>
+      </c>
+      <c r="N31">
+        <v>35.77202876666667</v>
+      </c>
+      <c r="O31">
+        <v>8.048706472500001</v>
+      </c>
+      <c r="P31">
+        <v>27.72332229416667</v>
+      </c>
+      <c r="Q31">
+        <v>35.72332229416667</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.239061316905255</v>
+      </c>
+      <c r="T31">
+        <v>1.286470465776697</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.225</v>
+      </c>
+      <c r="W31">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>13.35803233512097</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1793960357876938</v>
+      </c>
+      <c r="C32">
+        <v>206.151164320751</v>
+      </c>
+      <c r="D32">
+        <v>261.841164320751</v>
+      </c>
+      <c r="E32">
+        <v>-123.91</v>
+      </c>
+      <c r="F32">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="G32">
+        <v>11.3</v>
+      </c>
+      <c r="H32">
+        <v>32.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K32">
+        <v>8</v>
+      </c>
+      <c r="L32">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M32">
+        <v>2.994453</v>
+      </c>
+      <c r="N32">
+        <v>35.67221366666667</v>
+      </c>
+      <c r="O32">
+        <v>8.026248075000002</v>
+      </c>
+      <c r="P32">
+        <v>27.64596559166667</v>
+      </c>
+      <c r="Q32">
+        <v>35.64596559166667</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2414332654109911</v>
+      </c>
+      <c r="T32">
+        <v>1.301707765451583</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.225</v>
+      </c>
+      <c r="W32">
+        <v>0.03464250000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>12.91276459061694</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1792764865726564</v>
+      </c>
+      <c r="C33">
+        <v>204.140998094735</v>
+      </c>
+      <c r="D33">
+        <v>262.063998094735</v>
+      </c>
+      <c r="E33">
+        <v>-121.677</v>
+      </c>
+      <c r="F33">
+        <v>69.223</v>
+      </c>
+      <c r="G33">
+        <v>11.3</v>
+      </c>
+      <c r="H33">
+        <v>32.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K33">
+        <v>8</v>
+      </c>
+      <c r="L33">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M33">
+        <v>3.1704134</v>
+      </c>
+      <c r="N33">
+        <v>35.49625326666667</v>
+      </c>
+      <c r="O33">
+        <v>7.986656985000001</v>
+      </c>
+      <c r="P33">
+        <v>27.50959628166667</v>
+      </c>
+      <c r="Q33">
+        <v>35.50959628166667</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2438739660473281</v>
+      </c>
+      <c r="T33">
+        <v>1.31738672598661</v>
+      </c>
+      <c r="U33">
+        <v>0.0458</v>
+      </c>
+      <c r="V33">
+        <v>0.225</v>
+      </c>
+      <c r="W33">
+        <v>0.035495</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>12.19609615158284</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1789011873576191</v>
+      </c>
+      <c r="C34">
+        <v>202.6100079394014</v>
+      </c>
+      <c r="D34">
+        <v>262.7660079394014</v>
+      </c>
+      <c r="E34">
+        <v>-119.444</v>
+      </c>
+      <c r="F34">
+        <v>71.456</v>
+      </c>
+      <c r="G34">
+        <v>11.3</v>
+      </c>
+      <c r="H34">
+        <v>32.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K34">
+        <v>8</v>
+      </c>
+      <c r="L34">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M34">
+        <v>3.2726848</v>
+      </c>
+      <c r="N34">
+        <v>35.39398186666667</v>
+      </c>
+      <c r="O34">
+        <v>7.963645920000001</v>
+      </c>
+      <c r="P34">
+        <v>27.43033594666667</v>
+      </c>
+      <c r="Q34">
+        <v>35.43033594666667</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2463864519964987</v>
+      </c>
+      <c r="T34">
+        <v>1.333526832419726</v>
+      </c>
+      <c r="U34">
+        <v>0.0458</v>
+      </c>
+      <c r="V34">
+        <v>0.225</v>
+      </c>
+      <c r="W34">
+        <v>0.035495</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>11.81496814684588</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1785258881425818</v>
+      </c>
+      <c r="C35">
+        <v>201.0827889355294</v>
+      </c>
+      <c r="D35">
+        <v>263.4717889355294</v>
+      </c>
+      <c r="E35">
+        <v>-117.211</v>
+      </c>
+      <c r="F35">
+        <v>73.68900000000001</v>
+      </c>
+      <c r="G35">
+        <v>11.3</v>
+      </c>
+      <c r="H35">
+        <v>32.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K35">
+        <v>8</v>
+      </c>
+      <c r="L35">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M35">
+        <v>3.3749562</v>
+      </c>
+      <c r="N35">
+        <v>35.29171046666667</v>
+      </c>
+      <c r="O35">
+        <v>7.940634855000002</v>
+      </c>
+      <c r="P35">
+        <v>27.35107561166667</v>
+      </c>
+      <c r="Q35">
+        <v>35.35107561166667</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2489739375262415</v>
+      </c>
+      <c r="T35">
+        <v>1.350148733074726</v>
+      </c>
+      <c r="U35">
+        <v>0.0458</v>
+      </c>
+      <c r="V35">
+        <v>0.225</v>
+      </c>
+      <c r="W35">
+        <v>0.035495</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>11.45693880906267</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1781505889275444</v>
+      </c>
+      <c r="C36">
+        <v>199.5593715525316</v>
+      </c>
+      <c r="D36">
+        <v>264.1813715525316</v>
+      </c>
+      <c r="E36">
+        <v>-114.978</v>
+      </c>
+      <c r="F36">
+        <v>75.92200000000001</v>
+      </c>
+      <c r="G36">
+        <v>11.3</v>
+      </c>
+      <c r="H36">
+        <v>32.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K36">
+        <v>8</v>
+      </c>
+      <c r="L36">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M36">
+        <v>3.4772276</v>
+      </c>
+      <c r="N36">
+        <v>35.18943906666667</v>
+      </c>
+      <c r="O36">
+        <v>7.917623790000001</v>
+      </c>
+      <c r="P36">
+        <v>27.27181527666667</v>
+      </c>
+      <c r="Q36">
+        <v>35.27181527666667</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2516398317084007</v>
+      </c>
+      <c r="T36">
+        <v>1.367274327688969</v>
+      </c>
+      <c r="U36">
+        <v>0.0458</v>
+      </c>
+      <c r="V36">
+        <v>0.225</v>
+      </c>
+      <c r="W36">
+        <v>0.035495</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>11.11997002056082</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1777752897125071</v>
+      </c>
+      <c r="C37">
+        <v>198.0397865889474</v>
+      </c>
+      <c r="D37">
+        <v>264.8947865889475</v>
+      </c>
+      <c r="E37">
+        <v>-112.745</v>
+      </c>
+      <c r="F37">
+        <v>78.15500000000002</v>
+      </c>
+      <c r="G37">
+        <v>11.3</v>
+      </c>
+      <c r="H37">
+        <v>32.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K37">
+        <v>8</v>
+      </c>
+      <c r="L37">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M37">
+        <v>3.579499000000001</v>
+      </c>
+      <c r="N37">
+        <v>35.08716766666667</v>
+      </c>
+      <c r="O37">
+        <v>7.894612725000002</v>
+      </c>
+      <c r="P37">
+        <v>27.19255494166667</v>
+      </c>
+      <c r="Q37">
+        <v>35.19255494166667</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2543877534038571</v>
+      </c>
+      <c r="T37">
+        <v>1.384926863675957</v>
+      </c>
+      <c r="U37">
+        <v>0.0458</v>
+      </c>
+      <c r="V37">
+        <v>0.225</v>
+      </c>
+      <c r="W37">
+        <v>0.035495</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>10.80225659140194</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1773999904974698</v>
+      </c>
+      <c r="C38">
+        <v>196.5240651769002</v>
+      </c>
+      <c r="D38">
+        <v>265.6120651769002</v>
+      </c>
+      <c r="E38">
+        <v>-110.512</v>
+      </c>
+      <c r="F38">
+        <v>80.38800000000001</v>
+      </c>
+      <c r="G38">
+        <v>11.3</v>
+      </c>
+      <c r="H38">
+        <v>32.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K38">
+        <v>8</v>
+      </c>
+      <c r="L38">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M38">
+        <v>3.6817704</v>
+      </c>
+      <c r="N38">
+        <v>34.98489626666667</v>
+      </c>
+      <c r="O38">
+        <v>7.871601660000001</v>
+      </c>
+      <c r="P38">
+        <v>27.11329460666667</v>
+      </c>
+      <c r="Q38">
+        <v>35.11329460666667</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2572215476522965</v>
+      </c>
+      <c r="T38">
+        <v>1.403131041412539</v>
+      </c>
+      <c r="U38">
+        <v>0.0458</v>
+      </c>
+      <c r="V38">
+        <v>0.225</v>
+      </c>
+      <c r="W38">
+        <v>0.035495</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>10.50219390830745</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1770246912824325</v>
+      </c>
+      <c r="C39">
+        <v>195.0122387866257</v>
+      </c>
+      <c r="D39">
+        <v>266.3332387866257</v>
+      </c>
+      <c r="E39">
+        <v>-108.279</v>
+      </c>
+      <c r="F39">
+        <v>82.62100000000001</v>
+      </c>
+      <c r="G39">
+        <v>11.3</v>
+      </c>
+      <c r="H39">
+        <v>32.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K39">
+        <v>8</v>
+      </c>
+      <c r="L39">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M39">
+        <v>3.784041800000001</v>
+      </c>
+      <c r="N39">
+        <v>34.88262486666667</v>
+      </c>
+      <c r="O39">
+        <v>7.848590595000002</v>
+      </c>
+      <c r="P39">
+        <v>27.03403427166667</v>
+      </c>
+      <c r="Q39">
+        <v>35.03403427166667</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2601453036229087</v>
+      </c>
+      <c r="T39">
+        <v>1.421913129553457</v>
+      </c>
+      <c r="U39">
+        <v>0.0458</v>
+      </c>
+      <c r="V39">
+        <v>0.225</v>
+      </c>
+      <c r="W39">
+        <v>0.035495</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>10.21835082970454</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1772972920673951</v>
+      </c>
+      <c r="C40">
+        <v>192.2550216783263</v>
+      </c>
+      <c r="D40">
+        <v>265.8090216783262</v>
+      </c>
+      <c r="E40">
+        <v>-106.046</v>
+      </c>
+      <c r="F40">
+        <v>84.854</v>
+      </c>
+      <c r="G40">
+        <v>11.3</v>
+      </c>
+      <c r="H40">
+        <v>32.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K40">
+        <v>8</v>
+      </c>
+      <c r="L40">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M40">
+        <v>4.072992</v>
+      </c>
+      <c r="N40">
+        <v>34.59367466666667</v>
+      </c>
+      <c r="O40">
+        <v>7.783576800000001</v>
+      </c>
+      <c r="P40">
+        <v>26.81009786666667</v>
+      </c>
+      <c r="Q40">
+        <v>34.81009786666667</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2631633743022501</v>
+      </c>
+      <c r="T40">
+        <v>1.441301091505372</v>
+      </c>
+      <c r="U40">
+        <v>0.048</v>
+      </c>
+      <c r="V40">
+        <v>0.225</v>
+      </c>
+      <c r="W40">
+        <v>0.0372</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>9.493430546062125</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1769390428523577</v>
+      </c>
+      <c r="C41">
+        <v>190.7113696816123</v>
+      </c>
+      <c r="D41">
+        <v>266.4983696816122</v>
+      </c>
+      <c r="E41">
+        <v>-103.813</v>
+      </c>
+      <c r="F41">
+        <v>87.087</v>
+      </c>
+      <c r="G41">
+        <v>11.3</v>
+      </c>
+      <c r="H41">
+        <v>32.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K41">
+        <v>8</v>
+      </c>
+      <c r="L41">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M41">
+        <v>4.180176</v>
+      </c>
+      <c r="N41">
+        <v>34.48649066666667</v>
+      </c>
+      <c r="O41">
+        <v>7.759460400000001</v>
+      </c>
+      <c r="P41">
+        <v>26.72703026666667</v>
+      </c>
+      <c r="Q41">
+        <v>34.72703026666667</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2662803981186193</v>
+      </c>
+      <c r="T41">
+        <v>1.461324724340956</v>
+      </c>
+      <c r="U41">
+        <v>0.048</v>
+      </c>
+      <c r="V41">
+        <v>0.225</v>
+      </c>
+      <c r="W41">
+        <v>0.0372</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>9.250009250009249</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1765807936373204</v>
+      </c>
+      <c r="C42">
+        <v>189.1713024861544</v>
+      </c>
+      <c r="D42">
+        <v>267.1913024861544</v>
+      </c>
+      <c r="E42">
+        <v>-101.58</v>
+      </c>
+      <c r="F42">
+        <v>89.32000000000001</v>
+      </c>
+      <c r="G42">
+        <v>11.3</v>
+      </c>
+      <c r="H42">
+        <v>32.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K42">
+        <v>8</v>
+      </c>
+      <c r="L42">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M42">
+        <v>4.287360000000001</v>
+      </c>
+      <c r="N42">
+        <v>34.37930666666667</v>
+      </c>
+      <c r="O42">
+        <v>7.735344000000001</v>
+      </c>
+      <c r="P42">
+        <v>26.64396266666667</v>
+      </c>
+      <c r="Q42">
+        <v>34.64396266666667</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2695013227288674</v>
+      </c>
+      <c r="T42">
+        <v>1.482015811604394</v>
+      </c>
+      <c r="U42">
+        <v>0.048</v>
+      </c>
+      <c r="V42">
+        <v>0.225</v>
+      </c>
+      <c r="W42">
+        <v>0.0372</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>9.018759018759019</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1762225444222831</v>
+      </c>
+      <c r="C43">
+        <v>187.6348481277947</v>
+      </c>
+      <c r="D43">
+        <v>267.8878481277947</v>
+      </c>
+      <c r="E43">
+        <v>-99.34699999999999</v>
+      </c>
+      <c r="F43">
+        <v>91.55300000000001</v>
+      </c>
+      <c r="G43">
+        <v>11.3</v>
+      </c>
+      <c r="H43">
+        <v>32.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K43">
+        <v>8</v>
+      </c>
+      <c r="L43">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M43">
+        <v>4.394544000000001</v>
+      </c>
+      <c r="N43">
+        <v>34.27212266666667</v>
+      </c>
+      <c r="O43">
+        <v>7.711227600000001</v>
+      </c>
+      <c r="P43">
+        <v>26.56089506666667</v>
+      </c>
+      <c r="Q43">
+        <v>34.56089506666667</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2728314312242087</v>
+      </c>
+      <c r="T43">
+        <v>1.503408291656422</v>
+      </c>
+      <c r="U43">
+        <v>0.048</v>
+      </c>
+      <c r="V43">
+        <v>0.225</v>
+      </c>
+      <c r="W43">
+        <v>0.0372</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>8.798789286594165</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1758642952072458</v>
+      </c>
+      <c r="C44">
+        <v>186.1020349354875</v>
+      </c>
+      <c r="D44">
+        <v>268.5880349354875</v>
+      </c>
+      <c r="E44">
+        <v>-97.114</v>
+      </c>
+      <c r="F44">
+        <v>93.786</v>
+      </c>
+      <c r="G44">
+        <v>11.3</v>
+      </c>
+      <c r="H44">
+        <v>32.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K44">
+        <v>8</v>
+      </c>
+      <c r="L44">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M44">
+        <v>4.501728</v>
+      </c>
+      <c r="N44">
+        <v>34.16493866666667</v>
+      </c>
+      <c r="O44">
+        <v>7.687111200000001</v>
+      </c>
+      <c r="P44">
+        <v>26.47782746666667</v>
+      </c>
+      <c r="Q44">
+        <v>34.47782746666667</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2762763710469754</v>
+      </c>
+      <c r="T44">
+        <v>1.525538443434382</v>
+      </c>
+      <c r="U44">
+        <v>0.048</v>
+      </c>
+      <c r="V44">
+        <v>0.225</v>
+      </c>
+      <c r="W44">
+        <v>0.0372</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>8.589294303580019</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1755060459922085</v>
+      </c>
+      <c r="C45">
+        <v>184.5728915351402</v>
+      </c>
+      <c r="D45">
+        <v>269.2918915351402</v>
+      </c>
+      <c r="E45">
+        <v>-94.881</v>
+      </c>
+      <c r="F45">
+        <v>96.01900000000001</v>
+      </c>
+      <c r="G45">
+        <v>11.3</v>
+      </c>
+      <c r="H45">
+        <v>32.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K45">
+        <v>8</v>
+      </c>
+      <c r="L45">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M45">
+        <v>4.608912</v>
+      </c>
+      <c r="N45">
+        <v>34.05775466666667</v>
+      </c>
+      <c r="O45">
+        <v>7.662994800000001</v>
+      </c>
+      <c r="P45">
+        <v>26.39475986666667</v>
+      </c>
+      <c r="Q45">
+        <v>34.39475986666667</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2798421859512429</v>
+      </c>
+      <c r="T45">
+        <v>1.548445091765956</v>
+      </c>
+      <c r="U45">
+        <v>0.048</v>
+      </c>
+      <c r="V45">
+        <v>0.225</v>
+      </c>
+      <c r="W45">
+        <v>0.0372</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>8.389543273264204</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1751477967771712</v>
+      </c>
+      <c r="C46">
+        <v>183.0474468535151</v>
+      </c>
+      <c r="D46">
+        <v>269.9994468535151</v>
+      </c>
+      <c r="E46">
+        <v>-92.648</v>
+      </c>
+      <c r="F46">
+        <v>98.25200000000001</v>
+      </c>
+      <c r="G46">
+        <v>11.3</v>
+      </c>
+      <c r="H46">
+        <v>32.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K46">
+        <v>8</v>
+      </c>
+      <c r="L46">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M46">
+        <v>4.716096</v>
+      </c>
+      <c r="N46">
+        <v>33.95057066666667</v>
+      </c>
+      <c r="O46">
+        <v>7.638878400000001</v>
+      </c>
+      <c r="P46">
+        <v>26.31169226666667</v>
+      </c>
+      <c r="Q46">
+        <v>34.31169226666667</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2835353513878056</v>
+      </c>
+      <c r="T46">
+        <v>1.572169834680799</v>
+      </c>
+      <c r="U46">
+        <v>0.048</v>
+      </c>
+      <c r="V46">
+        <v>0.225</v>
+      </c>
+      <c r="W46">
+        <v>0.0372</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>8.198871835235472</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1747895475621338</v>
+      </c>
+      <c r="C47">
+        <v>181.5257301221913</v>
+      </c>
+      <c r="D47">
+        <v>270.7107301221913</v>
+      </c>
+      <c r="E47">
+        <v>-90.41499999999999</v>
+      </c>
+      <c r="F47">
+        <v>100.485</v>
+      </c>
+      <c r="G47">
+        <v>11.3</v>
+      </c>
+      <c r="H47">
+        <v>32.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K47">
+        <v>8</v>
+      </c>
+      <c r="L47">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M47">
+        <v>4.82328</v>
+      </c>
+      <c r="N47">
+        <v>33.84338666666667</v>
+      </c>
+      <c r="O47">
+        <v>7.614762000000002</v>
+      </c>
+      <c r="P47">
+        <v>26.22862466666667</v>
+      </c>
+      <c r="Q47">
+        <v>34.22862466666668</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2873628137493341</v>
+      </c>
+      <c r="T47">
+        <v>1.596757295519819</v>
+      </c>
+      <c r="U47">
+        <v>0.048</v>
+      </c>
+      <c r="V47">
+        <v>0.225</v>
+      </c>
+      <c r="W47">
+        <v>0.0372</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>8.01667468334135</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1744312983470965</v>
+      </c>
+      <c r="C48">
+        <v>180.0077708815908</v>
+      </c>
+      <c r="D48">
+        <v>271.4257708815908</v>
+      </c>
+      <c r="E48">
+        <v>-88.182</v>
+      </c>
+      <c r="F48">
+        <v>102.718</v>
+      </c>
+      <c r="G48">
+        <v>11.3</v>
+      </c>
+      <c r="H48">
+        <v>32.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K48">
+        <v>8</v>
+      </c>
+      <c r="L48">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M48">
+        <v>4.930464000000001</v>
+      </c>
+      <c r="N48">
+        <v>33.73620266666667</v>
+      </c>
+      <c r="O48">
+        <v>7.590645600000001</v>
+      </c>
+      <c r="P48">
+        <v>26.14555706666667</v>
+      </c>
+      <c r="Q48">
+        <v>34.14555706666667</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2913320339761045</v>
+      </c>
+      <c r="T48">
+        <v>1.62225540305658</v>
+      </c>
+      <c r="U48">
+        <v>0.048</v>
+      </c>
+      <c r="V48">
+        <v>0.225</v>
+      </c>
+      <c r="W48">
+        <v>0.0372</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>7.842399146746973</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1746194241320591</v>
+      </c>
+      <c r="C49">
+        <v>177.3988144487574</v>
+      </c>
+      <c r="D49">
+        <v>271.0498144487574</v>
+      </c>
+      <c r="E49">
+        <v>-85.949</v>
+      </c>
+      <c r="F49">
+        <v>104.951</v>
+      </c>
+      <c r="G49">
+        <v>11.3</v>
+      </c>
+      <c r="H49">
+        <v>32.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K49">
+        <v>8</v>
+      </c>
+      <c r="L49">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M49">
+        <v>5.1950745</v>
+      </c>
+      <c r="N49">
+        <v>33.47159216666667</v>
+      </c>
+      <c r="O49">
+        <v>7.531108237500001</v>
+      </c>
+      <c r="P49">
+        <v>25.94048392916667</v>
+      </c>
+      <c r="Q49">
+        <v>33.94048392916667</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2954510360982248</v>
+      </c>
+      <c r="T49">
+        <v>1.648715703330577</v>
+      </c>
+      <c r="U49">
+        <v>0.0495</v>
+      </c>
+      <c r="V49">
+        <v>0.225</v>
+      </c>
+      <c r="W49">
+        <v>0.0383625</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>7.442947481632201</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1742727999170218</v>
+      </c>
+      <c r="C50">
+        <v>175.8593295250446</v>
+      </c>
+      <c r="D50">
+        <v>271.7433295250446</v>
+      </c>
+      <c r="E50">
+        <v>-83.71600000000001</v>
+      </c>
+      <c r="F50">
+        <v>107.184</v>
+      </c>
+      <c r="G50">
+        <v>11.3</v>
+      </c>
+      <c r="H50">
+        <v>32.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K50">
+        <v>8</v>
+      </c>
+      <c r="L50">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M50">
+        <v>5.305608</v>
+      </c>
+      <c r="N50">
+        <v>33.36105866666667</v>
+      </c>
+      <c r="O50">
+        <v>7.506238200000001</v>
+      </c>
+      <c r="P50">
+        <v>25.85482046666667</v>
+      </c>
+      <c r="Q50">
+        <v>33.85482046666667</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2997284613788881</v>
+      </c>
+      <c r="T50">
+        <v>1.676193707461267</v>
+      </c>
+      <c r="U50">
+        <v>0.0495</v>
+      </c>
+      <c r="V50">
+        <v>0.225</v>
+      </c>
+      <c r="W50">
+        <v>0.0383625</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>7.287886075764864</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1739261757019844</v>
+      </c>
+      <c r="C51">
+        <v>174.3234025961868</v>
+      </c>
+      <c r="D51">
+        <v>272.4404025961867</v>
+      </c>
+      <c r="E51">
+        <v>-81.483</v>
+      </c>
+      <c r="F51">
+        <v>109.417</v>
+      </c>
+      <c r="G51">
+        <v>11.3</v>
+      </c>
+      <c r="H51">
+        <v>32.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K51">
+        <v>8</v>
+      </c>
+      <c r="L51">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M51">
+        <v>5.4161415</v>
+      </c>
+      <c r="N51">
+        <v>33.25052516666667</v>
+      </c>
+      <c r="O51">
+        <v>7.481368162500001</v>
+      </c>
+      <c r="P51">
+        <v>25.76915700416667</v>
+      </c>
+      <c r="Q51">
+        <v>33.76915700416667</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3041736288274205</v>
+      </c>
+      <c r="T51">
+        <v>1.704749280381395</v>
+      </c>
+      <c r="U51">
+        <v>0.0495</v>
+      </c>
+      <c r="V51">
+        <v>0.225</v>
+      </c>
+      <c r="W51">
+        <v>0.0383625</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>7.139153706871704</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1735795514869471</v>
+      </c>
+      <c r="C52">
+        <v>172.7910611133914</v>
+      </c>
+      <c r="D52">
+        <v>273.1410611133913</v>
+      </c>
+      <c r="E52">
+        <v>-79.25</v>
+      </c>
+      <c r="F52">
+        <v>111.65</v>
+      </c>
+      <c r="G52">
+        <v>11.3</v>
+      </c>
+      <c r="H52">
+        <v>32.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K52">
+        <v>8</v>
+      </c>
+      <c r="L52">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M52">
+        <v>5.526675000000001</v>
+      </c>
+      <c r="N52">
+        <v>33.13999166666667</v>
+      </c>
+      <c r="O52">
+        <v>7.456498125000002</v>
+      </c>
+      <c r="P52">
+        <v>25.68349354166667</v>
+      </c>
+      <c r="Q52">
+        <v>33.68349354166667</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3087966029738943</v>
+      </c>
+      <c r="T52">
+        <v>1.734447076218329</v>
+      </c>
+      <c r="U52">
+        <v>0.0495</v>
+      </c>
+      <c r="V52">
+        <v>0.225</v>
+      </c>
+      <c r="W52">
+        <v>0.0383625</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>6.996370632734269</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1732329272719098</v>
+      </c>
+      <c r="C53">
+        <v>171.2623328109895</v>
+      </c>
+      <c r="D53">
+        <v>273.8453328109895</v>
+      </c>
+      <c r="E53">
+        <v>-77.017</v>
+      </c>
+      <c r="F53">
+        <v>113.883</v>
+      </c>
+      <c r="G53">
+        <v>11.3</v>
+      </c>
+      <c r="H53">
+        <v>32.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K53">
+        <v>8</v>
+      </c>
+      <c r="L53">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M53">
+        <v>5.637208500000001</v>
+      </c>
+      <c r="N53">
+        <v>33.02945816666667</v>
+      </c>
+      <c r="O53">
+        <v>7.431628087500001</v>
+      </c>
+      <c r="P53">
+        <v>25.59783007916667</v>
+      </c>
+      <c r="Q53">
+        <v>33.59783007916667</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3136082699426731</v>
+      </c>
+      <c r="T53">
+        <v>1.765357026987382</v>
+      </c>
+      <c r="U53">
+        <v>0.0495</v>
+      </c>
+      <c r="V53">
+        <v>0.225</v>
+      </c>
+      <c r="W53">
+        <v>0.0383625</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>6.859186894837519</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1728863030568725</v>
+      </c>
+      <c r="C54">
+        <v>169.7372457100944</v>
+      </c>
+      <c r="D54">
+        <v>274.5532457100944</v>
+      </c>
+      <c r="E54">
+        <v>-74.78399999999999</v>
+      </c>
+      <c r="F54">
+        <v>116.116</v>
+      </c>
+      <c r="G54">
+        <v>11.3</v>
+      </c>
+      <c r="H54">
+        <v>32.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K54">
+        <v>8</v>
+      </c>
+      <c r="L54">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M54">
+        <v>5.747742000000001</v>
+      </c>
+      <c r="N54">
+        <v>32.91892466666667</v>
+      </c>
+      <c r="O54">
+        <v>7.406758050000001</v>
+      </c>
+      <c r="P54">
+        <v>25.51216661666667</v>
+      </c>
+      <c r="Q54">
+        <v>33.51216661666667</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.318620423035151</v>
+      </c>
+      <c r="T54">
+        <v>1.797554892371813</v>
+      </c>
+      <c r="U54">
+        <v>0.0495</v>
+      </c>
+      <c r="V54">
+        <v>0.225</v>
+      </c>
+      <c r="W54">
+        <v>0.0383625</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>6.727279454552182</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1725396788418351</v>
+      </c>
+      <c r="C55">
+        <v>168.2158281223176</v>
+      </c>
+      <c r="D55">
+        <v>275.2648281223176</v>
+      </c>
+      <c r="E55">
+        <v>-72.55099999999999</v>
+      </c>
+      <c r="F55">
+        <v>118.349</v>
+      </c>
+      <c r="G55">
+        <v>11.3</v>
+      </c>
+      <c r="H55">
+        <v>32.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K55">
+        <v>8</v>
+      </c>
+      <c r="L55">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M55">
+        <v>5.858275500000001</v>
+      </c>
+      <c r="N55">
+        <v>32.80839116666667</v>
+      </c>
+      <c r="O55">
+        <v>7.3818880125</v>
+      </c>
+      <c r="P55">
+        <v>25.42650315416667</v>
+      </c>
+      <c r="Q55">
+        <v>33.42650315416667</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3238458592379471</v>
+      </c>
+      <c r="T55">
+        <v>1.831122879687496</v>
+      </c>
+      <c r="U55">
+        <v>0.0495</v>
+      </c>
+      <c r="V55">
+        <v>0.225</v>
+      </c>
+      <c r="W55">
+        <v>0.0383625</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>6.600349653522894</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1721930546267978</v>
+      </c>
+      <c r="C56">
+        <v>166.6981086535433</v>
+      </c>
+      <c r="D56">
+        <v>275.9801086535433</v>
+      </c>
+      <c r="E56">
+        <v>-70.318</v>
+      </c>
+      <c r="F56">
+        <v>120.582</v>
+      </c>
+      <c r="G56">
+        <v>11.3</v>
+      </c>
+      <c r="H56">
+        <v>32.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K56">
+        <v>8</v>
+      </c>
+      <c r="L56">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M56">
+        <v>5.968809</v>
+      </c>
+      <c r="N56">
+        <v>32.69785766666667</v>
+      </c>
+      <c r="O56">
+        <v>7.357017975000002</v>
+      </c>
+      <c r="P56">
+        <v>25.34083969166667</v>
+      </c>
+      <c r="Q56">
+        <v>33.34083969166667</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3292984883191257</v>
+      </c>
+      <c r="T56">
+        <v>1.866150344712556</v>
+      </c>
+      <c r="U56">
+        <v>0.0495</v>
+      </c>
+      <c r="V56">
+        <v>0.225</v>
+      </c>
+      <c r="W56">
+        <v>0.0383625</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>6.478120956235434</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1718464304117605</v>
+      </c>
+      <c r="C57">
+        <v>165.1841162077625</v>
+      </c>
+      <c r="D57">
+        <v>276.6991162077625</v>
+      </c>
+      <c r="E57">
+        <v>-68.08499999999999</v>
+      </c>
+      <c r="F57">
+        <v>122.815</v>
+      </c>
+      <c r="G57">
+        <v>11.3</v>
+      </c>
+      <c r="H57">
+        <v>32.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K57">
+        <v>8</v>
+      </c>
+      <c r="L57">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M57">
+        <v>6.079342500000001</v>
+      </c>
+      <c r="N57">
+        <v>32.58732416666667</v>
+      </c>
+      <c r="O57">
+        <v>7.3321479375</v>
+      </c>
+      <c r="P57">
+        <v>25.25517622916667</v>
+      </c>
+      <c r="Q57">
+        <v>33.25517622916666</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3349934564705789</v>
+      </c>
+      <c r="T57">
+        <v>1.902734585960953</v>
+      </c>
+      <c r="U57">
+        <v>0.0495</v>
+      </c>
+      <c r="V57">
+        <v>0.225</v>
+      </c>
+      <c r="W57">
+        <v>0.0383625</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>6.360336938849335</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1714998061967231</v>
+      </c>
+      <c r="C58">
+        <v>163.6738799909655</v>
+      </c>
+      <c r="D58">
+        <v>277.4218799909655</v>
+      </c>
+      <c r="E58">
+        <v>-65.85199999999999</v>
+      </c>
+      <c r="F58">
+        <v>125.048</v>
+      </c>
+      <c r="G58">
+        <v>11.3</v>
+      </c>
+      <c r="H58">
+        <v>32.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K58">
+        <v>8</v>
+      </c>
+      <c r="L58">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M58">
+        <v>6.189876000000001</v>
+      </c>
+      <c r="N58">
+        <v>32.47679066666667</v>
+      </c>
+      <c r="O58">
+        <v>7.307277900000002</v>
+      </c>
+      <c r="P58">
+        <v>25.16951276666667</v>
+      </c>
+      <c r="Q58">
+        <v>33.16951276666667</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3409472868107344</v>
+      </c>
+      <c r="T58">
+        <v>1.940981747266094</v>
+      </c>
+      <c r="U58">
+        <v>0.0495</v>
+      </c>
+      <c r="V58">
+        <v>0.225</v>
+      </c>
+      <c r="W58">
+        <v>0.0383625</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>6.246759493512741</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1717716319816858</v>
+      </c>
+      <c r="C59">
+        <v>160.8737633874425</v>
+      </c>
+      <c r="D59">
+        <v>276.8547633874425</v>
+      </c>
+      <c r="E59">
+        <v>-63.61899999999999</v>
+      </c>
+      <c r="F59">
+        <v>127.281</v>
+      </c>
+      <c r="G59">
+        <v>11.3</v>
+      </c>
+      <c r="H59">
+        <v>32.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K59">
+        <v>8</v>
+      </c>
+      <c r="L59">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M59">
+        <v>6.478602900000001</v>
+      </c>
+      <c r="N59">
+        <v>32.18806376666667</v>
+      </c>
+      <c r="O59">
+        <v>7.242314347500002</v>
+      </c>
+      <c r="P59">
+        <v>24.94574941916667</v>
+      </c>
+      <c r="Q59">
+        <v>32.94574941916667</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3471780394922926</v>
+      </c>
+      <c r="T59">
+        <v>1.981007846306359</v>
+      </c>
+      <c r="U59">
+        <v>0.0509</v>
+      </c>
+      <c r="V59">
+        <v>0.225</v>
+      </c>
+      <c r="W59">
+        <v>0.0394475</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>5.968364979842593</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1714358577666485</v>
+      </c>
+      <c r="C60">
+        <v>159.3416348743921</v>
+      </c>
+      <c r="D60">
+        <v>277.5556348743921</v>
+      </c>
+      <c r="E60">
+        <v>-61.386</v>
+      </c>
+      <c r="F60">
+        <v>129.514</v>
+      </c>
+      <c r="G60">
+        <v>11.3</v>
+      </c>
+      <c r="H60">
+        <v>32.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K60">
+        <v>8</v>
+      </c>
+      <c r="L60">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M60">
+        <v>6.592262600000001</v>
+      </c>
+      <c r="N60">
+        <v>32.07440406666667</v>
+      </c>
+      <c r="O60">
+        <v>7.216740915000002</v>
+      </c>
+      <c r="P60">
+        <v>24.85766315166667</v>
+      </c>
+      <c r="Q60">
+        <v>32.85766315166667</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3537054946824964</v>
+      </c>
+      <c r="T60">
+        <v>2.022939950062826</v>
+      </c>
+      <c r="U60">
+        <v>0.0509</v>
+      </c>
+      <c r="V60">
+        <v>0.225</v>
+      </c>
+      <c r="W60">
+        <v>0.0394475</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>5.86546213536255</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1711000835516112</v>
+      </c>
+      <c r="C61">
+        <v>157.8130639490177</v>
+      </c>
+      <c r="D61">
+        <v>278.2600639490176</v>
+      </c>
+      <c r="E61">
+        <v>-59.15300000000002</v>
+      </c>
+      <c r="F61">
+        <v>131.747</v>
+      </c>
+      <c r="G61">
+        <v>11.3</v>
+      </c>
+      <c r="H61">
+        <v>32.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K61">
+        <v>8</v>
+      </c>
+      <c r="L61">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M61">
+        <v>6.705922299999999</v>
+      </c>
+      <c r="N61">
+        <v>31.96074436666667</v>
+      </c>
+      <c r="O61">
+        <v>7.191167482500002</v>
+      </c>
+      <c r="P61">
+        <v>24.76957688416667</v>
+      </c>
+      <c r="Q61">
+        <v>32.76957688416667</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3605513623210028</v>
+      </c>
+      <c r="T61">
+        <v>2.066917522295219</v>
+      </c>
+      <c r="U61">
+        <v>0.0509</v>
+      </c>
+      <c r="V61">
+        <v>0.225</v>
+      </c>
+      <c r="W61">
+        <v>0.0394475</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>5.766047522898778</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1707643093365738</v>
+      </c>
+      <c r="C62">
+        <v>156.288077767439</v>
+      </c>
+      <c r="D62">
+        <v>278.968077767439</v>
+      </c>
+      <c r="E62">
+        <v>-56.92000000000002</v>
+      </c>
+      <c r="F62">
+        <v>133.98</v>
+      </c>
+      <c r="G62">
+        <v>11.3</v>
+      </c>
+      <c r="H62">
+        <v>32.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K62">
+        <v>8</v>
+      </c>
+      <c r="L62">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M62">
+        <v>6.819582</v>
+      </c>
+      <c r="N62">
+        <v>31.84708466666667</v>
+      </c>
+      <c r="O62">
+        <v>7.165594050000001</v>
+      </c>
+      <c r="P62">
+        <v>24.68149061666667</v>
+      </c>
+      <c r="Q62">
+        <v>32.68149061666667</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3677395233414345</v>
+      </c>
+      <c r="T62">
+        <v>2.113093973139232</v>
+      </c>
+      <c r="U62">
+        <v>0.0509</v>
+      </c>
+      <c r="V62">
+        <v>0.225</v>
+      </c>
+      <c r="W62">
+        <v>0.0394475</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>5.669946730850465</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1704285351215365</v>
+      </c>
+      <c r="C63">
+        <v>154.7667037628688</v>
+      </c>
+      <c r="D63">
+        <v>279.6797037628688</v>
+      </c>
+      <c r="E63">
+        <v>-54.68700000000001</v>
+      </c>
+      <c r="F63">
+        <v>136.213</v>
+      </c>
+      <c r="G63">
+        <v>11.3</v>
+      </c>
+      <c r="H63">
+        <v>32.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K63">
+        <v>8</v>
+      </c>
+      <c r="L63">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M63">
+        <v>6.9332417</v>
+      </c>
+      <c r="N63">
+        <v>31.73342496666667</v>
+      </c>
+      <c r="O63">
+        <v>7.140020617500001</v>
+      </c>
+      <c r="P63">
+        <v>24.59340434916667</v>
+      </c>
+      <c r="Q63">
+        <v>32.59340434916667</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3752963080039398</v>
+      </c>
+      <c r="T63">
+        <v>2.16163844710345</v>
+      </c>
+      <c r="U63">
+        <v>0.0509</v>
+      </c>
+      <c r="V63">
+        <v>0.225</v>
+      </c>
+      <c r="W63">
+        <v>0.0394475</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.57699678444308</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1700927609064991</v>
+      </c>
+      <c r="C64">
+        <v>153.2489696491558</v>
+      </c>
+      <c r="D64">
+        <v>280.3949696491558</v>
+      </c>
+      <c r="E64">
+        <v>-52.45400000000001</v>
+      </c>
+      <c r="F64">
+        <v>138.446</v>
+      </c>
+      <c r="G64">
+        <v>11.3</v>
+      </c>
+      <c r="H64">
+        <v>32.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K64">
+        <v>8</v>
+      </c>
+      <c r="L64">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M64">
+        <v>7.0469014</v>
+      </c>
+      <c r="N64">
+        <v>31.61976526666667</v>
+      </c>
+      <c r="O64">
+        <v>7.114447185000001</v>
+      </c>
+      <c r="P64">
+        <v>24.50531808166667</v>
+      </c>
+      <c r="Q64">
+        <v>32.50531808166667</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3832508181749977</v>
+      </c>
+      <c r="T64">
+        <v>2.212737893381574</v>
+      </c>
+      <c r="U64">
+        <v>0.0509</v>
+      </c>
+      <c r="V64">
+        <v>0.225</v>
+      </c>
+      <c r="W64">
+        <v>0.0394475</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.487045223403675</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1697569866914618</v>
+      </c>
+      <c r="C65">
+        <v>151.7349034243822</v>
+      </c>
+      <c r="D65">
+        <v>281.1139034243822</v>
+      </c>
+      <c r="E65">
+        <v>-50.221</v>
+      </c>
+      <c r="F65">
+        <v>140.679</v>
+      </c>
+      <c r="G65">
+        <v>11.3</v>
+      </c>
+      <c r="H65">
+        <v>32.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K65">
+        <v>8</v>
+      </c>
+      <c r="L65">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M65">
+        <v>7.1605611</v>
+      </c>
+      <c r="N65">
+        <v>31.50610556666667</v>
+      </c>
+      <c r="O65">
+        <v>7.088873752500001</v>
+      </c>
+      <c r="P65">
+        <v>24.41723181416667</v>
+      </c>
+      <c r="Q65">
+        <v>32.41723181416667</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3916353018688157</v>
+      </c>
+      <c r="T65">
+        <v>2.266599471890949</v>
+      </c>
+      <c r="U65">
+        <v>0.0509</v>
+      </c>
+      <c r="V65">
+        <v>0.225</v>
+      </c>
+      <c r="W65">
+        <v>0.0394475</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.399949267476633</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1694212124764245</v>
+      </c>
+      <c r="C66">
+        <v>150.2245333745171</v>
+      </c>
+      <c r="D66">
+        <v>281.836533374517</v>
+      </c>
+      <c r="E66">
+        <v>-47.988</v>
+      </c>
+      <c r="F66">
+        <v>142.912</v>
+      </c>
+      <c r="G66">
+        <v>11.3</v>
+      </c>
+      <c r="H66">
+        <v>32.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K66">
+        <v>8</v>
+      </c>
+      <c r="L66">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M66">
+        <v>7.2742208</v>
+      </c>
+      <c r="N66">
+        <v>31.39244586666667</v>
+      </c>
+      <c r="O66">
+        <v>7.063300320000001</v>
+      </c>
+      <c r="P66">
+        <v>24.32914554666667</v>
+      </c>
+      <c r="Q66">
+        <v>32.32914554666667</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.4004855902122904</v>
+      </c>
+      <c r="T66">
+        <v>2.323453360317512</v>
+      </c>
+      <c r="U66">
+        <v>0.0509</v>
+      </c>
+      <c r="V66">
+        <v>0.225</v>
+      </c>
+      <c r="W66">
+        <v>0.0394475</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>5.31557506017231</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1690854382613872</v>
+      </c>
+      <c r="C67">
+        <v>148.7178880771263</v>
+      </c>
+      <c r="D67">
+        <v>282.5628880771263</v>
+      </c>
+      <c r="E67">
+        <v>-45.755</v>
+      </c>
+      <c r="F67">
+        <v>145.145</v>
+      </c>
+      <c r="G67">
+        <v>11.3</v>
+      </c>
+      <c r="H67">
+        <v>32.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K67">
+        <v>8</v>
+      </c>
+      <c r="L67">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M67">
+        <v>7.387880500000001</v>
+      </c>
+      <c r="N67">
+        <v>31.27878616666667</v>
+      </c>
+      <c r="O67">
+        <v>7.037726887500001</v>
+      </c>
+      <c r="P67">
+        <v>24.24105927916667</v>
+      </c>
+      <c r="Q67">
+        <v>32.24105927916667</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4098416093182491</v>
+      </c>
+      <c r="T67">
+        <v>2.383556042368448</v>
+      </c>
+      <c r="U67">
+        <v>0.0509</v>
+      </c>
+      <c r="V67">
+        <v>0.225</v>
+      </c>
+      <c r="W67">
+        <v>0.0394475</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>5.233796982323505</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1687496640463498</v>
+      </c>
+      <c r="C68">
+        <v>147.2149964051397</v>
+      </c>
+      <c r="D68">
+        <v>283.2929964051397</v>
+      </c>
+      <c r="E68">
+        <v>-43.52199999999999</v>
+      </c>
+      <c r="F68">
+        <v>147.378</v>
+      </c>
+      <c r="G68">
+        <v>11.3</v>
+      </c>
+      <c r="H68">
+        <v>32.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K68">
+        <v>8</v>
+      </c>
+      <c r="L68">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M68">
+        <v>7.501540200000001</v>
+      </c>
+      <c r="N68">
+        <v>31.16512646666667</v>
+      </c>
+      <c r="O68">
+        <v>7.012153455000001</v>
+      </c>
+      <c r="P68">
+        <v>24.15297301166667</v>
+      </c>
+      <c r="Q68">
+        <v>32.15297301166667</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4197479824892643</v>
+      </c>
+      <c r="T68">
+        <v>2.447194176304734</v>
+      </c>
+      <c r="U68">
+        <v>0.0509</v>
+      </c>
+      <c r="V68">
+        <v>0.225</v>
+      </c>
+      <c r="W68">
+        <v>0.0394475</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>5.154497028045876</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1684138898313126</v>
+      </c>
+      <c r="C69">
+        <v>145.7158875306764</v>
+      </c>
+      <c r="D69">
+        <v>284.0268875306764</v>
+      </c>
+      <c r="E69">
+        <v>-41.28899999999999</v>
+      </c>
+      <c r="F69">
+        <v>149.611</v>
+      </c>
+      <c r="G69">
+        <v>11.3</v>
+      </c>
+      <c r="H69">
+        <v>32.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K69">
+        <v>8</v>
+      </c>
+      <c r="L69">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M69">
+        <v>7.615199900000001</v>
+      </c>
+      <c r="N69">
+        <v>31.05146676666667</v>
+      </c>
+      <c r="O69">
+        <v>6.986580022500001</v>
+      </c>
+      <c r="P69">
+        <v>24.06488674416667</v>
+      </c>
+      <c r="Q69">
+        <v>32.06488674416667</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4302547419130683</v>
+      </c>
+      <c r="T69">
+        <v>2.51468916684322</v>
+      </c>
+      <c r="U69">
+        <v>0.0509</v>
+      </c>
+      <c r="V69">
+        <v>0.225</v>
+      </c>
+      <c r="W69">
+        <v>0.0394475</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>5.077564236582504</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1680781156162752</v>
+      </c>
+      <c r="C70">
+        <v>144.2205909289314</v>
+      </c>
+      <c r="D70">
+        <v>284.7645909289314</v>
+      </c>
+      <c r="E70">
+        <v>-39.05599999999998</v>
+      </c>
+      <c r="F70">
+        <v>151.844</v>
+      </c>
+      <c r="G70">
+        <v>11.3</v>
+      </c>
+      <c r="H70">
+        <v>32.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K70">
+        <v>8</v>
+      </c>
+      <c r="L70">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M70">
+        <v>7.728859600000002</v>
+      </c>
+      <c r="N70">
+        <v>30.93780706666667</v>
+      </c>
+      <c r="O70">
+        <v>6.961006590000001</v>
+      </c>
+      <c r="P70">
+        <v>23.97680047666667</v>
+      </c>
+      <c r="Q70">
+        <v>31.97680047666667</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.44141817380086</v>
+      </c>
+      <c r="T70">
+        <v>2.586402594290361</v>
+      </c>
+      <c r="U70">
+        <v>0.0509</v>
+      </c>
+      <c r="V70">
+        <v>0.225</v>
+      </c>
+      <c r="W70">
+        <v>0.0394475</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.00289417427982</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1677423414012378</v>
+      </c>
+      <c r="C71">
+        <v>142.7291363821201</v>
+      </c>
+      <c r="D71">
+        <v>285.5061363821201</v>
+      </c>
+      <c r="E71">
+        <v>-36.82299999999998</v>
+      </c>
+      <c r="F71">
+        <v>154.077</v>
+      </c>
+      <c r="G71">
+        <v>11.3</v>
+      </c>
+      <c r="H71">
+        <v>32.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K71">
+        <v>8</v>
+      </c>
+      <c r="L71">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M71">
+        <v>7.842519300000001</v>
+      </c>
+      <c r="N71">
+        <v>30.82414736666667</v>
+      </c>
+      <c r="O71">
+        <v>6.935433157500001</v>
+      </c>
+      <c r="P71">
+        <v>23.88871420916667</v>
+      </c>
+      <c r="Q71">
+        <v>31.88871420916667</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4533018271007673</v>
+      </c>
+      <c r="T71">
+        <v>2.662742694476027</v>
+      </c>
+      <c r="U71">
+        <v>0.0509</v>
+      </c>
+      <c r="V71">
+        <v>0.225</v>
+      </c>
+      <c r="W71">
+        <v>0.0394475</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>4.930388461609099</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1674065671862005</v>
+      </c>
+      <c r="C72">
+        <v>141.2415539834876</v>
+      </c>
+      <c r="D72">
+        <v>286.2515539834876</v>
+      </c>
+      <c r="E72">
+        <v>-34.58999999999997</v>
+      </c>
+      <c r="F72">
+        <v>156.31</v>
+      </c>
+      <c r="G72">
+        <v>11.3</v>
+      </c>
+      <c r="H72">
+        <v>32.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K72">
+        <v>8</v>
+      </c>
+      <c r="L72">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M72">
+        <v>7.956179000000001</v>
+      </c>
+      <c r="N72">
+        <v>30.71048766666667</v>
+      </c>
+      <c r="O72">
+        <v>6.909859725</v>
+      </c>
+      <c r="P72">
+        <v>23.80062794166667</v>
+      </c>
+      <c r="Q72">
+        <v>31.80062794166667</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4659777239540018</v>
+      </c>
+      <c r="T72">
+        <v>2.74417213467407</v>
+      </c>
+      <c r="U72">
+        <v>0.0509</v>
+      </c>
+      <c r="V72">
+        <v>0.225</v>
+      </c>
+      <c r="W72">
+        <v>0.0394475</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>4.859954340728969</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1670707929711632</v>
+      </c>
+      <c r="C73">
+        <v>139.7578741413791</v>
+      </c>
+      <c r="D73">
+        <v>287.0008741413791</v>
+      </c>
+      <c r="E73">
+        <v>-32.357</v>
+      </c>
+      <c r="F73">
+        <v>158.543</v>
+      </c>
+      <c r="G73">
+        <v>11.3</v>
+      </c>
+      <c r="H73">
+        <v>32.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K73">
+        <v>8</v>
+      </c>
+      <c r="L73">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M73">
+        <v>8.0698387</v>
+      </c>
+      <c r="N73">
+        <v>30.59682796666667</v>
+      </c>
+      <c r="O73">
+        <v>6.884286292500001</v>
+      </c>
+      <c r="P73">
+        <v>23.71254167416667</v>
+      </c>
+      <c r="Q73">
+        <v>31.71254167416667</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4795278205902179</v>
+      </c>
+      <c r="T73">
+        <v>2.831217398334047</v>
+      </c>
+      <c r="U73">
+        <v>0.0509</v>
+      </c>
+      <c r="V73">
+        <v>0.225</v>
+      </c>
+      <c r="W73">
+        <v>0.0394475</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>4.791504279591942</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1667350187561258</v>
+      </c>
+      <c r="C74">
+        <v>138.2781275833749</v>
+      </c>
+      <c r="D74">
+        <v>287.7541275833749</v>
+      </c>
+      <c r="E74">
+        <v>-30.124</v>
+      </c>
+      <c r="F74">
+        <v>160.776</v>
+      </c>
+      <c r="G74">
+        <v>11.3</v>
+      </c>
+      <c r="H74">
+        <v>32.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K74">
+        <v>8</v>
+      </c>
+      <c r="L74">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M74">
+        <v>8.183498400000001</v>
+      </c>
+      <c r="N74">
+        <v>30.48316826666667</v>
+      </c>
+      <c r="O74">
+        <v>6.858712860000001</v>
+      </c>
+      <c r="P74">
+        <v>23.62445540666667</v>
+      </c>
+      <c r="Q74">
+        <v>31.62445540666667</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.494045781271878</v>
+      </c>
+      <c r="T74">
+        <v>2.924480180826881</v>
+      </c>
+      <c r="U74">
+        <v>0.0509</v>
+      </c>
+      <c r="V74">
+        <v>0.225</v>
+      </c>
+      <c r="W74">
+        <v>0.0394475</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>4.724955609042053</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1663992445410885</v>
+      </c>
+      <c r="C75">
+        <v>136.8023453604907</v>
+      </c>
+      <c r="D75">
+        <v>288.5113453604907</v>
+      </c>
+      <c r="E75">
+        <v>-27.89099999999999</v>
+      </c>
+      <c r="F75">
+        <v>163.009</v>
+      </c>
+      <c r="G75">
+        <v>11.3</v>
+      </c>
+      <c r="H75">
+        <v>32.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K75">
+        <v>8</v>
+      </c>
+      <c r="L75">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M75">
+        <v>8.297158100000001</v>
+      </c>
+      <c r="N75">
+        <v>30.36950856666667</v>
+      </c>
+      <c r="O75">
+        <v>6.833139427500001</v>
+      </c>
+      <c r="P75">
+        <v>23.53636913916667</v>
+      </c>
+      <c r="Q75">
+        <v>31.53636913916667</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.509639146448476</v>
+      </c>
+      <c r="T75">
+        <v>3.024651317578442</v>
+      </c>
+      <c r="U75">
+        <v>0.0509</v>
+      </c>
+      <c r="V75">
+        <v>0.225</v>
+      </c>
+      <c r="W75">
+        <v>0.0394475</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.660230189740107</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1660634703260512</v>
+      </c>
+      <c r="C76">
+        <v>135.3305588514445</v>
+      </c>
+      <c r="D76">
+        <v>289.2725588514445</v>
+      </c>
+      <c r="E76">
+        <v>-25.65799999999999</v>
+      </c>
+      <c r="F76">
+        <v>165.242</v>
+      </c>
+      <c r="G76">
+        <v>11.3</v>
+      </c>
+      <c r="H76">
+        <v>32.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K76">
+        <v>8</v>
+      </c>
+      <c r="L76">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M76">
+        <v>8.4108178</v>
+      </c>
+      <c r="N76">
+        <v>30.25584886666667</v>
+      </c>
+      <c r="O76">
+        <v>6.807565995000001</v>
+      </c>
+      <c r="P76">
+        <v>23.44828287166667</v>
+      </c>
+      <c r="Q76">
+        <v>31.44828287166667</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.526432001254043</v>
+      </c>
+      <c r="T76">
+        <v>3.132527926387816</v>
+      </c>
+      <c r="U76">
+        <v>0.0509</v>
+      </c>
+      <c r="V76">
+        <v>0.225</v>
+      </c>
+      <c r="W76">
+        <v>0.0394475</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.597254106094971</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1657276961110138</v>
+      </c>
+      <c r="C77">
+        <v>133.8627997669909</v>
+      </c>
+      <c r="D77">
+        <v>290.0377997669909</v>
+      </c>
+      <c r="E77">
+        <v>-23.42499999999998</v>
+      </c>
+      <c r="F77">
+        <v>167.475</v>
+      </c>
+      <c r="G77">
+        <v>11.3</v>
+      </c>
+      <c r="H77">
+        <v>32.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K77">
+        <v>8</v>
+      </c>
+      <c r="L77">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M77">
+        <v>8.524477500000001</v>
+      </c>
+      <c r="N77">
+        <v>30.14218916666667</v>
+      </c>
+      <c r="O77">
+        <v>6.7819925625</v>
+      </c>
+      <c r="P77">
+        <v>23.36019660416667</v>
+      </c>
+      <c r="Q77">
+        <v>31.36019660416667</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5445682844440554</v>
+      </c>
+      <c r="T77">
+        <v>3.24903466390194</v>
+      </c>
+      <c r="U77">
+        <v>0.0509</v>
+      </c>
+      <c r="V77">
+        <v>0.225</v>
+      </c>
+      <c r="W77">
+        <v>0.0394475</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.535957384680371</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1669233218959766</v>
+      </c>
+      <c r="C78">
+        <v>128.9232146825297</v>
+      </c>
+      <c r="D78">
+        <v>287.3312146825297</v>
+      </c>
+      <c r="E78">
+        <v>-21.19200000000001</v>
+      </c>
+      <c r="F78">
+        <v>169.708</v>
+      </c>
+      <c r="G78">
+        <v>11.3</v>
+      </c>
+      <c r="H78">
+        <v>32.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K78">
+        <v>8</v>
+      </c>
+      <c r="L78">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M78">
+        <v>9.079378</v>
+      </c>
+      <c r="N78">
+        <v>29.58728866666667</v>
+      </c>
+      <c r="O78">
+        <v>6.657139950000001</v>
+      </c>
+      <c r="P78">
+        <v>22.93014871666667</v>
+      </c>
+      <c r="Q78">
+        <v>30.93014871666667</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.564215924566569</v>
+      </c>
+      <c r="T78">
+        <v>3.375250296208908</v>
+      </c>
+      <c r="U78">
+        <v>0.0535</v>
+      </c>
+      <c r="V78">
+        <v>0.225</v>
+      </c>
+      <c r="W78">
+        <v>0.0414625</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>4.258735198233477</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1666076976809392</v>
+      </c>
+      <c r="C79">
+        <v>127.3997860990832</v>
+      </c>
+      <c r="D79">
+        <v>288.0407860990832</v>
+      </c>
+      <c r="E79">
+        <v>-18.959</v>
+      </c>
+      <c r="F79">
+        <v>171.941</v>
+      </c>
+      <c r="G79">
+        <v>11.3</v>
+      </c>
+      <c r="H79">
+        <v>32.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K79">
+        <v>8</v>
+      </c>
+      <c r="L79">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M79">
+        <v>9.198843500000001</v>
+      </c>
+      <c r="N79">
+        <v>29.46782316666667</v>
+      </c>
+      <c r="O79">
+        <v>6.630260212500001</v>
+      </c>
+      <c r="P79">
+        <v>22.83756295416667</v>
+      </c>
+      <c r="Q79">
+        <v>30.83756295416667</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5855720551345183</v>
+      </c>
+      <c r="T79">
+        <v>3.512441200890394</v>
+      </c>
+      <c r="U79">
+        <v>0.0535</v>
+      </c>
+      <c r="V79">
+        <v>0.225</v>
+      </c>
+      <c r="W79">
+        <v>0.0414625</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>4.203426948905769</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1662920734659019</v>
+      </c>
+      <c r="C80">
+        <v>125.8798707994867</v>
+      </c>
+      <c r="D80">
+        <v>288.7538707994867</v>
+      </c>
+      <c r="E80">
+        <v>-16.726</v>
+      </c>
+      <c r="F80">
+        <v>174.174</v>
+      </c>
+      <c r="G80">
+        <v>11.3</v>
+      </c>
+      <c r="H80">
+        <v>32.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K80">
+        <v>8</v>
+      </c>
+      <c r="L80">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M80">
+        <v>9.318308999999999</v>
+      </c>
+      <c r="N80">
+        <v>29.34835766666667</v>
+      </c>
+      <c r="O80">
+        <v>6.603380475000002</v>
+      </c>
+      <c r="P80">
+        <v>22.74497719166667</v>
+      </c>
+      <c r="Q80">
+        <v>30.74497719166667</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6088696521177359</v>
+      </c>
+      <c r="T80">
+        <v>3.662104005997471</v>
+      </c>
+      <c r="U80">
+        <v>0.0535</v>
+      </c>
+      <c r="V80">
+        <v>0.225</v>
+      </c>
+      <c r="W80">
+        <v>0.0414625</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>4.149536859817235</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1659764492508645</v>
+      </c>
+      <c r="C81">
+        <v>124.3634949413536</v>
+      </c>
+      <c r="D81">
+        <v>289.4704949413536</v>
+      </c>
+      <c r="E81">
+        <v>-14.49299999999999</v>
+      </c>
+      <c r="F81">
+        <v>176.407</v>
+      </c>
+      <c r="G81">
+        <v>11.3</v>
+      </c>
+      <c r="H81">
+        <v>32.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K81">
+        <v>8</v>
+      </c>
+      <c r="L81">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M81">
+        <v>9.4377745</v>
+      </c>
+      <c r="N81">
+        <v>29.22889216666667</v>
+      </c>
+      <c r="O81">
+        <v>6.576500737500001</v>
+      </c>
+      <c r="P81">
+        <v>22.65239142916667</v>
+      </c>
+      <c r="Q81">
+        <v>30.65239142916667</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6343860678612598</v>
+      </c>
+      <c r="T81">
+        <v>3.826020411590935</v>
+      </c>
+      <c r="U81">
+        <v>0.0535</v>
+      </c>
+      <c r="V81">
+        <v>0.225</v>
+      </c>
+      <c r="W81">
+        <v>0.0414625</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>4.097011076781573</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1656608250358272</v>
+      </c>
+      <c r="C82">
+        <v>122.850684942613</v>
+      </c>
+      <c r="D82">
+        <v>290.190684942613</v>
+      </c>
+      <c r="E82">
+        <v>-12.25999999999999</v>
+      </c>
+      <c r="F82">
+        <v>178.64</v>
+      </c>
+      <c r="G82">
+        <v>11.3</v>
+      </c>
+      <c r="H82">
+        <v>32.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K82">
+        <v>8</v>
+      </c>
+      <c r="L82">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M82">
+        <v>9.55724</v>
+      </c>
+      <c r="N82">
+        <v>29.10942666666667</v>
+      </c>
+      <c r="O82">
+        <v>6.549621000000001</v>
+      </c>
+      <c r="P82">
+        <v>22.55980566666667</v>
+      </c>
+      <c r="Q82">
+        <v>30.55980566666667</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6624541251791363</v>
+      </c>
+      <c r="T82">
+        <v>4.006328457743747</v>
+      </c>
+      <c r="U82">
+        <v>0.0535</v>
+      </c>
+      <c r="V82">
+        <v>0.225</v>
+      </c>
+      <c r="W82">
+        <v>0.0414625</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>4.045798438321803</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1670401258207899</v>
+      </c>
+      <c r="C83">
+        <v>117.496507097782</v>
+      </c>
+      <c r="D83">
+        <v>287.069507097782</v>
+      </c>
+      <c r="E83">
+        <v>-10.02699999999999</v>
+      </c>
+      <c r="F83">
+        <v>180.873</v>
+      </c>
+      <c r="G83">
+        <v>11.3</v>
+      </c>
+      <c r="H83">
+        <v>32.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K83">
+        <v>8</v>
+      </c>
+      <c r="L83">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M83">
+        <v>10.1650626</v>
+      </c>
+      <c r="N83">
+        <v>28.50160406666667</v>
+      </c>
+      <c r="O83">
+        <v>6.412860915000001</v>
+      </c>
+      <c r="P83">
+        <v>22.08874315166667</v>
+      </c>
+      <c r="Q83">
+        <v>30.08874315166667</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6934767148462626</v>
+      </c>
+      <c r="T83">
+        <v>4.205616298228432</v>
+      </c>
+      <c r="U83">
+        <v>0.0562</v>
+      </c>
+      <c r="V83">
+        <v>0.225</v>
+      </c>
+      <c r="W83">
+        <v>0.043555</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>3.803878853305505</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1667454266057525</v>
+      </c>
+      <c r="C84">
+        <v>115.9247199339669</v>
+      </c>
+      <c r="D84">
+        <v>287.7307199339669</v>
+      </c>
+      <c r="E84">
+        <v>-7.793999999999983</v>
+      </c>
+      <c r="F84">
+        <v>183.106</v>
+      </c>
+      <c r="G84">
+        <v>11.3</v>
+      </c>
+      <c r="H84">
+        <v>32.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K84">
+        <v>8</v>
+      </c>
+      <c r="L84">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M84">
+        <v>10.2905572</v>
+      </c>
+      <c r="N84">
+        <v>28.37610946666667</v>
+      </c>
+      <c r="O84">
+        <v>6.384624630000001</v>
+      </c>
+      <c r="P84">
+        <v>21.99148483666667</v>
+      </c>
+      <c r="Q84">
+        <v>29.99148483666667</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7279462589208476</v>
+      </c>
+      <c r="T84">
+        <v>4.427047232100305</v>
+      </c>
+      <c r="U84">
+        <v>0.0562</v>
+      </c>
+      <c r="V84">
+        <v>0.225</v>
+      </c>
+      <c r="W84">
+        <v>0.043555</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>3.757490086801778</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1664507273907152</v>
+      </c>
+      <c r="C85">
+        <v>114.3559857712239</v>
+      </c>
+      <c r="D85">
+        <v>288.394985771224</v>
+      </c>
+      <c r="E85">
+        <v>-5.560999999999979</v>
+      </c>
+      <c r="F85">
+        <v>185.339</v>
+      </c>
+      <c r="G85">
+        <v>11.3</v>
+      </c>
+      <c r="H85">
+        <v>32.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K85">
+        <v>8</v>
+      </c>
+      <c r="L85">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M85">
+        <v>10.4160518</v>
+      </c>
+      <c r="N85">
+        <v>28.25061486666667</v>
+      </c>
+      <c r="O85">
+        <v>6.356388345000001</v>
+      </c>
+      <c r="P85">
+        <v>21.89422652166667</v>
+      </c>
+      <c r="Q85">
+        <v>29.89422652166667</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7664710434747957</v>
+      </c>
+      <c r="T85">
+        <v>4.674528864074752</v>
+      </c>
+      <c r="U85">
+        <v>0.0562</v>
+      </c>
+      <c r="V85">
+        <v>0.225</v>
+      </c>
+      <c r="W85">
+        <v>0.043555</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>3.712219121900552</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1661560281756779</v>
+      </c>
+      <c r="C86">
+        <v>112.7903258032971</v>
+      </c>
+      <c r="D86">
+        <v>289.0623258032971</v>
+      </c>
+      <c r="E86">
+        <v>-3.328000000000003</v>
+      </c>
+      <c r="F86">
+        <v>187.572</v>
+      </c>
+      <c r="G86">
+        <v>11.3</v>
+      </c>
+      <c r="H86">
+        <v>32.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K86">
+        <v>8</v>
+      </c>
+      <c r="L86">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M86">
+        <v>10.5415464</v>
+      </c>
+      <c r="N86">
+        <v>28.12512026666667</v>
+      </c>
+      <c r="O86">
+        <v>6.328152060000001</v>
+      </c>
+      <c r="P86">
+        <v>21.79696820666667</v>
+      </c>
+      <c r="Q86">
+        <v>29.79696820666667</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.8098114260979867</v>
+      </c>
+      <c r="T86">
+        <v>4.952945700046002</v>
+      </c>
+      <c r="U86">
+        <v>0.0562</v>
+      </c>
+      <c r="V86">
+        <v>0.225</v>
+      </c>
+      <c r="W86">
+        <v>0.043555</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>3.668026037116022</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1658613289606406</v>
+      </c>
+      <c r="C87">
+        <v>111.2277614205532</v>
+      </c>
+      <c r="D87">
+        <v>289.7327614205532</v>
+      </c>
+      <c r="E87">
+        <v>-1.094999999999999</v>
+      </c>
+      <c r="F87">
+        <v>189.805</v>
+      </c>
+      <c r="G87">
+        <v>11.3</v>
+      </c>
+      <c r="H87">
+        <v>32.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K87">
+        <v>8</v>
+      </c>
+      <c r="L87">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M87">
+        <v>10.667041</v>
+      </c>
+      <c r="N87">
+        <v>27.99962566666667</v>
+      </c>
+      <c r="O87">
+        <v>6.299915775000001</v>
+      </c>
+      <c r="P87">
+        <v>21.69970989166667</v>
+      </c>
+      <c r="Q87">
+        <v>29.69970989166667</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8589305264042704</v>
+      </c>
+      <c r="T87">
+        <v>5.268484780813422</v>
+      </c>
+      <c r="U87">
+        <v>0.0562</v>
+      </c>
+      <c r="V87">
+        <v>0.225</v>
+      </c>
+      <c r="W87">
+        <v>0.043555</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>3.624872789620539</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1655666297456032</v>
+      </c>
+      <c r="C88">
+        <v>109.6683142122665</v>
+      </c>
+      <c r="D88">
+        <v>290.4063142122665</v>
+      </c>
+      <c r="E88">
+        <v>1.138000000000005</v>
+      </c>
+      <c r="F88">
+        <v>192.038</v>
+      </c>
+      <c r="G88">
+        <v>11.3</v>
+      </c>
+      <c r="H88">
+        <v>32.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K88">
+        <v>8</v>
+      </c>
+      <c r="L88">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M88">
+        <v>10.7925356</v>
+      </c>
+      <c r="N88">
+        <v>27.87413106666667</v>
+      </c>
+      <c r="O88">
+        <v>6.271679490000001</v>
+      </c>
+      <c r="P88">
+        <v>21.60245157666667</v>
+      </c>
+      <c r="Q88">
+        <v>29.60245157666667</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.915066641040023</v>
+      </c>
+      <c r="T88">
+        <v>5.629100873119043</v>
+      </c>
+      <c r="U88">
+        <v>0.0562</v>
+      </c>
+      <c r="V88">
+        <v>0.225</v>
+      </c>
+      <c r="W88">
+        <v>0.043555</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>3.582723106020301</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1652719305305659</v>
+      </c>
+      <c r="C89">
+        <v>108.112005968937</v>
+      </c>
+      <c r="D89">
+        <v>291.083005968937</v>
+      </c>
+      <c r="E89">
+        <v>3.371000000000009</v>
+      </c>
+      <c r="F89">
+        <v>194.271</v>
+      </c>
+      <c r="G89">
+        <v>11.3</v>
+      </c>
+      <c r="H89">
+        <v>32.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K89">
+        <v>8</v>
+      </c>
+      <c r="L89">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M89">
+        <v>10.9180302</v>
+      </c>
+      <c r="N89">
+        <v>27.74863646666667</v>
+      </c>
+      <c r="O89">
+        <v>6.243443205000001</v>
+      </c>
+      <c r="P89">
+        <v>21.50519326166667</v>
+      </c>
+      <c r="Q89">
+        <v>29.50519326166667</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.9798390810043531</v>
+      </c>
+      <c r="T89">
+        <v>6.045196364240915</v>
+      </c>
+      <c r="U89">
+        <v>0.0562</v>
+      </c>
+      <c r="V89">
+        <v>0.225</v>
+      </c>
+      <c r="W89">
+        <v>0.043555</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>3.541542380663746</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1649772313155286</v>
+      </c>
+      <c r="C90">
+        <v>106.55885868464</v>
+      </c>
+      <c r="D90">
+        <v>291.76285868464</v>
+      </c>
+      <c r="E90">
+        <v>5.604000000000013</v>
+      </c>
+      <c r="F90">
+        <v>196.504</v>
+      </c>
+      <c r="G90">
+        <v>11.3</v>
+      </c>
+      <c r="H90">
+        <v>32.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K90">
+        <v>8</v>
+      </c>
+      <c r="L90">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M90">
+        <v>11.0435248</v>
+      </c>
+      <c r="N90">
+        <v>27.62314186666667</v>
+      </c>
+      <c r="O90">
+        <v>6.215206920000001</v>
+      </c>
+      <c r="P90">
+        <v>21.40793494666667</v>
+      </c>
+      <c r="Q90">
+        <v>29.40793494666667</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.055406927629405</v>
+      </c>
+      <c r="T90">
+        <v>6.530641103883098</v>
+      </c>
+      <c r="U90">
+        <v>0.0562</v>
+      </c>
+      <c r="V90">
+        <v>0.225</v>
+      </c>
+      <c r="W90">
+        <v>0.043555</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>3.501297580883475</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1679243571004912</v>
+      </c>
+      <c r="C91">
+        <v>97.66668249796032</v>
+      </c>
+      <c r="D91">
+        <v>285.1036824979603</v>
+      </c>
+      <c r="E91">
+        <v>7.837000000000018</v>
+      </c>
+      <c r="F91">
+        <v>198.737</v>
+      </c>
+      <c r="G91">
+        <v>11.3</v>
+      </c>
+      <c r="H91">
+        <v>32.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K91">
+        <v>8</v>
+      </c>
+      <c r="L91">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M91">
+        <v>12.1030833</v>
+      </c>
+      <c r="N91">
+        <v>26.56358336666667</v>
+      </c>
+      <c r="O91">
+        <v>5.976806257500001</v>
+      </c>
+      <c r="P91">
+        <v>20.58677710916667</v>
+      </c>
+      <c r="Q91">
+        <v>28.58677710916667</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.144714382731739</v>
+      </c>
+      <c r="T91">
+        <v>7.104348523460223</v>
+      </c>
+      <c r="U91">
+        <v>0.0609</v>
+      </c>
+      <c r="V91">
+        <v>0.225</v>
+      </c>
+      <c r="W91">
+        <v>0.0471975</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>3.194778198929414</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1676660828854539</v>
+      </c>
+      <c r="C92">
+        <v>96.0050890942706</v>
+      </c>
+      <c r="D92">
+        <v>285.6750890942706</v>
+      </c>
+      <c r="E92">
+        <v>10.07000000000002</v>
+      </c>
+      <c r="F92">
+        <v>200.97</v>
+      </c>
+      <c r="G92">
+        <v>11.3</v>
+      </c>
+      <c r="H92">
+        <v>32.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K92">
+        <v>8</v>
+      </c>
+      <c r="L92">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M92">
+        <v>12.239073</v>
+      </c>
+      <c r="N92">
+        <v>26.42759366666667</v>
+      </c>
+      <c r="O92">
+        <v>5.946208575</v>
+      </c>
+      <c r="P92">
+        <v>20.48138509166667</v>
+      </c>
+      <c r="Q92">
+        <v>28.48138509166667</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.251883328854539</v>
+      </c>
+      <c r="T92">
+        <v>7.792797426952775</v>
+      </c>
+      <c r="U92">
+        <v>0.0609</v>
+      </c>
+      <c r="V92">
+        <v>0.225</v>
+      </c>
+      <c r="W92">
+        <v>0.0471975</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>3.159280663385753</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1674078086704166</v>
+      </c>
+      <c r="C93">
+        <v>94.34579072369979</v>
+      </c>
+      <c r="D93">
+        <v>286.2487907236998</v>
+      </c>
+      <c r="E93">
+        <v>12.30300000000003</v>
+      </c>
+      <c r="F93">
+        <v>203.203</v>
+      </c>
+      <c r="G93">
+        <v>11.3</v>
+      </c>
+      <c r="H93">
+        <v>32.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K93">
+        <v>8</v>
+      </c>
+      <c r="L93">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M93">
+        <v>12.3750627</v>
+      </c>
+      <c r="N93">
+        <v>26.29160396666667</v>
+      </c>
+      <c r="O93">
+        <v>5.915610892500001</v>
+      </c>
+      <c r="P93">
+        <v>20.37599307416667</v>
+      </c>
+      <c r="Q93">
+        <v>28.37599307416667</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.382867596337962</v>
+      </c>
+      <c r="T93">
+        <v>8.634234975665894</v>
+      </c>
+      <c r="U93">
+        <v>0.0609</v>
+      </c>
+      <c r="V93">
+        <v>0.225</v>
+      </c>
+      <c r="W93">
+        <v>0.0471975</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>3.124563293458438</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1671495344553792</v>
+      </c>
+      <c r="C94">
+        <v>92.68880124094292</v>
+      </c>
+      <c r="D94">
+        <v>286.8248012409429</v>
+      </c>
+      <c r="E94">
+        <v>14.536</v>
+      </c>
+      <c r="F94">
+        <v>205.436</v>
+      </c>
+      <c r="G94">
+        <v>11.3</v>
+      </c>
+      <c r="H94">
+        <v>32.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K94">
+        <v>8</v>
+      </c>
+      <c r="L94">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M94">
+        <v>12.5110524</v>
+      </c>
+      <c r="N94">
+        <v>26.15561426666667</v>
+      </c>
+      <c r="O94">
+        <v>5.885013210000001</v>
+      </c>
+      <c r="P94">
+        <v>20.27060105666667</v>
+      </c>
+      <c r="Q94">
+        <v>28.27060105666667</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.546597930692241</v>
+      </c>
+      <c r="T94">
+        <v>9.686031911557292</v>
+      </c>
+      <c r="U94">
+        <v>0.0609</v>
+      </c>
+      <c r="V94">
+        <v>0.225</v>
+      </c>
+      <c r="W94">
+        <v>0.0471975</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>3.090600648964325</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1668912602403419</v>
+      </c>
+      <c r="C95">
+        <v>91.03413461243716</v>
+      </c>
+      <c r="D95">
+        <v>287.4031346124372</v>
+      </c>
+      <c r="E95">
+        <v>16.76900000000001</v>
+      </c>
+      <c r="F95">
+        <v>207.669</v>
+      </c>
+      <c r="G95">
+        <v>11.3</v>
+      </c>
+      <c r="H95">
+        <v>32.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K95">
+        <v>8</v>
+      </c>
+      <c r="L95">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M95">
+        <v>12.6470421</v>
+      </c>
+      <c r="N95">
+        <v>26.01962456666667</v>
+      </c>
+      <c r="O95">
+        <v>5.854415527500001</v>
+      </c>
+      <c r="P95">
+        <v>20.16520903916667</v>
+      </c>
+      <c r="Q95">
+        <v>28.16520903916667</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.757108360576314</v>
+      </c>
+      <c r="T95">
+        <v>11.03834225770338</v>
+      </c>
+      <c r="U95">
+        <v>0.0609</v>
+      </c>
+      <c r="V95">
+        <v>0.225</v>
+      </c>
+      <c r="W95">
+        <v>0.0471975</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>3.057368383921697</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1666329860253046</v>
+      </c>
+      <c r="C96">
+        <v>89.38180491749128</v>
+      </c>
+      <c r="D96">
+        <v>287.9838049174913</v>
+      </c>
+      <c r="E96">
+        <v>19.00200000000001</v>
+      </c>
+      <c r="F96">
+        <v>209.902</v>
+      </c>
+      <c r="G96">
+        <v>11.3</v>
+      </c>
+      <c r="H96">
+        <v>32.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K96">
+        <v>8</v>
+      </c>
+      <c r="L96">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M96">
+        <v>12.7830318</v>
+      </c>
+      <c r="N96">
+        <v>25.88363486666667</v>
+      </c>
+      <c r="O96">
+        <v>5.823817845000001</v>
+      </c>
+      <c r="P96">
+        <v>20.05981702166667</v>
+      </c>
+      <c r="Q96">
+        <v>28.05981702166667</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.037788933755078</v>
+      </c>
+      <c r="T96">
+        <v>12.84142271923149</v>
+      </c>
+      <c r="U96">
+        <v>0.0609</v>
+      </c>
+      <c r="V96">
+        <v>0.225</v>
+      </c>
+      <c r="W96">
+        <v>0.0471975</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>3.024843188348062</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1732218368102673</v>
+      </c>
+      <c r="C97">
+        <v>73.0329263957195</v>
+      </c>
+      <c r="D97">
+        <v>273.8679263957195</v>
+      </c>
+      <c r="E97">
+        <v>21.23500000000001</v>
+      </c>
+      <c r="F97">
+        <v>212.135</v>
+      </c>
+      <c r="G97">
+        <v>11.3</v>
+      </c>
+      <c r="H97">
+        <v>32.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K97">
+        <v>8</v>
+      </c>
+      <c r="L97">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M97">
+        <v>14.891877</v>
+      </c>
+      <c r="N97">
+        <v>23.77478966666667</v>
+      </c>
+      <c r="O97">
+        <v>5.349327675000001</v>
+      </c>
+      <c r="P97">
+        <v>18.42546199166667</v>
+      </c>
+      <c r="Q97">
+        <v>26.42546199166667</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.430741736205349</v>
+      </c>
+      <c r="T97">
+        <v>15.36573536537085</v>
+      </c>
+      <c r="U97">
+        <v>0.0702</v>
+      </c>
+      <c r="V97">
+        <v>0.225</v>
+      </c>
+      <c r="W97">
+        <v>0.054405</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>2.596493824564</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1730356375952299</v>
+      </c>
+      <c r="C98">
+        <v>71.17981055936133</v>
+      </c>
+      <c r="D98">
+        <v>274.2478105593613</v>
+      </c>
+      <c r="E98">
+        <v>23.46799999999999</v>
+      </c>
+      <c r="F98">
+        <v>214.368</v>
+      </c>
+      <c r="G98">
+        <v>11.3</v>
+      </c>
+      <c r="H98">
+        <v>32.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K98">
+        <v>8</v>
+      </c>
+      <c r="L98">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M98">
+        <v>15.0486336</v>
+      </c>
+      <c r="N98">
+        <v>23.61803306666667</v>
+      </c>
+      <c r="O98">
+        <v>5.314057440000002</v>
+      </c>
+      <c r="P98">
+        <v>18.30397562666667</v>
+      </c>
+      <c r="Q98">
+        <v>26.30397562666667</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.020170939880746</v>
+      </c>
+      <c r="T98">
+        <v>19.15220433457984</v>
+      </c>
+      <c r="U98">
+        <v>0.0702</v>
+      </c>
+      <c r="V98">
+        <v>0.225</v>
+      </c>
+      <c r="W98">
+        <v>0.054405</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>2.569447013891459</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1728494383801926</v>
+      </c>
+      <c r="C99">
+        <v>69.32775006697074</v>
+      </c>
+      <c r="D99">
+        <v>274.6287500669707</v>
+      </c>
+      <c r="E99">
+        <v>25.70099999999999</v>
+      </c>
+      <c r="F99">
+        <v>216.601</v>
+      </c>
+      <c r="G99">
+        <v>11.3</v>
+      </c>
+      <c r="H99">
+        <v>32.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K99">
+        <v>8</v>
+      </c>
+      <c r="L99">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M99">
+        <v>15.2053902</v>
+      </c>
+      <c r="N99">
+        <v>23.46127646666667</v>
+      </c>
+      <c r="O99">
+        <v>5.278787205000001</v>
+      </c>
+      <c r="P99">
+        <v>18.18248926166667</v>
+      </c>
+      <c r="Q99">
+        <v>26.18248926166667</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.002552946006416</v>
+      </c>
+      <c r="T99">
+        <v>25.46298594992822</v>
+      </c>
+      <c r="U99">
+        <v>0.0702</v>
+      </c>
+      <c r="V99">
+        <v>0.225</v>
+      </c>
+      <c r="W99">
+        <v>0.054405</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>2.542957869418351</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1726632391651552</v>
+      </c>
+      <c r="C100">
+        <v>67.47674932239039</v>
+      </c>
+      <c r="D100">
+        <v>275.0107493223904</v>
+      </c>
+      <c r="E100">
+        <v>27.934</v>
+      </c>
+      <c r="F100">
+        <v>218.834</v>
+      </c>
+      <c r="G100">
+        <v>11.3</v>
+      </c>
+      <c r="H100">
+        <v>32.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K100">
+        <v>8</v>
+      </c>
+      <c r="L100">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M100">
+        <v>15.3621468</v>
+      </c>
+      <c r="N100">
+        <v>23.30451986666667</v>
+      </c>
+      <c r="O100">
+        <v>5.243516970000002</v>
+      </c>
+      <c r="P100">
+        <v>18.06100289666667</v>
+      </c>
+      <c r="Q100">
+        <v>26.06100289666667</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.967316958257757</v>
+      </c>
+      <c r="T100">
+        <v>38.08454918062496</v>
+      </c>
+      <c r="U100">
+        <v>0.0702</v>
+      </c>
+      <c r="V100">
+        <v>0.225</v>
+      </c>
+      <c r="W100">
+        <v>0.054405</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>2.517009319730409</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1760831149501179</v>
+      </c>
+      <c r="C101">
+        <v>58.39292427698103</v>
+      </c>
+      <c r="D101">
+        <v>268.159924276981</v>
+      </c>
+      <c r="E101">
+        <v>30.167</v>
+      </c>
+      <c r="F101">
+        <v>221.067</v>
+      </c>
+      <c r="G101">
+        <v>11.3</v>
+      </c>
+      <c r="H101">
+        <v>32.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>46.66666666666667</v>
+      </c>
+      <c r="K101">
+        <v>8</v>
+      </c>
+      <c r="L101">
+        <v>38.66666666666667</v>
+      </c>
+      <c r="M101">
+        <v>16.5579183</v>
+      </c>
+      <c r="N101">
+        <v>22.10874836666667</v>
+      </c>
+      <c r="O101">
+        <v>4.974468382500001</v>
+      </c>
+      <c r="P101">
+        <v>17.13427998416667</v>
+      </c>
+      <c r="Q101">
+        <v>25.13427998416667</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>11.86160899501178</v>
+      </c>
+      <c r="T101">
+        <v>75.94923887271521</v>
+      </c>
+      <c r="U101">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V101">
+        <v>0.225</v>
+      </c>
+      <c r="W101">
+        <v>0.05804749999999999</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>2.335237193836539</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_retail_special_lines.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.185945045970635</v>
+        <v>0.1855615446172011</v>
       </c>
       <c r="C2">
-        <v>232.7418267910654</v>
+        <v>231.2656151914656</v>
       </c>
       <c r="D2">
-        <v>226.6018267910655</v>
+        <v>227.2236151914656</v>
       </c>
       <c r="E2">
-        <v>-143.5</v>
+        <v>-141.402</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.098</v>
       </c>
       <c r="G2">
         <v>6.14</v>
@@ -1582,28 +1582,28 @@
         <v>45</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1055294</v>
       </c>
       <c r="N2">
-        <v>45</v>
+        <v>44.8944706</v>
       </c>
       <c r="O2">
-        <v>10.125</v>
+        <v>10.101255885</v>
       </c>
       <c r="P2">
-        <v>34.875</v>
+        <v>34.793214715</v>
       </c>
       <c r="Q2">
-        <v>38.275</v>
+        <v>38.193214715</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.185945045970635</v>
+        <v>0.1870421410274759</v>
       </c>
       <c r="T2">
-        <v>0.9771532823765237</v>
+        <v>0.9848027146375519</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>426.4214522208976</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1855615446172011</v>
+        <v>0.1851780432637672</v>
       </c>
       <c r="C3">
-        <v>231.2656151914656</v>
+        <v>229.7928253172325</v>
       </c>
       <c r="D3">
-        <v>227.2236151914656</v>
+        <v>227.8488253172325</v>
       </c>
       <c r="E3">
-        <v>-141.402</v>
+        <v>-139.304</v>
       </c>
       <c r="F3">
-        <v>2.098</v>
+        <v>4.196000000000001</v>
       </c>
       <c r="G3">
         <v>6.14</v>
@@ -1664,28 +1664,28 @@
         <v>45</v>
       </c>
       <c r="M3">
-        <v>0.1055294</v>
+        <v>0.2110588</v>
       </c>
       <c r="N3">
-        <v>44.8944706</v>
+        <v>44.7889412</v>
       </c>
       <c r="O3">
-        <v>10.101255885</v>
+        <v>10.07751177</v>
       </c>
       <c r="P3">
-        <v>34.793214715</v>
+        <v>34.71142943</v>
       </c>
       <c r="Q3">
-        <v>38.193214715</v>
+        <v>38.11142942999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1870421410274759</v>
+        <v>0.1881616257793542</v>
       </c>
       <c r="T3">
-        <v>0.9848027146375519</v>
+        <v>0.9926082577610502</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>426.4214522208976</v>
+        <v>213.2107261104488</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1851780432637672</v>
+        <v>0.1847945419103332</v>
       </c>
       <c r="C4">
-        <v>229.7928253172325</v>
+        <v>228.3234854911252</v>
       </c>
       <c r="D4">
-        <v>227.8488253172325</v>
+        <v>228.4774854911252</v>
       </c>
       <c r="E4">
-        <v>-139.304</v>
+        <v>-137.206</v>
       </c>
       <c r="F4">
-        <v>4.196000000000001</v>
+        <v>6.294</v>
       </c>
       <c r="G4">
         <v>6.14</v>
@@ -1746,28 +1746,28 @@
         <v>45</v>
       </c>
       <c r="M4">
-        <v>0.2110588</v>
+        <v>0.3165882</v>
       </c>
       <c r="N4">
-        <v>44.7889412</v>
+        <v>44.6834118</v>
       </c>
       <c r="O4">
-        <v>10.07751177</v>
+        <v>10.053767655</v>
       </c>
       <c r="P4">
-        <v>34.71142943</v>
+        <v>34.629644145</v>
       </c>
       <c r="Q4">
-        <v>38.11142942999999</v>
+        <v>38.029644145</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1881616257793542</v>
+        <v>0.1893041926910652</v>
       </c>
       <c r="T4">
-        <v>0.9926082577610502</v>
+        <v>1.000574739918023</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>213.2107261104488</v>
+        <v>142.1404840736326</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1847945419103332</v>
+        <v>0.1844110405568993</v>
       </c>
       <c r="C5">
-        <v>228.3234854911252</v>
+        <v>226.8576243493502</v>
       </c>
       <c r="D5">
-        <v>228.4774854911252</v>
+        <v>229.1096243493502</v>
       </c>
       <c r="E5">
-        <v>-137.206</v>
+        <v>-135.108</v>
       </c>
       <c r="F5">
-        <v>6.294</v>
+        <v>8.392000000000001</v>
       </c>
       <c r="G5">
         <v>6.14</v>
@@ -1828,28 +1828,28 @@
         <v>45</v>
       </c>
       <c r="M5">
-        <v>0.3165882</v>
+        <v>0.4221176</v>
       </c>
       <c r="N5">
-        <v>44.6834118</v>
+        <v>44.5778824</v>
       </c>
       <c r="O5">
-        <v>10.053767655</v>
+        <v>10.03002354</v>
       </c>
       <c r="P5">
-        <v>34.629644145</v>
+        <v>34.54785886</v>
       </c>
       <c r="Q5">
-        <v>38.029644145</v>
+        <v>37.94785886</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1893041926910652</v>
+        <v>0.1904705630801034</v>
       </c>
       <c r="T5">
-        <v>1.000574739918023</v>
+        <v>1.008707190453265</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>142.1404840736326</v>
+        <v>106.6053630552244</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1844110405568993</v>
+        <v>0.1840275392034654</v>
       </c>
       <c r="C6">
-        <v>226.8576243493502</v>
+        <v>225.3952708459097</v>
       </c>
       <c r="D6">
-        <v>229.1096243493502</v>
+        <v>229.7452708459097</v>
       </c>
       <c r="E6">
-        <v>-135.108</v>
+        <v>-133.01</v>
       </c>
       <c r="F6">
-        <v>8.392000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="G6">
         <v>6.14</v>
@@ -1910,28 +1910,28 @@
         <v>45</v>
       </c>
       <c r="M6">
-        <v>0.4221176</v>
+        <v>0.5276470000000001</v>
       </c>
       <c r="N6">
-        <v>44.5778824</v>
+        <v>44.472353</v>
       </c>
       <c r="O6">
-        <v>10.03002354</v>
+        <v>10.006279425</v>
       </c>
       <c r="P6">
-        <v>34.54785886</v>
+        <v>34.466073575</v>
       </c>
       <c r="Q6">
-        <v>37.94785886</v>
+        <v>37.86607357499999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1904705630801034</v>
+        <v>0.1916614886352267</v>
       </c>
       <c r="T6">
-        <v>1.008707190453265</v>
+        <v>1.017010850473461</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>106.6053630552244</v>
+        <v>85.28429044417952</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1840275392034654</v>
+        <v>0.1836440378500315</v>
       </c>
       <c r="C7">
-        <v>225.3952708459097</v>
+        <v>223.9364542570218</v>
       </c>
       <c r="D7">
-        <v>229.7452708459097</v>
+        <v>230.3844542570218</v>
       </c>
       <c r="E7">
-        <v>-133.01</v>
+        <v>-130.912</v>
       </c>
       <c r="F7">
-        <v>10.49</v>
+        <v>12.588</v>
       </c>
       <c r="G7">
         <v>6.14</v>
@@ -1992,28 +1992,28 @@
         <v>45</v>
       </c>
       <c r="M7">
-        <v>0.5276470000000001</v>
+        <v>0.6331764</v>
       </c>
       <c r="N7">
-        <v>44.472353</v>
+        <v>44.3668236</v>
       </c>
       <c r="O7">
-        <v>10.006279425</v>
+        <v>9.982535310000001</v>
       </c>
       <c r="P7">
-        <v>34.466073575</v>
+        <v>34.38428829</v>
       </c>
       <c r="Q7">
-        <v>37.86607357499999</v>
+        <v>37.78428829</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1916614886352267</v>
+        <v>0.1928777530319484</v>
       </c>
       <c r="T7">
-        <v>1.017010850473461</v>
+        <v>1.025491184111107</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>85.28429044417952</v>
+        <v>71.0702420368163</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1836440378500315</v>
+        <v>0.1832605364965975</v>
       </c>
       <c r="C8">
-        <v>223.9364542570218</v>
+        <v>222.4812041856159</v>
       </c>
       <c r="D8">
-        <v>230.3844542570218</v>
+        <v>231.0272041856159</v>
       </c>
       <c r="E8">
-        <v>-130.912</v>
+        <v>-128.814</v>
       </c>
       <c r="F8">
-        <v>12.588</v>
+        <v>14.686</v>
       </c>
       <c r="G8">
         <v>6.14</v>
@@ -2074,28 +2074,28 @@
         <v>45</v>
       </c>
       <c r="M8">
-        <v>0.6331764</v>
+        <v>0.7387058</v>
       </c>
       <c r="N8">
-        <v>44.3668236</v>
+        <v>44.2612942</v>
       </c>
       <c r="O8">
-        <v>9.982535310000001</v>
+        <v>9.958791195</v>
       </c>
       <c r="P8">
-        <v>34.38428829</v>
+        <v>34.30250300500001</v>
       </c>
       <c r="Q8">
-        <v>37.78428829</v>
+        <v>37.702503005</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1928777530319484</v>
+        <v>0.1941201736522554</v>
       </c>
       <c r="T8">
-        <v>1.025491184111107</v>
+        <v>1.034153890515154</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>71.0702420368163</v>
+        <v>60.9173503172711</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1832605364965975</v>
+        <v>0.1828770351431636</v>
       </c>
       <c r="C9">
-        <v>222.481204185616</v>
+        <v>221.0295505659028</v>
       </c>
       <c r="D9">
-        <v>231.027204185616</v>
+        <v>231.6735505659028</v>
       </c>
       <c r="E9">
-        <v>-128.814</v>
+        <v>-126.716</v>
       </c>
       <c r="F9">
-        <v>14.686</v>
+        <v>16.784</v>
       </c>
       <c r="G9">
         <v>6.14</v>
@@ -2156,28 +2156,28 @@
         <v>45</v>
       </c>
       <c r="M9">
-        <v>0.7387058000000001</v>
+        <v>0.8442352000000001</v>
       </c>
       <c r="N9">
-        <v>44.2612942</v>
+        <v>44.1557648</v>
       </c>
       <c r="O9">
-        <v>9.958791195</v>
+        <v>9.93504708</v>
       </c>
       <c r="P9">
-        <v>34.30250300500001</v>
+        <v>34.22071772</v>
       </c>
       <c r="Q9">
-        <v>37.702503005</v>
+        <v>37.62071771999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1941201736522554</v>
+        <v>0.1953896034164822</v>
       </c>
       <c r="T9">
-        <v>1.034153890515154</v>
+        <v>1.043004916623637</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>60.91735031727109</v>
+        <v>53.30268152761221</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1828770351431636</v>
+        <v>0.1824935337897297</v>
       </c>
       <c r="C10">
-        <v>221.0295505659028</v>
+        <v>219.5815236680214</v>
       </c>
       <c r="D10">
-        <v>231.6735505659028</v>
+        <v>232.3235236680214</v>
       </c>
       <c r="E10">
-        <v>-126.716</v>
+        <v>-124.618</v>
       </c>
       <c r="F10">
-        <v>16.784</v>
+        <v>18.882</v>
       </c>
       <c r="G10">
         <v>6.14</v>
@@ -2238,28 +2238,28 @@
         <v>45</v>
       </c>
       <c r="M10">
-        <v>0.8442352000000001</v>
+        <v>0.9497646000000001</v>
       </c>
       <c r="N10">
-        <v>44.1557648</v>
+        <v>44.0502354</v>
       </c>
       <c r="O10">
-        <v>9.93504708</v>
+        <v>9.911302964999999</v>
       </c>
       <c r="P10">
-        <v>34.22071772</v>
+        <v>34.138932435</v>
       </c>
       <c r="Q10">
-        <v>37.62071771999999</v>
+        <v>37.538932435</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1953896034164822</v>
+        <v>0.1966869327359667</v>
       </c>
       <c r="T10">
-        <v>1.043004916623637</v>
+        <v>1.05205047077846</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>53.30268152761221</v>
+        <v>47.38016135787751</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1824935337897297</v>
+        <v>0.1821100324362958</v>
       </c>
       <c r="C11">
-        <v>219.5815236680214</v>
+        <v>218.1371541027648</v>
       </c>
       <c r="D11">
-        <v>232.3235236680214</v>
+        <v>232.9771541027648</v>
       </c>
       <c r="E11">
-        <v>-124.618</v>
+        <v>-122.52</v>
       </c>
       <c r="F11">
-        <v>18.882</v>
+        <v>20.98</v>
       </c>
       <c r="G11">
         <v>6.14</v>
@@ -2320,28 +2320,28 @@
         <v>45</v>
       </c>
       <c r="M11">
-        <v>0.9497646000000001</v>
+        <v>1.055294</v>
       </c>
       <c r="N11">
-        <v>44.0502354</v>
+        <v>43.944706</v>
       </c>
       <c r="O11">
-        <v>9.911302964999999</v>
+        <v>9.88755885</v>
       </c>
       <c r="P11">
-        <v>34.138932435</v>
+        <v>34.05714715</v>
       </c>
       <c r="Q11">
-        <v>37.538932435</v>
+        <v>37.45714715</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1966869327359667</v>
+        <v>0.1980130915958842</v>
       </c>
       <c r="T11">
-        <v>1.05205047077846</v>
+        <v>1.061297037247835</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>47.38016135787751</v>
+        <v>42.64214522208977</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1821100324362958</v>
+        <v>0.1817265310828618</v>
       </c>
       <c r="C12">
-        <v>218.1371541027648</v>
+        <v>216.6964728263857</v>
       </c>
       <c r="D12">
-        <v>232.9771541027648</v>
+        <v>233.6344728263857</v>
       </c>
       <c r="E12">
-        <v>-122.52</v>
+        <v>-120.422</v>
       </c>
       <c r="F12">
-        <v>20.98</v>
+        <v>23.078</v>
       </c>
       <c r="G12">
         <v>6.14</v>
@@ -2402,28 +2402,28 @@
         <v>45</v>
       </c>
       <c r="M12">
-        <v>1.055294</v>
+        <v>1.1608234</v>
       </c>
       <c r="N12">
-        <v>43.944706</v>
+        <v>43.8391766</v>
       </c>
       <c r="O12">
-        <v>9.88755885</v>
+        <v>9.863814735</v>
       </c>
       <c r="P12">
-        <v>34.05714715</v>
+        <v>33.975361865</v>
       </c>
       <c r="Q12">
-        <v>37.45714715</v>
+        <v>37.375361865</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1980130915958842</v>
+        <v>0.1993690517784964</v>
       </c>
       <c r="T12">
-        <v>1.061297037247835</v>
+        <v>1.070751391727758</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>42.64214522208976</v>
+        <v>38.76558656553615</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1817265310828618</v>
+        <v>0.1813430297294279</v>
       </c>
       <c r="C13">
-        <v>216.6964728263857</v>
+        <v>215.2595111454833</v>
       </c>
       <c r="D13">
-        <v>233.6344728263857</v>
+        <v>234.2955111454833</v>
       </c>
       <c r="E13">
-        <v>-120.422</v>
+        <v>-118.324</v>
       </c>
       <c r="F13">
-        <v>23.078</v>
+        <v>25.176</v>
       </c>
       <c r="G13">
         <v>6.14</v>
@@ -2484,28 +2484,28 @@
         <v>45</v>
       </c>
       <c r="M13">
-        <v>1.1608234</v>
+        <v>1.2663528</v>
       </c>
       <c r="N13">
-        <v>43.8391766</v>
+        <v>43.7336472</v>
       </c>
       <c r="O13">
-        <v>9.863814735</v>
+        <v>9.840070620000001</v>
       </c>
       <c r="P13">
-        <v>33.975361865</v>
+        <v>33.89357658</v>
       </c>
       <c r="Q13">
-        <v>37.375361865</v>
+        <v>37.29357658</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1993690517784964</v>
+        <v>0.2007558292379862</v>
       </c>
       <c r="T13">
-        <v>1.070751391727758</v>
+        <v>1.080420617900406</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>38.76558656553615</v>
+        <v>35.53512101840814</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1813430297294279</v>
+        <v>0.180959528375994</v>
       </c>
       <c r="C14">
-        <v>215.2595111454833</v>
+        <v>213.8263007219742</v>
       </c>
       <c r="D14">
-        <v>234.2955111454833</v>
+        <v>234.9603007219742</v>
       </c>
       <c r="E14">
-        <v>-118.324</v>
+        <v>-116.226</v>
       </c>
       <c r="F14">
-        <v>25.176</v>
+        <v>27.274</v>
       </c>
       <c r="G14">
         <v>6.14</v>
@@ -2566,28 +2566,28 @@
         <v>45</v>
       </c>
       <c r="M14">
-        <v>1.2663528</v>
+        <v>1.3718822</v>
       </c>
       <c r="N14">
-        <v>43.7336472</v>
+        <v>43.6281178</v>
       </c>
       <c r="O14">
-        <v>9.840070620000001</v>
+        <v>9.816326504999999</v>
       </c>
       <c r="P14">
-        <v>33.89357658</v>
+        <v>33.811791295</v>
       </c>
       <c r="Q14">
-        <v>37.29357658</v>
+        <v>37.211791295</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2007558292379862</v>
+        <v>0.2021744866390735</v>
       </c>
       <c r="T14">
-        <v>1.080420617900406</v>
+        <v>1.090312125134495</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>35.53512101840814</v>
+        <v>32.80165017083829</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.180959528375994</v>
+        <v>0.18057602702256</v>
       </c>
       <c r="C15">
-        <v>213.8263007219742</v>
+        <v>212.3968735781472</v>
       </c>
       <c r="D15">
-        <v>234.9603007219742</v>
+        <v>235.6288735781472</v>
       </c>
       <c r="E15">
-        <v>-116.226</v>
+        <v>-114.128</v>
       </c>
       <c r="F15">
-        <v>27.274</v>
+        <v>29.372</v>
       </c>
       <c r="G15">
         <v>6.14</v>
@@ -2648,28 +2648,28 @@
         <v>45</v>
       </c>
       <c r="M15">
-        <v>1.3718822</v>
+        <v>1.4774116</v>
       </c>
       <c r="N15">
-        <v>43.6281178</v>
+        <v>43.5225884</v>
       </c>
       <c r="O15">
-        <v>9.816326504999999</v>
+        <v>9.79258239</v>
       </c>
       <c r="P15">
-        <v>33.811791295</v>
+        <v>33.73000601</v>
       </c>
       <c r="Q15">
-        <v>37.211791295</v>
+        <v>37.13000601</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2021744866390735</v>
+        <v>0.2036261360727442</v>
       </c>
       <c r="T15">
-        <v>1.090312125134495</v>
+        <v>1.100433667420538</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>32.80165017083829</v>
+        <v>30.45867515863554</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.18057602702256</v>
+        <v>0.1801925256691261</v>
       </c>
       <c r="C16">
-        <v>212.3968735781472</v>
+        <v>210.9712621018052</v>
       </c>
       <c r="D16">
-        <v>235.6288735781472</v>
+        <v>236.3012621018052</v>
       </c>
       <c r="E16">
-        <v>-114.128</v>
+        <v>-112.03</v>
       </c>
       <c r="F16">
-        <v>29.372</v>
+        <v>31.47000000000001</v>
       </c>
       <c r="G16">
         <v>6.14</v>
@@ -2730,28 +2730,28 @@
         <v>45</v>
       </c>
       <c r="M16">
-        <v>1.4774116</v>
+        <v>1.582941</v>
       </c>
       <c r="N16">
-        <v>43.5225884</v>
+        <v>43.417059</v>
       </c>
       <c r="O16">
-        <v>9.79258239</v>
+        <v>9.768838275</v>
       </c>
       <c r="P16">
-        <v>33.73000601</v>
+        <v>33.648220725</v>
       </c>
       <c r="Q16">
-        <v>37.13000601</v>
+        <v>37.048220725</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2036261360727442</v>
+        <v>0.2051119419636778</v>
       </c>
       <c r="T16">
-        <v>1.100433667420538</v>
+        <v>1.110793363642725</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>30.45867515863554</v>
+        <v>28.42809681472651</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1801925256691261</v>
+        <v>0.1798090243156922</v>
       </c>
       <c r="C17">
-        <v>210.9712621018052</v>
+        <v>209.5494990514953</v>
       </c>
       <c r="D17">
-        <v>236.3012621018052</v>
+        <v>236.9774990514954</v>
       </c>
       <c r="E17">
-        <v>-112.03</v>
+        <v>-109.932</v>
       </c>
       <c r="F17">
-        <v>31.47</v>
+        <v>33.568</v>
       </c>
       <c r="G17">
         <v>6.14</v>
@@ -2812,28 +2812,28 @@
         <v>45</v>
       </c>
       <c r="M17">
-        <v>1.582941</v>
+        <v>1.6884704</v>
       </c>
       <c r="N17">
-        <v>43.417059</v>
+        <v>43.3115296</v>
       </c>
       <c r="O17">
-        <v>9.768838275</v>
+        <v>9.745094160000001</v>
       </c>
       <c r="P17">
-        <v>33.648220725</v>
+        <v>33.56643544</v>
       </c>
       <c r="Q17">
-        <v>37.048220725</v>
+        <v>36.96643544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2051119419636778</v>
+        <v>0.2066331241853478</v>
       </c>
       <c r="T17">
-        <v>1.110793363642725</v>
+        <v>1.121399719298772</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>28.42809681472652</v>
+        <v>26.6513407638061</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1798090243156922</v>
+        <v>0.1794255229622582</v>
       </c>
       <c r="C18">
-        <v>209.5494990514953</v>
+        <v>208.1316175618289</v>
       </c>
       <c r="D18">
-        <v>236.9774990514954</v>
+        <v>237.6576175618289</v>
       </c>
       <c r="E18">
-        <v>-109.932</v>
+        <v>-107.834</v>
       </c>
       <c r="F18">
-        <v>33.568</v>
+        <v>35.666</v>
       </c>
       <c r="G18">
         <v>6.14</v>
@@ -2894,28 +2894,28 @@
         <v>45</v>
       </c>
       <c r="M18">
-        <v>1.6884704</v>
+        <v>1.7939998</v>
       </c>
       <c r="N18">
-        <v>43.3115296</v>
+        <v>43.2060002</v>
       </c>
       <c r="O18">
-        <v>9.745094160000001</v>
+        <v>9.721350044999999</v>
       </c>
       <c r="P18">
-        <v>33.56643544</v>
+        <v>33.484650155</v>
       </c>
       <c r="Q18">
-        <v>36.96643544</v>
+        <v>36.884650155</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2066331241853478</v>
+        <v>0.2081909614003111</v>
       </c>
       <c r="T18">
-        <v>1.121399719298772</v>
+        <v>1.132261649789905</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>26.6513407638061</v>
+        <v>25.08361483652339</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1794255229622582</v>
+        <v>0.1790420216088243</v>
       </c>
       <c r="C19">
-        <v>208.1316175618289</v>
+        <v>206.7176511488936</v>
       </c>
       <c r="D19">
-        <v>237.6576175618289</v>
+        <v>238.3416511488936</v>
       </c>
       <c r="E19">
-        <v>-107.834</v>
+        <v>-105.736</v>
       </c>
       <c r="F19">
-        <v>35.666</v>
+        <v>37.76400000000001</v>
       </c>
       <c r="G19">
         <v>6.14</v>
@@ -2976,28 +2976,28 @@
         <v>45</v>
       </c>
       <c r="M19">
-        <v>1.7939998</v>
+        <v>1.8995292</v>
       </c>
       <c r="N19">
-        <v>43.2060002</v>
+        <v>43.1004708</v>
       </c>
       <c r="O19">
-        <v>9.721350044999999</v>
+        <v>9.69760593</v>
       </c>
       <c r="P19">
-        <v>33.484650155</v>
+        <v>33.40286486999999</v>
       </c>
       <c r="Q19">
-        <v>36.884650155</v>
+        <v>36.80286486999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2081909614003111</v>
+        <v>0.2097867946449077</v>
       </c>
       <c r="T19">
-        <v>1.132261649789905</v>
+        <v>1.143388505414969</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>25.08361483652339</v>
+        <v>23.69008067893875</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1790420216088243</v>
+        <v>0.1786585202553904</v>
       </c>
       <c r="C20">
-        <v>206.7176511488936</v>
+        <v>205.3076337157592</v>
       </c>
       <c r="D20">
-        <v>238.3416511488936</v>
+        <v>239.0296337157592</v>
       </c>
       <c r="E20">
-        <v>-105.736</v>
+        <v>-103.638</v>
       </c>
       <c r="F20">
-        <v>37.764</v>
+        <v>39.862</v>
       </c>
       <c r="G20">
         <v>6.14</v>
@@ -3058,28 +3058,28 @@
         <v>45</v>
       </c>
       <c r="M20">
-        <v>1.8995292</v>
+        <v>2.0050586</v>
       </c>
       <c r="N20">
-        <v>43.1004708</v>
+        <v>42.9949414</v>
       </c>
       <c r="O20">
-        <v>9.69760593</v>
+        <v>9.673861815</v>
       </c>
       <c r="P20">
-        <v>33.40286486999999</v>
+        <v>33.321079585</v>
       </c>
       <c r="Q20">
-        <v>36.80286486999999</v>
+        <v>36.721079585</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2097867946449077</v>
+        <v>0.2114220311794943</v>
       </c>
       <c r="T20">
-        <v>1.143388505414969</v>
+        <v>1.15479009821596</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>23.69008067893876</v>
+        <v>22.44323432741567</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1786585202553904</v>
+        <v>0.1782750189019565</v>
       </c>
       <c r="C21">
-        <v>205.3076337157592</v>
+        <v>203.9015995580789</v>
       </c>
       <c r="D21">
-        <v>239.0296337157592</v>
+        <v>239.721599558079</v>
       </c>
       <c r="E21">
-        <v>-103.638</v>
+        <v>-101.54</v>
       </c>
       <c r="F21">
-        <v>39.862</v>
+        <v>41.96000000000001</v>
       </c>
       <c r="G21">
         <v>6.14</v>
@@ -3140,28 +3140,28 @@
         <v>45</v>
       </c>
       <c r="M21">
-        <v>2.0050586</v>
+        <v>2.110588</v>
       </c>
       <c r="N21">
-        <v>42.9949414</v>
+        <v>42.889412</v>
       </c>
       <c r="O21">
-        <v>9.673861815</v>
+        <v>9.650117700000001</v>
       </c>
       <c r="P21">
-        <v>33.321079585</v>
+        <v>33.2392943</v>
       </c>
       <c r="Q21">
-        <v>36.721079585</v>
+        <v>36.6392943</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2114220311794943</v>
+        <v>0.2130981486274456</v>
       </c>
       <c r="T21">
-        <v>1.15479009821596</v>
+        <v>1.166476730836975</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>22.44323432741567</v>
+        <v>21.32107261104488</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1782750189019565</v>
+        <v>0.1778915175485225</v>
       </c>
       <c r="C22">
-        <v>203.9015995580789</v>
+        <v>202.4995833697881</v>
       </c>
       <c r="D22">
-        <v>239.721599558079</v>
+        <v>240.4175833697882</v>
       </c>
       <c r="E22">
-        <v>-101.54</v>
+        <v>-99.44199999999999</v>
       </c>
       <c r="F22">
-        <v>41.96000000000001</v>
+        <v>44.05800000000001</v>
       </c>
       <c r="G22">
         <v>6.14</v>
@@ -3222,28 +3222,28 @@
         <v>45</v>
       </c>
       <c r="M22">
-        <v>2.110588</v>
+        <v>2.2161174</v>
       </c>
       <c r="N22">
-        <v>42.889412</v>
+        <v>42.7838826</v>
       </c>
       <c r="O22">
-        <v>9.650117700000001</v>
+        <v>9.626373585</v>
       </c>
       <c r="P22">
-        <v>33.2392943</v>
+        <v>33.157509015</v>
       </c>
       <c r="Q22">
-        <v>36.6392943</v>
+        <v>36.557509015</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2130981486274456</v>
+        <v>0.2148166994285095</v>
       </c>
       <c r="T22">
-        <v>1.166476730836975</v>
+        <v>1.178459227574978</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>21.32107261104488</v>
+        <v>20.30578343909036</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1778915175485225</v>
+        <v>0.1775080161950886</v>
       </c>
       <c r="C23">
-        <v>202.4995833697882</v>
+        <v>201.101620248903</v>
       </c>
       <c r="D23">
-        <v>240.4175833697882</v>
+        <v>241.1176202489031</v>
       </c>
       <c r="E23">
-        <v>-99.44200000000001</v>
+        <v>-97.34399999999999</v>
       </c>
       <c r="F23">
-        <v>44.058</v>
+        <v>46.15600000000001</v>
       </c>
       <c r="G23">
         <v>6.14</v>
@@ -3304,28 +3304,28 @@
         <v>45</v>
       </c>
       <c r="M23">
-        <v>2.2161174</v>
+        <v>2.3216468</v>
       </c>
       <c r="N23">
-        <v>42.7838826</v>
+        <v>42.6783532</v>
       </c>
       <c r="O23">
-        <v>9.626373585</v>
+        <v>9.60262947</v>
       </c>
       <c r="P23">
-        <v>33.157509015</v>
+        <v>33.07572372999999</v>
       </c>
       <c r="Q23">
-        <v>36.557509015</v>
+        <v>36.47572372999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2148166994285095</v>
+        <v>0.216579315634729</v>
       </c>
       <c r="T23">
-        <v>1.178459227574978</v>
+        <v>1.190748967819084</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>20.30578343909037</v>
+        <v>19.38279328276807</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1775080161950886</v>
+        <v>0.1771245148416547</v>
       </c>
       <c r="C24">
-        <v>201.101620248903</v>
+        <v>199.707745703421</v>
       </c>
       <c r="D24">
-        <v>241.1176202489031</v>
+        <v>241.821745703421</v>
       </c>
       <c r="E24">
-        <v>-97.34399999999999</v>
+        <v>-95.246</v>
       </c>
       <c r="F24">
-        <v>46.15600000000001</v>
+        <v>48.254</v>
       </c>
       <c r="G24">
         <v>6.14</v>
@@ -3386,28 +3386,28 @@
         <v>45</v>
       </c>
       <c r="M24">
-        <v>2.3216468</v>
+        <v>2.4271762</v>
       </c>
       <c r="N24">
-        <v>42.6783532</v>
+        <v>42.5728238</v>
       </c>
       <c r="O24">
-        <v>9.60262947</v>
+        <v>9.578885355000001</v>
       </c>
       <c r="P24">
-        <v>33.07572372999999</v>
+        <v>32.993938445</v>
       </c>
       <c r="Q24">
-        <v>36.47572372999999</v>
+        <v>36.393938445</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.216579315634729</v>
+        <v>0.218387714080071</v>
       </c>
       <c r="T24">
-        <v>1.190748967819084</v>
+        <v>1.203357922095505</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>19.38279328276807</v>
+        <v>18.54006314003903</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1771245148416547</v>
+        <v>0.1767410134882207</v>
       </c>
       <c r="C25">
-        <v>199.707745703421</v>
+        <v>198.3179956573238</v>
       </c>
       <c r="D25">
-        <v>241.821745703421</v>
+        <v>242.5299956573238</v>
       </c>
       <c r="E25">
-        <v>-95.246</v>
+        <v>-93.148</v>
       </c>
       <c r="F25">
-        <v>48.254</v>
+        <v>50.352</v>
       </c>
       <c r="G25">
         <v>6.14</v>
@@ -3468,28 +3468,28 @@
         <v>45</v>
       </c>
       <c r="M25">
-        <v>2.4271762</v>
+        <v>2.5327056</v>
       </c>
       <c r="N25">
-        <v>42.5728238</v>
+        <v>42.4672944</v>
       </c>
       <c r="O25">
-        <v>9.578885355000001</v>
+        <v>9.555141240000001</v>
       </c>
       <c r="P25">
-        <v>32.993938445</v>
+        <v>32.91215316</v>
       </c>
       <c r="Q25">
-        <v>36.393938445</v>
+        <v>36.31215316</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.218387714080071</v>
+        <v>0.2202437019581852</v>
       </c>
       <c r="T25">
-        <v>1.203357922095505</v>
+        <v>1.216298690958147</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.54006314003903</v>
+        <v>17.76756050920407</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1767410134882207</v>
+        <v>0.1763575121347868</v>
       </c>
       <c r="C26">
-        <v>198.3179956573238</v>
+        <v>196.9324064566876</v>
       </c>
       <c r="D26">
-        <v>242.5299956573238</v>
+        <v>243.2424064566876</v>
       </c>
       <c r="E26">
-        <v>-93.148</v>
+        <v>-91.05</v>
       </c>
       <c r="F26">
-        <v>50.352</v>
+        <v>52.45</v>
       </c>
       <c r="G26">
         <v>6.14</v>
@@ -3550,28 +3550,28 @@
         <v>45</v>
       </c>
       <c r="M26">
-        <v>2.5327056</v>
+        <v>2.638235</v>
       </c>
       <c r="N26">
-        <v>42.4672944</v>
+        <v>42.361765</v>
       </c>
       <c r="O26">
-        <v>9.555141240000001</v>
+        <v>9.531397125</v>
       </c>
       <c r="P26">
-        <v>32.91215316</v>
+        <v>32.830367875</v>
       </c>
       <c r="Q26">
-        <v>36.31215316</v>
+        <v>36.230367875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2202437019581852</v>
+        <v>0.2221491828463824</v>
       </c>
       <c r="T26">
-        <v>1.216298690958147</v>
+        <v>1.229584546990459</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.76756050920407</v>
+        <v>17.05685808883591</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1763575121347868</v>
+        <v>0.1759740107813529</v>
       </c>
       <c r="C27">
-        <v>196.9324064566876</v>
+        <v>195.5510148759008</v>
       </c>
       <c r="D27">
-        <v>243.2424064566876</v>
+        <v>243.9590148759009</v>
       </c>
       <c r="E27">
-        <v>-91.05</v>
+        <v>-88.952</v>
       </c>
       <c r="F27">
-        <v>52.45</v>
+        <v>54.548</v>
       </c>
       <c r="G27">
         <v>6.14</v>
@@ -3632,28 +3632,28 @@
         <v>45</v>
       </c>
       <c r="M27">
-        <v>2.638235</v>
+        <v>2.7437644</v>
       </c>
       <c r="N27">
-        <v>42.361765</v>
+        <v>42.2562356</v>
       </c>
       <c r="O27">
-        <v>9.531397125</v>
+        <v>9.50765301</v>
       </c>
       <c r="P27">
-        <v>32.830367875</v>
+        <v>32.74858259</v>
       </c>
       <c r="Q27">
-        <v>36.230367875</v>
+        <v>36.14858259</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2221491828463824</v>
+        <v>0.2241061632180445</v>
       </c>
       <c r="T27">
-        <v>1.229584546990459</v>
+        <v>1.243229480212834</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>17.05685808883591</v>
+        <v>16.40082508541914</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1759740107813529</v>
+        <v>0.175590509427919</v>
       </c>
       <c r="C28">
-        <v>195.5510148759008</v>
+        <v>194.1738581239911</v>
       </c>
       <c r="D28">
-        <v>243.9590148759009</v>
+        <v>244.6798581239912</v>
       </c>
       <c r="E28">
-        <v>-88.952</v>
+        <v>-86.85399999999998</v>
       </c>
       <c r="F28">
-        <v>54.548</v>
+        <v>56.64600000000001</v>
       </c>
       <c r="G28">
         <v>6.14</v>
@@ -3714,28 +3714,28 @@
         <v>45</v>
       </c>
       <c r="M28">
-        <v>2.7437644</v>
+        <v>2.8492938</v>
       </c>
       <c r="N28">
-        <v>42.2562356</v>
+        <v>42.1507062</v>
       </c>
       <c r="O28">
-        <v>9.50765301</v>
+        <v>9.483908895000001</v>
       </c>
       <c r="P28">
-        <v>32.74858259</v>
+        <v>32.666797305</v>
       </c>
       <c r="Q28">
-        <v>36.14858259</v>
+        <v>36.066797305</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2241061632180445</v>
+        <v>0.2261167594903</v>
       </c>
       <c r="T28">
-        <v>1.243229480212834</v>
+        <v>1.257248247222123</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.40082508541914</v>
+        <v>15.79338711929251</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.175590509427919</v>
+        <v>0.175207008074485</v>
       </c>
       <c r="C29">
-        <v>194.1738581239911</v>
+        <v>192.8009738510665</v>
       </c>
       <c r="D29">
-        <v>244.6798581239912</v>
+        <v>245.4049738510665</v>
       </c>
       <c r="E29">
-        <v>-86.85399999999998</v>
+        <v>-84.756</v>
       </c>
       <c r="F29">
-        <v>56.64600000000001</v>
+        <v>58.74400000000001</v>
       </c>
       <c r="G29">
         <v>6.14</v>
@@ -3796,28 +3796,28 @@
         <v>45</v>
       </c>
       <c r="M29">
-        <v>2.8492938</v>
+        <v>2.9548232</v>
       </c>
       <c r="N29">
-        <v>42.1507062</v>
+        <v>42.0451768</v>
       </c>
       <c r="O29">
-        <v>9.483908895000001</v>
+        <v>9.460164779999999</v>
       </c>
       <c r="P29">
-        <v>32.666797305</v>
+        <v>32.58501202</v>
       </c>
       <c r="Q29">
-        <v>36.066797305</v>
+        <v>35.98501202</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2261167594903</v>
+        <v>0.228183205659007</v>
       </c>
       <c r="T29">
-        <v>1.257248247222123</v>
+        <v>1.271656424426115</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.79338711929251</v>
+        <v>15.22933757931777</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.175207008074485</v>
+        <v>0.1748235067210511</v>
       </c>
       <c r="C30">
-        <v>192.8009738510665</v>
+        <v>191.4324001548699</v>
       </c>
       <c r="D30">
-        <v>245.4049738510665</v>
+        <v>246.13440015487</v>
       </c>
       <c r="E30">
-        <v>-84.756</v>
+        <v>-82.65799999999999</v>
       </c>
       <c r="F30">
-        <v>58.74400000000001</v>
+        <v>60.84200000000001</v>
       </c>
       <c r="G30">
         <v>6.14</v>
@@ -3878,28 +3878,28 @@
         <v>45</v>
       </c>
       <c r="M30">
-        <v>2.9548232</v>
+        <v>3.0603526</v>
       </c>
       <c r="N30">
-        <v>42.0451768</v>
+        <v>41.9396474</v>
       </c>
       <c r="O30">
-        <v>9.460164779999999</v>
+        <v>9.436420665</v>
       </c>
       <c r="P30">
-        <v>32.58501202</v>
+        <v>32.503226735</v>
       </c>
       <c r="Q30">
-        <v>35.98501202</v>
+        <v>35.903226735</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.228183205659007</v>
+        <v>0.2303078615789453</v>
       </c>
       <c r="T30">
-        <v>1.271656424426115</v>
+        <v>1.286470465776698</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.22933757931777</v>
+        <v>14.70418800761716</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1748235067210511</v>
+        <v>0.1744400053676172</v>
       </c>
       <c r="C31">
-        <v>191.43240015487</v>
+        <v>190.0681755874525</v>
       </c>
       <c r="D31">
-        <v>246.13440015487</v>
+        <v>246.8681755874525</v>
       </c>
       <c r="E31">
-        <v>-82.658</v>
+        <v>-80.56</v>
       </c>
       <c r="F31">
-        <v>60.842</v>
+        <v>62.94</v>
       </c>
       <c r="G31">
         <v>6.14</v>
@@ -3960,28 +3960,28 @@
         <v>45</v>
       </c>
       <c r="M31">
-        <v>3.0603526</v>
+        <v>3.165882</v>
       </c>
       <c r="N31">
-        <v>41.9396474</v>
+        <v>41.834118</v>
       </c>
       <c r="O31">
-        <v>9.436420665</v>
+        <v>9.41267655</v>
       </c>
       <c r="P31">
-        <v>32.503226735</v>
+        <v>32.42144145</v>
       </c>
       <c r="Q31">
-        <v>35.903226735</v>
+        <v>35.82144145</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2303078615789452</v>
+        <v>0.2324932219537388</v>
       </c>
       <c r="T31">
-        <v>1.286470465776698</v>
+        <v>1.301707765451583</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.70418800761716</v>
+        <v>14.21404840736326</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1744400053676172</v>
+        <v>0.1740565040141832</v>
       </c>
       <c r="C32">
-        <v>190.0681755874525</v>
+        <v>188.7083391619648</v>
       </c>
       <c r="D32">
-        <v>246.8681755874525</v>
+        <v>247.6063391619648</v>
       </c>
       <c r="E32">
-        <v>-80.56</v>
+        <v>-78.462</v>
       </c>
       <c r="F32">
-        <v>62.94</v>
+        <v>65.038</v>
       </c>
       <c r="G32">
         <v>6.14</v>
@@ -4042,28 +4042,28 @@
         <v>45</v>
       </c>
       <c r="M32">
-        <v>3.165882</v>
+        <v>3.2714114</v>
       </c>
       <c r="N32">
-        <v>41.834118</v>
+        <v>41.7285886</v>
       </c>
       <c r="O32">
-        <v>9.41267655</v>
+        <v>9.388932435000001</v>
       </c>
       <c r="P32">
-        <v>32.42144145</v>
+        <v>32.339656165</v>
       </c>
       <c r="Q32">
-        <v>35.82144145</v>
+        <v>35.739656165</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2324932219537388</v>
+        <v>0.2347419261075119</v>
       </c>
       <c r="T32">
-        <v>1.301707765451583</v>
+        <v>1.31738672598661</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.21404840736326</v>
+        <v>13.75553071680315</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1740565040141832</v>
+        <v>0.1736730026607493</v>
       </c>
       <c r="C33">
-        <v>188.7083391619648</v>
+        <v>187.3529303595716</v>
       </c>
       <c r="D33">
-        <v>247.6063391619648</v>
+        <v>248.3489303595717</v>
       </c>
       <c r="E33">
-        <v>-78.462</v>
+        <v>-76.36399999999999</v>
       </c>
       <c r="F33">
-        <v>65.038</v>
+        <v>67.13600000000001</v>
       </c>
       <c r="G33">
         <v>6.14</v>
@@ -4124,28 +4124,28 @@
         <v>45</v>
       </c>
       <c r="M33">
-        <v>3.2714114</v>
+        <v>3.3769408</v>
       </c>
       <c r="N33">
-        <v>41.7285886</v>
+        <v>41.6230592</v>
       </c>
       <c r="O33">
-        <v>9.388932435000001</v>
+        <v>9.36518832</v>
       </c>
       <c r="P33">
-        <v>32.339656165</v>
+        <v>32.25787088</v>
       </c>
       <c r="Q33">
-        <v>35.739656165</v>
+        <v>35.65787088</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2347419261075119</v>
+        <v>0.237056768618749</v>
       </c>
       <c r="T33">
-        <v>1.31738672598661</v>
+        <v>1.333526832419726</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.75553071680315</v>
+        <v>13.32567038190305</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1736730026607493</v>
+        <v>0.1732895013073154</v>
       </c>
       <c r="C34">
-        <v>187.3529303595716</v>
+        <v>186.0019891364914</v>
       </c>
       <c r="D34">
-        <v>248.3489303595717</v>
+        <v>249.0959891364914</v>
       </c>
       <c r="E34">
-        <v>-76.36399999999999</v>
+        <v>-74.26599999999999</v>
       </c>
       <c r="F34">
-        <v>67.13600000000001</v>
+        <v>69.23400000000001</v>
       </c>
       <c r="G34">
         <v>6.14</v>
@@ -4206,28 +4206,28 @@
         <v>45</v>
       </c>
       <c r="M34">
-        <v>3.3769408</v>
+        <v>3.4824702</v>
       </c>
       <c r="N34">
-        <v>41.6230592</v>
+        <v>41.5175298</v>
       </c>
       <c r="O34">
-        <v>9.36518832</v>
+        <v>9.341444205</v>
       </c>
       <c r="P34">
-        <v>32.25787088</v>
+        <v>32.176085595</v>
       </c>
       <c r="Q34">
-        <v>35.65787088</v>
+        <v>35.576085595</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.237056768618749</v>
+        <v>0.2394407109064409</v>
       </c>
       <c r="T34">
-        <v>1.333526832419726</v>
+        <v>1.350148733074727</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>13.32567038190305</v>
+        <v>12.92186218851205</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1732895013073154</v>
+        <v>0.1733012499538815</v>
       </c>
       <c r="C35">
-        <v>186.0019891364914</v>
+        <v>183.8810361008275</v>
       </c>
       <c r="D35">
-        <v>249.0959891364914</v>
+        <v>249.0730361008275</v>
       </c>
       <c r="E35">
-        <v>-74.26599999999999</v>
+        <v>-72.16799999999999</v>
       </c>
       <c r="F35">
-        <v>69.23400000000001</v>
+        <v>71.33200000000001</v>
       </c>
       <c r="G35">
         <v>6.14</v>
@@ -4288,45 +4288,45 @@
         <v>45</v>
       </c>
       <c r="M35">
-        <v>3.4824702</v>
+        <v>3.6949976</v>
       </c>
       <c r="N35">
-        <v>41.5175298</v>
+        <v>41.3050024</v>
       </c>
       <c r="O35">
-        <v>9.341444205</v>
+        <v>9.293625540000001</v>
       </c>
       <c r="P35">
-        <v>32.176085595</v>
+        <v>32.01137686</v>
       </c>
       <c r="Q35">
-        <v>35.576085595</v>
+        <v>35.41137686</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2394407109064409</v>
+        <v>0.2418968938695174</v>
       </c>
       <c r="T35">
-        <v>1.350148733074727</v>
+        <v>1.367274327688969</v>
       </c>
       <c r="U35">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V35">
         <v>0.225</v>
       </c>
       <c r="W35">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y35">
-        <v>12.92186218851205</v>
+        <v>12.17862766676763</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1733012499538815</v>
+        <v>0.1729293736004475</v>
       </c>
       <c r="C36">
-        <v>183.8810361008275</v>
+        <v>182.5116196671637</v>
       </c>
       <c r="D36">
-        <v>249.0730361008275</v>
+        <v>249.8016196671637</v>
       </c>
       <c r="E36">
-        <v>-72.16799999999999</v>
+        <v>-70.06999999999999</v>
       </c>
       <c r="F36">
-        <v>71.33200000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="G36">
         <v>6.14</v>
@@ -4370,28 +4370,28 @@
         <v>45</v>
       </c>
       <c r="M36">
-        <v>3.6949976</v>
+        <v>3.803674</v>
       </c>
       <c r="N36">
-        <v>41.3050024</v>
+        <v>41.196326</v>
       </c>
       <c r="O36">
-        <v>9.293625540000001</v>
+        <v>9.269173350000001</v>
       </c>
       <c r="P36">
-        <v>32.01137686</v>
+        <v>31.92715265</v>
       </c>
       <c r="Q36">
-        <v>35.41137686</v>
+        <v>35.32715265</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2418968938695174</v>
+        <v>0.2444286516929962</v>
       </c>
       <c r="T36">
-        <v>1.367274327688969</v>
+        <v>1.384926863675958</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>12.17862766676763</v>
+        <v>11.83066687628856</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1729293736004475</v>
+        <v>0.1725574972470136</v>
       </c>
       <c r="C37">
-        <v>182.5116196671637</v>
+        <v>181.1464782153463</v>
       </c>
       <c r="D37">
-        <v>249.8016196671637</v>
+        <v>250.5344782153464</v>
       </c>
       <c r="E37">
-        <v>-70.06999999999999</v>
+        <v>-67.97199999999998</v>
       </c>
       <c r="F37">
-        <v>73.43000000000001</v>
+        <v>75.52800000000002</v>
       </c>
       <c r="G37">
         <v>6.14</v>
@@ -4452,28 +4452,28 @@
         <v>45</v>
       </c>
       <c r="M37">
-        <v>3.803674</v>
+        <v>3.912350400000001</v>
       </c>
       <c r="N37">
-        <v>41.196326</v>
+        <v>41.0876496</v>
       </c>
       <c r="O37">
-        <v>9.269173350000001</v>
+        <v>9.244721159999999</v>
       </c>
       <c r="P37">
-        <v>31.92715265</v>
+        <v>31.84292844</v>
       </c>
       <c r="Q37">
-        <v>35.32715265</v>
+        <v>35.24292844</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2444286516929962</v>
+        <v>0.2470395269484588</v>
       </c>
       <c r="T37">
-        <v>1.384926863675958</v>
+        <v>1.40313104141254</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.83066687628856</v>
+        <v>11.50203724083609</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1725574972470136</v>
+        <v>0.1721856208935797</v>
       </c>
       <c r="C38">
-        <v>181.1464782153463</v>
+        <v>179.7856494814244</v>
       </c>
       <c r="D38">
-        <v>250.5344782153463</v>
+        <v>251.2716494814244</v>
       </c>
       <c r="E38">
-        <v>-67.97199999999999</v>
+        <v>-65.874</v>
       </c>
       <c r="F38">
-        <v>75.52800000000001</v>
+        <v>77.626</v>
       </c>
       <c r="G38">
         <v>6.14</v>
@@ -4534,28 +4534,28 @@
         <v>45</v>
       </c>
       <c r="M38">
-        <v>3.9123504</v>
+        <v>4.0210268</v>
       </c>
       <c r="N38">
-        <v>41.0876496</v>
+        <v>40.9789732</v>
       </c>
       <c r="O38">
-        <v>9.244721159999999</v>
+        <v>9.220268969999999</v>
       </c>
       <c r="P38">
-        <v>31.84292844</v>
+        <v>31.75870423</v>
       </c>
       <c r="Q38">
-        <v>35.24292844</v>
+        <v>35.15870423</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2470395269484588</v>
+        <v>0.2497332871326662</v>
       </c>
       <c r="T38">
-        <v>1.40313104141254</v>
+        <v>1.421913129553457</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.5020372408361</v>
+        <v>11.19117136946215</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1721856208935797</v>
+        <v>0.1718137445401458</v>
       </c>
       <c r="C39">
-        <v>179.7856494814244</v>
+        <v>178.4291716468952</v>
       </c>
       <c r="D39">
-        <v>251.2716494814244</v>
+        <v>252.0131716468952</v>
       </c>
       <c r="E39">
-        <v>-65.874</v>
+        <v>-63.776</v>
       </c>
       <c r="F39">
-        <v>77.626</v>
+        <v>79.724</v>
       </c>
       <c r="G39">
         <v>6.14</v>
@@ -4616,28 +4616,28 @@
         <v>45</v>
       </c>
       <c r="M39">
-        <v>4.0210268</v>
+        <v>4.1297032</v>
       </c>
       <c r="N39">
-        <v>40.9789732</v>
+        <v>40.8702968</v>
       </c>
       <c r="O39">
-        <v>9.220268969999999</v>
+        <v>9.195816779999999</v>
       </c>
       <c r="P39">
-        <v>31.75870423</v>
+        <v>31.67448002</v>
       </c>
       <c r="Q39">
-        <v>35.15870423</v>
+        <v>35.07448002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2497332871326662</v>
+        <v>0.2525139428066867</v>
       </c>
       <c r="T39">
-        <v>1.421913129553457</v>
+        <v>1.441301091505373</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.19117136946215</v>
+        <v>10.89666685973946</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1718137445401458</v>
+        <v>0.1714418681867118</v>
       </c>
       <c r="C40">
-        <v>178.4291716468952</v>
+        <v>177.0770833452958</v>
       </c>
       <c r="D40">
-        <v>252.0131716468952</v>
+        <v>252.7590833452957</v>
       </c>
       <c r="E40">
-        <v>-63.776</v>
+        <v>-61.678</v>
       </c>
       <c r="F40">
-        <v>79.724</v>
+        <v>81.822</v>
       </c>
       <c r="G40">
         <v>6.14</v>
@@ -4698,28 +4698,28 @@
         <v>45</v>
       </c>
       <c r="M40">
-        <v>4.1297032</v>
+        <v>4.2383796</v>
       </c>
       <c r="N40">
-        <v>40.8702968</v>
+        <v>40.7616204</v>
       </c>
       <c r="O40">
-        <v>9.195816779999999</v>
+        <v>9.17136459</v>
       </c>
       <c r="P40">
-        <v>31.67448002</v>
+        <v>31.59025581</v>
       </c>
       <c r="Q40">
-        <v>35.07448002</v>
+        <v>34.99025580999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2525139428066867</v>
+        <v>0.2553857675191997</v>
       </c>
       <c r="T40">
-        <v>1.441301091505373</v>
+        <v>1.461324724340957</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.89666685973946</v>
+        <v>10.61726514538717</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1714418681867118</v>
+        <v>0.1710699918332778</v>
       </c>
       <c r="C41">
-        <v>177.0770833452958</v>
+        <v>175.7294236689134</v>
       </c>
       <c r="D41">
-        <v>252.7590833452957</v>
+        <v>253.5094236689134</v>
       </c>
       <c r="E41">
-        <v>-61.678</v>
+        <v>-59.57999999999998</v>
       </c>
       <c r="F41">
-        <v>81.822</v>
+        <v>83.92000000000002</v>
       </c>
       <c r="G41">
         <v>6.14</v>
@@ -4780,28 +4780,28 @@
         <v>45</v>
       </c>
       <c r="M41">
-        <v>4.2383796</v>
+        <v>4.347056000000001</v>
       </c>
       <c r="N41">
-        <v>40.7616204</v>
+        <v>40.652944</v>
       </c>
       <c r="O41">
-        <v>9.17136459</v>
+        <v>9.1469124</v>
       </c>
       <c r="P41">
-        <v>31.59025581</v>
+        <v>31.5060316</v>
       </c>
       <c r="Q41">
-        <v>34.99025580999999</v>
+        <v>34.9060316</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2553857675191997</v>
+        <v>0.2583533197221298</v>
       </c>
       <c r="T41">
-        <v>1.461324724340957</v>
+        <v>1.482015811604394</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.61726514538717</v>
+        <v>10.35183351675248</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1710699918332778</v>
+        <v>0.170698115479844</v>
       </c>
       <c r="C42">
-        <v>175.7294236689134</v>
+        <v>174.3862321756144</v>
       </c>
       <c r="D42">
-        <v>253.5094236689134</v>
+        <v>254.2642321756144</v>
       </c>
       <c r="E42">
-        <v>-59.57999999999998</v>
+        <v>-57.48199999999999</v>
       </c>
       <c r="F42">
-        <v>83.92000000000002</v>
+        <v>86.01800000000001</v>
       </c>
       <c r="G42">
         <v>6.14</v>
@@ -4862,28 +4862,28 @@
         <v>45</v>
       </c>
       <c r="M42">
-        <v>4.347056000000001</v>
+        <v>4.4557324</v>
       </c>
       <c r="N42">
-        <v>40.652944</v>
+        <v>40.5442676</v>
       </c>
       <c r="O42">
-        <v>9.1469124</v>
+        <v>9.12246021</v>
       </c>
       <c r="P42">
-        <v>31.5060316</v>
+        <v>31.42180739</v>
       </c>
       <c r="Q42">
-        <v>34.9060316</v>
+        <v>34.82180739</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2583533197221298</v>
+        <v>0.2614214669149898</v>
       </c>
       <c r="T42">
-        <v>1.482015811604394</v>
+        <v>1.503408291656423</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.35183351675248</v>
+        <v>10.09934977244145</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.170698115479844</v>
+        <v>0.17032623912641</v>
       </c>
       <c r="C43">
-        <v>174.3862321756144</v>
+        <v>173.0475488957971</v>
       </c>
       <c r="D43">
-        <v>254.2642321756144</v>
+        <v>255.0235488957971</v>
       </c>
       <c r="E43">
-        <v>-57.48199999999999</v>
+        <v>-55.38399999999999</v>
       </c>
       <c r="F43">
-        <v>86.01800000000001</v>
+        <v>88.11600000000001</v>
       </c>
       <c r="G43">
         <v>6.14</v>
@@ -4944,28 +4944,28 @@
         <v>45</v>
       </c>
       <c r="M43">
-        <v>4.4557324</v>
+        <v>4.564408800000001</v>
       </c>
       <c r="N43">
-        <v>40.5442676</v>
+        <v>40.4355912</v>
       </c>
       <c r="O43">
-        <v>9.12246021</v>
+        <v>9.09800802</v>
       </c>
       <c r="P43">
-        <v>31.42180739</v>
+        <v>31.33758318</v>
       </c>
       <c r="Q43">
-        <v>34.82180739</v>
+        <v>34.73758317999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2614214669149898</v>
+        <v>0.2645954122869139</v>
       </c>
       <c r="T43">
-        <v>1.503408291656423</v>
+        <v>1.525538443434383</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.09934977244145</v>
+        <v>9.858889063573795</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.17032623912641</v>
+        <v>0.1705208877729761</v>
       </c>
       <c r="C44">
-        <v>173.0475488957971</v>
+        <v>170.5515402741346</v>
       </c>
       <c r="D44">
-        <v>255.0235488957971</v>
+        <v>254.6255402741346</v>
       </c>
       <c r="E44">
-        <v>-55.384</v>
+        <v>-53.286</v>
       </c>
       <c r="F44">
-        <v>88.116</v>
+        <v>90.214</v>
       </c>
       <c r="G44">
         <v>6.14</v>
@@ -5026,45 +5026,45 @@
         <v>45</v>
       </c>
       <c r="M44">
-        <v>4.5644088</v>
+        <v>4.826449</v>
       </c>
       <c r="N44">
-        <v>40.4355912</v>
+        <v>40.173551</v>
       </c>
       <c r="O44">
-        <v>9.09800802</v>
+        <v>9.039048975000002</v>
       </c>
       <c r="P44">
-        <v>31.33758318</v>
+        <v>31.134502025</v>
       </c>
       <c r="Q44">
-        <v>34.73758317999999</v>
+        <v>34.534502025</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2645954122869138</v>
+        <v>0.267880724163116</v>
       </c>
       <c r="T44">
-        <v>1.525538443434383</v>
+        <v>1.548445091765956</v>
       </c>
       <c r="U44">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V44">
         <v>0.225</v>
       </c>
       <c r="W44">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>9.858889063573796</v>
+        <v>9.323624884464749</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1705208877729761</v>
+        <v>0.1701621864195422</v>
       </c>
       <c r="C45">
-        <v>170.5515402741346</v>
+        <v>169.1879638842749</v>
       </c>
       <c r="D45">
-        <v>254.6255402741346</v>
+        <v>255.3599638842749</v>
       </c>
       <c r="E45">
-        <v>-53.286</v>
+        <v>-51.18799999999999</v>
       </c>
       <c r="F45">
-        <v>90.214</v>
+        <v>92.31200000000001</v>
       </c>
       <c r="G45">
         <v>6.14</v>
@@ -5108,28 +5108,28 @@
         <v>45</v>
       </c>
       <c r="M45">
-        <v>4.826449</v>
+        <v>4.938692000000001</v>
       </c>
       <c r="N45">
-        <v>40.173551</v>
+        <v>40.061308</v>
       </c>
       <c r="O45">
-        <v>9.039048975000002</v>
+        <v>9.013794299999999</v>
       </c>
       <c r="P45">
-        <v>31.134502025</v>
+        <v>31.0475137</v>
       </c>
       <c r="Q45">
-        <v>34.534502025</v>
+        <v>34.44751369999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.267880724163116</v>
+        <v>0.2712833686063253</v>
       </c>
       <c r="T45">
-        <v>1.548445091765956</v>
+        <v>1.5721698346808</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.323624884464749</v>
+        <v>9.111724318908729</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1701621864195422</v>
+        <v>0.1698034850661082</v>
       </c>
       <c r="C46">
-        <v>169.1879638842749</v>
+        <v>167.8286363869815</v>
       </c>
       <c r="D46">
-        <v>255.3599638842749</v>
+        <v>256.0986363869816</v>
       </c>
       <c r="E46">
-        <v>-51.18799999999999</v>
+        <v>-49.08999999999999</v>
       </c>
       <c r="F46">
-        <v>92.31200000000001</v>
+        <v>94.41000000000001</v>
       </c>
       <c r="G46">
         <v>6.14</v>
@@ -5190,28 +5190,28 @@
         <v>45</v>
       </c>
       <c r="M46">
-        <v>4.938692000000001</v>
+        <v>5.050935000000001</v>
       </c>
       <c r="N46">
-        <v>40.061308</v>
+        <v>39.949065</v>
       </c>
       <c r="O46">
-        <v>9.013794299999999</v>
+        <v>8.988539625</v>
       </c>
       <c r="P46">
-        <v>31.0475137</v>
+        <v>30.960525375</v>
       </c>
       <c r="Q46">
-        <v>34.44751369999999</v>
+        <v>34.36052537499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2712833686063253</v>
+        <v>0.2748097455747422</v>
       </c>
       <c r="T46">
-        <v>1.5721698346808</v>
+        <v>1.596757295519819</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.111724318908729</v>
+        <v>8.909241556266313</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1698034850661082</v>
+        <v>0.1694447837126743</v>
       </c>
       <c r="C47">
-        <v>167.8286363869815</v>
+        <v>166.4735947611744</v>
       </c>
       <c r="D47">
-        <v>256.0986363869816</v>
+        <v>256.8415947611745</v>
       </c>
       <c r="E47">
-        <v>-49.08999999999999</v>
+        <v>-46.99199999999999</v>
       </c>
       <c r="F47">
-        <v>94.41000000000001</v>
+        <v>96.50800000000001</v>
       </c>
       <c r="G47">
         <v>6.14</v>
@@ -5272,28 +5272,28 @@
         <v>45</v>
       </c>
       <c r="M47">
-        <v>5.050935000000001</v>
+        <v>5.163178</v>
       </c>
       <c r="N47">
-        <v>39.949065</v>
+        <v>39.836822</v>
       </c>
       <c r="O47">
-        <v>8.988539625</v>
+        <v>8.96328495</v>
       </c>
       <c r="P47">
-        <v>30.960525375</v>
+        <v>30.87353705</v>
       </c>
       <c r="Q47">
-        <v>34.36052537499999</v>
+        <v>34.27353704999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2748097455747422</v>
+        <v>0.278466729097545</v>
       </c>
       <c r="T47">
-        <v>1.596757295519819</v>
+        <v>1.622255403056581</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.909241556266313</v>
+        <v>8.715562391999654</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1694447837126743</v>
+        <v>0.1690860823592404</v>
       </c>
       <c r="C48">
-        <v>166.4735947611744</v>
+        <v>165.1228764161345</v>
       </c>
       <c r="D48">
-        <v>256.8415947611745</v>
+        <v>257.5888764161345</v>
       </c>
       <c r="E48">
-        <v>-46.99199999999999</v>
+        <v>-44.89399999999999</v>
       </c>
       <c r="F48">
-        <v>96.50800000000001</v>
+        <v>98.60600000000001</v>
       </c>
       <c r="G48">
         <v>6.14</v>
@@ -5354,28 +5354,28 @@
         <v>45</v>
       </c>
       <c r="M48">
-        <v>5.163178</v>
+        <v>5.275421000000001</v>
       </c>
       <c r="N48">
-        <v>39.836822</v>
+        <v>39.724579</v>
       </c>
       <c r="O48">
-        <v>8.96328495</v>
+        <v>8.938030274999999</v>
       </c>
       <c r="P48">
-        <v>30.87353705</v>
+        <v>30.786548725</v>
       </c>
       <c r="Q48">
-        <v>34.27353704999999</v>
+        <v>34.18654872499999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.278466729097545</v>
+        <v>0.2822617119985668</v>
       </c>
       <c r="T48">
-        <v>1.622255403056581</v>
+        <v>1.648715703330578</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.715562391999654</v>
+        <v>8.530124894297535</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1690860823592404</v>
+        <v>0.1687273810058065</v>
       </c>
       <c r="C49">
-        <v>165.1228764161345</v>
+        <v>163.7765191977831</v>
       </c>
       <c r="D49">
-        <v>257.5888764161345</v>
+        <v>258.3405191977831</v>
       </c>
       <c r="E49">
-        <v>-44.89399999999999</v>
+        <v>-42.79599999999999</v>
       </c>
       <c r="F49">
-        <v>98.60600000000001</v>
+        <v>100.704</v>
       </c>
       <c r="G49">
         <v>6.14</v>
@@ -5436,28 +5436,28 @@
         <v>45</v>
       </c>
       <c r="M49">
-        <v>5.275421000000001</v>
+        <v>5.387664</v>
       </c>
       <c r="N49">
-        <v>39.724579</v>
+        <v>39.612336</v>
       </c>
       <c r="O49">
-        <v>8.938030274999999</v>
+        <v>8.9127756</v>
       </c>
       <c r="P49">
-        <v>30.786548725</v>
+        <v>30.6995604</v>
       </c>
       <c r="Q49">
-        <v>34.18654872499999</v>
+        <v>34.0995604</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2822617119985668</v>
+        <v>0.2862026557803971</v>
       </c>
       <c r="T49">
-        <v>1.648715703330578</v>
+        <v>1.676193707461268</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.530124894297535</v>
+        <v>8.352413958999669</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1687273810058065</v>
+        <v>0.1683686796523725</v>
       </c>
       <c r="C50">
-        <v>163.7765191977831</v>
+        <v>162.4345613950711</v>
       </c>
       <c r="D50">
-        <v>258.3405191977831</v>
+        <v>259.0965613950711</v>
       </c>
       <c r="E50">
-        <v>-42.79599999999999</v>
+        <v>-40.69799999999999</v>
       </c>
       <c r="F50">
-        <v>100.704</v>
+        <v>102.802</v>
       </c>
       <c r="G50">
         <v>6.14</v>
@@ -5518,28 +5518,28 @@
         <v>45</v>
       </c>
       <c r="M50">
-        <v>5.387664</v>
+        <v>5.499907</v>
       </c>
       <c r="N50">
-        <v>39.612336</v>
+        <v>39.500093</v>
       </c>
       <c r="O50">
-        <v>8.9127756</v>
+        <v>8.887520925</v>
       </c>
       <c r="P50">
-        <v>30.6995604</v>
+        <v>30.612572075</v>
       </c>
       <c r="Q50">
-        <v>34.0995604</v>
+        <v>34.01257207499999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2862026557803971</v>
+        <v>0.290298146377201</v>
       </c>
       <c r="T50">
-        <v>1.676193707461268</v>
+        <v>1.704749280381396</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.352413958999669</v>
+        <v>8.181956531264984</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1683686796523725</v>
+        <v>0.1680099782989386</v>
       </c>
       <c r="C51">
-        <v>162.4345613950711</v>
+        <v>161.0970417464804</v>
       </c>
       <c r="D51">
-        <v>259.0965613950711</v>
+        <v>259.8570417464804</v>
       </c>
       <c r="E51">
-        <v>-40.69799999999999</v>
+        <v>-38.59999999999999</v>
       </c>
       <c r="F51">
-        <v>102.802</v>
+        <v>104.9</v>
       </c>
       <c r="G51">
         <v>6.14</v>
@@ -5600,28 +5600,28 @@
         <v>45</v>
       </c>
       <c r="M51">
-        <v>5.499907</v>
+        <v>5.61215</v>
       </c>
       <c r="N51">
-        <v>39.500093</v>
+        <v>39.38785</v>
       </c>
       <c r="O51">
-        <v>8.887520925</v>
+        <v>8.862266250000001</v>
       </c>
       <c r="P51">
-        <v>30.612572075</v>
+        <v>30.52558375</v>
       </c>
       <c r="Q51">
-        <v>34.01257207499999</v>
+        <v>33.92558375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.290298146377201</v>
+        <v>0.2945574565978772</v>
       </c>
       <c r="T51">
-        <v>1.704749280381396</v>
+        <v>1.734447076218329</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.181956531264984</v>
+        <v>8.018317400639685</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1680099782989386</v>
+        <v>0.1676512769455047</v>
       </c>
       <c r="C52">
-        <v>161.0970417464804</v>
+        <v>159.7639994466404</v>
       </c>
       <c r="D52">
-        <v>259.8570417464804</v>
+        <v>260.6219994466404</v>
       </c>
       <c r="E52">
-        <v>-38.59999999999999</v>
+        <v>-36.502</v>
       </c>
       <c r="F52">
-        <v>104.9</v>
+        <v>106.998</v>
       </c>
       <c r="G52">
         <v>6.14</v>
@@ -5682,28 +5682,28 @@
         <v>45</v>
       </c>
       <c r="M52">
-        <v>5.61215</v>
+        <v>5.724393</v>
       </c>
       <c r="N52">
-        <v>39.38785</v>
+        <v>39.275607</v>
       </c>
       <c r="O52">
-        <v>8.862266250000001</v>
+        <v>8.837011575</v>
       </c>
       <c r="P52">
-        <v>30.52558375</v>
+        <v>30.438595425</v>
       </c>
       <c r="Q52">
-        <v>33.92558375</v>
+        <v>33.838595425</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2945574565978772</v>
+        <v>0.2989906162153157</v>
       </c>
       <c r="T52">
-        <v>1.734447076218329</v>
+        <v>1.765357026987383</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.018317400639685</v>
+        <v>7.861095490823219</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1676512769455047</v>
+        <v>0.1672925755920708</v>
       </c>
       <c r="C53">
-        <v>159.7639994466404</v>
+        <v>158.4354741530625</v>
       </c>
       <c r="D53">
-        <v>260.6219994466404</v>
+        <v>261.3914741530625</v>
       </c>
       <c r="E53">
-        <v>-36.502</v>
+        <v>-34.404</v>
       </c>
       <c r="F53">
-        <v>106.998</v>
+        <v>109.096</v>
       </c>
       <c r="G53">
         <v>6.14</v>
@@ -5764,28 +5764,28 @@
         <v>45</v>
       </c>
       <c r="M53">
-        <v>5.724393</v>
+        <v>5.836636</v>
       </c>
       <c r="N53">
-        <v>39.275607</v>
+        <v>39.163364</v>
       </c>
       <c r="O53">
-        <v>8.837011575</v>
+        <v>8.811756900000001</v>
       </c>
       <c r="P53">
-        <v>30.438595425</v>
+        <v>30.3516071</v>
       </c>
       <c r="Q53">
-        <v>33.838595425</v>
+        <v>33.7516071</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2989906162153157</v>
+        <v>0.3036084908168141</v>
       </c>
       <c r="T53">
-        <v>1.765357026987383</v>
+        <v>1.797554892371814</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.861095490823219</v>
+        <v>7.709920577538157</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1672925755920708</v>
+        <v>0.1672624742386368</v>
       </c>
       <c r="C54">
-        <v>158.4354741530625</v>
+        <v>156.402253313848</v>
       </c>
       <c r="D54">
-        <v>261.3914741530625</v>
+        <v>261.456253313848</v>
       </c>
       <c r="E54">
-        <v>-34.404</v>
+        <v>-32.30599999999998</v>
       </c>
       <c r="F54">
-        <v>109.096</v>
+        <v>111.194</v>
       </c>
       <c r="G54">
         <v>6.14</v>
@@ -5846,45 +5846,45 @@
         <v>45</v>
       </c>
       <c r="M54">
-        <v>5.836636</v>
+        <v>6.037834200000001</v>
       </c>
       <c r="N54">
-        <v>39.163364</v>
+        <v>38.9621658</v>
       </c>
       <c r="O54">
-        <v>8.811756900000001</v>
+        <v>8.766487305</v>
       </c>
       <c r="P54">
-        <v>30.3516071</v>
+        <v>30.195678495</v>
       </c>
       <c r="Q54">
-        <v>33.7516071</v>
+        <v>33.595678495</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3036084908168141</v>
+        <v>0.3084228707205038</v>
       </c>
       <c r="T54">
-        <v>1.797554892371814</v>
+        <v>1.831122879687496</v>
       </c>
       <c r="U54">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V54">
         <v>0.225</v>
       </c>
       <c r="W54">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y54">
-        <v>7.709920577538157</v>
+        <v>7.453003595229561</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1672624742386368</v>
+        <v>0.1669099728852029</v>
       </c>
       <c r="C55">
-        <v>156.402253313848</v>
+        <v>155.0652450056241</v>
       </c>
       <c r="D55">
-        <v>261.456253313848</v>
+        <v>262.2172450056242</v>
       </c>
       <c r="E55">
-        <v>-32.30599999999998</v>
+        <v>-30.20799999999998</v>
       </c>
       <c r="F55">
-        <v>111.194</v>
+        <v>113.292</v>
       </c>
       <c r="G55">
         <v>6.14</v>
@@ -5928,28 +5928,28 @@
         <v>45</v>
       </c>
       <c r="M55">
-        <v>6.037834200000001</v>
+        <v>6.151755600000001</v>
       </c>
       <c r="N55">
-        <v>38.9621658</v>
+        <v>38.8482444</v>
       </c>
       <c r="O55">
-        <v>8.766487305</v>
+        <v>8.740854990000001</v>
       </c>
       <c r="P55">
-        <v>30.195678495</v>
+        <v>30.10738941</v>
       </c>
       <c r="Q55">
-        <v>33.595678495</v>
+        <v>33.50738940999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3084228707205038</v>
+        <v>0.3134465714895715</v>
       </c>
       <c r="T55">
-        <v>1.831122879687496</v>
+        <v>1.866150344712557</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.453003595229561</v>
+        <v>7.314985010132716</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1669099728852029</v>
+        <v>0.1665574715317689</v>
       </c>
       <c r="C56">
-        <v>155.0652450056241</v>
+        <v>153.7326794966394</v>
       </c>
       <c r="D56">
-        <v>262.2172450056242</v>
+        <v>262.9826794966394</v>
       </c>
       <c r="E56">
-        <v>-30.20799999999998</v>
+        <v>-28.10999999999999</v>
       </c>
       <c r="F56">
-        <v>113.292</v>
+        <v>115.39</v>
       </c>
       <c r="G56">
         <v>6.14</v>
@@ -6010,28 +6010,28 @@
         <v>45</v>
       </c>
       <c r="M56">
-        <v>6.151755600000001</v>
+        <v>6.265677000000001</v>
       </c>
       <c r="N56">
-        <v>38.8482444</v>
+        <v>38.734323</v>
       </c>
       <c r="O56">
-        <v>8.740854990000001</v>
+        <v>8.715222675</v>
       </c>
       <c r="P56">
-        <v>30.10738941</v>
+        <v>30.019100325</v>
       </c>
       <c r="Q56">
-        <v>33.50738940999999</v>
+        <v>33.419100325</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3134465714895715</v>
+        <v>0.3186935478483755</v>
       </c>
       <c r="T56">
-        <v>1.866150344712557</v>
+        <v>1.902734585960953</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.314985010132716</v>
+        <v>7.181985282675758</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1665574715317689</v>
+        <v>0.166204970178335</v>
       </c>
       <c r="C57">
-        <v>153.7326794966394</v>
+        <v>152.4045958075271</v>
       </c>
       <c r="D57">
-        <v>262.9826794966394</v>
+        <v>263.7525958075271</v>
       </c>
       <c r="E57">
-        <v>-28.10999999999999</v>
+        <v>-26.01199999999999</v>
       </c>
       <c r="F57">
-        <v>115.39</v>
+        <v>117.488</v>
       </c>
       <c r="G57">
         <v>6.14</v>
@@ -6092,28 +6092,28 @@
         <v>45</v>
       </c>
       <c r="M57">
-        <v>6.265677000000001</v>
+        <v>6.379598400000001</v>
       </c>
       <c r="N57">
-        <v>38.734323</v>
+        <v>38.6204016</v>
       </c>
       <c r="O57">
-        <v>8.715222675</v>
+        <v>8.68959036</v>
       </c>
       <c r="P57">
-        <v>30.019100325</v>
+        <v>29.93081124</v>
       </c>
       <c r="Q57">
-        <v>33.419100325</v>
+        <v>33.33081124</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3186935478483755</v>
+        <v>0.3241790231325796</v>
       </c>
       <c r="T57">
-        <v>1.902734585960953</v>
+        <v>1.940981747266095</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.181985282675758</v>
+        <v>7.05373554548512</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.166204970178335</v>
+        <v>0.1658524688249011</v>
       </c>
       <c r="C58">
-        <v>152.4045958075271</v>
+        <v>151.0810334172149</v>
       </c>
       <c r="D58">
-        <v>263.7525958075271</v>
+        <v>264.5270334172149</v>
       </c>
       <c r="E58">
-        <v>-26.01199999999999</v>
+        <v>-23.91399999999999</v>
       </c>
       <c r="F58">
-        <v>117.488</v>
+        <v>119.586</v>
       </c>
       <c r="G58">
         <v>6.14</v>
@@ -6174,28 +6174,28 @@
         <v>45</v>
       </c>
       <c r="M58">
-        <v>6.379598400000001</v>
+        <v>6.493519800000001</v>
       </c>
       <c r="N58">
-        <v>38.6204016</v>
+        <v>38.5064802</v>
       </c>
       <c r="O58">
-        <v>8.68959036</v>
+        <v>8.663958044999999</v>
       </c>
       <c r="P58">
-        <v>29.93081124</v>
+        <v>29.842522155</v>
       </c>
       <c r="Q58">
-        <v>33.33081124</v>
+        <v>33.242522155</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3241790231325796</v>
+        <v>0.3299196368020956</v>
       </c>
       <c r="T58">
-        <v>1.940981747266095</v>
+        <v>1.981007846306359</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.05373554548512</v>
+        <v>6.9299857990731</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1658524688249011</v>
+        <v>0.1654999674714672</v>
       </c>
       <c r="C59">
-        <v>151.0810334172149</v>
+        <v>149.7620322696719</v>
       </c>
       <c r="D59">
-        <v>264.5270334172149</v>
+        <v>265.306032269672</v>
       </c>
       <c r="E59">
-        <v>-23.91399999999999</v>
+        <v>-21.81599999999997</v>
       </c>
       <c r="F59">
-        <v>119.586</v>
+        <v>121.684</v>
       </c>
       <c r="G59">
         <v>6.14</v>
@@ -6256,28 +6256,28 @@
         <v>45</v>
       </c>
       <c r="M59">
-        <v>6.493519800000001</v>
+        <v>6.607441200000001</v>
       </c>
       <c r="N59">
-        <v>38.5064802</v>
+        <v>38.3925588</v>
       </c>
       <c r="O59">
-        <v>8.663958044999999</v>
+        <v>8.63832573</v>
       </c>
       <c r="P59">
-        <v>29.842522155</v>
+        <v>29.75423307</v>
       </c>
       <c r="Q59">
-        <v>33.242522155</v>
+        <v>33.15423307</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3299196368020956</v>
+        <v>0.3359336130273028</v>
       </c>
       <c r="T59">
-        <v>1.981007846306359</v>
+        <v>2.022939950062827</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.9299857990731</v>
+        <v>6.810503285295977</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1654999674714672</v>
+        <v>0.1651474661180332</v>
       </c>
       <c r="C60">
-        <v>149.7620322696719</v>
+        <v>148.4476327807775</v>
       </c>
       <c r="D60">
-        <v>265.306032269672</v>
+        <v>266.0896327807775</v>
       </c>
       <c r="E60">
-        <v>-21.816</v>
+        <v>-19.718</v>
       </c>
       <c r="F60">
-        <v>121.684</v>
+        <v>123.782</v>
       </c>
       <c r="G60">
         <v>6.14</v>
@@ -6338,28 +6338,28 @@
         <v>45</v>
       </c>
       <c r="M60">
-        <v>6.6074412</v>
+        <v>6.7213626</v>
       </c>
       <c r="N60">
-        <v>38.3925588</v>
+        <v>38.2786374</v>
       </c>
       <c r="O60">
-        <v>8.638325730000002</v>
+        <v>8.612693415000001</v>
       </c>
       <c r="P60">
-        <v>29.75423307</v>
+        <v>29.665943985</v>
       </c>
       <c r="Q60">
-        <v>33.15423307</v>
+        <v>33.065943985</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3359336130273027</v>
+        <v>0.3422409539464225</v>
       </c>
       <c r="T60">
-        <v>2.022939950062827</v>
+        <v>2.06691752229522</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.810503285295979</v>
+        <v>6.695071026223165</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1651474661180332</v>
+        <v>0.1647949647645993</v>
       </c>
       <c r="C61">
-        <v>148.4476327807775</v>
+        <v>147.1378758453098</v>
       </c>
       <c r="D61">
-        <v>266.0896327807775</v>
+        <v>266.8778758453099</v>
       </c>
       <c r="E61">
-        <v>-19.718</v>
+        <v>-17.62</v>
       </c>
       <c r="F61">
-        <v>123.782</v>
+        <v>125.88</v>
       </c>
       <c r="G61">
         <v>6.14</v>
@@ -6420,28 +6420,28 @@
         <v>45</v>
       </c>
       <c r="M61">
-        <v>6.7213626</v>
+        <v>6.835284</v>
       </c>
       <c r="N61">
-        <v>38.2786374</v>
+        <v>38.164716</v>
       </c>
       <c r="O61">
-        <v>8.612693415000001</v>
+        <v>8.5870611</v>
       </c>
       <c r="P61">
-        <v>29.665943985</v>
+        <v>29.5776549</v>
       </c>
       <c r="Q61">
-        <v>33.065943985</v>
+        <v>32.9776549</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3422409539464225</v>
+        <v>0.3488636619114982</v>
       </c>
       <c r="T61">
-        <v>2.06691752229522</v>
+        <v>2.113093973139232</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.695071026223165</v>
+        <v>6.583486509119446</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1647949647645993</v>
+        <v>0.1644424634111654</v>
       </c>
       <c r="C62">
-        <v>147.1378758453098</v>
+        <v>145.8328028440608</v>
       </c>
       <c r="D62">
-        <v>266.8778758453099</v>
+        <v>267.6708028440609</v>
       </c>
       <c r="E62">
-        <v>-17.62</v>
+        <v>-15.52199999999999</v>
       </c>
       <c r="F62">
-        <v>125.88</v>
+        <v>127.978</v>
       </c>
       <c r="G62">
         <v>6.14</v>
@@ -6502,28 +6502,28 @@
         <v>45</v>
       </c>
       <c r="M62">
-        <v>6.835284</v>
+        <v>6.9492054</v>
       </c>
       <c r="N62">
-        <v>38.164716</v>
+        <v>38.0507946</v>
       </c>
       <c r="O62">
-        <v>8.5870611</v>
+        <v>8.561428785</v>
       </c>
       <c r="P62">
-        <v>29.5776549</v>
+        <v>29.489365815</v>
       </c>
       <c r="Q62">
-        <v>32.9776549</v>
+        <v>32.88936581500001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3488636619114982</v>
+        <v>0.3558259959260651</v>
       </c>
       <c r="T62">
-        <v>2.113093973139232</v>
+        <v>2.161638447103451</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.583486509119446</v>
+        <v>6.475560500773225</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1644424634111654</v>
+        <v>0.1640899620577314</v>
       </c>
       <c r="C63">
-        <v>145.8328028440608</v>
+        <v>144.5324556510779</v>
       </c>
       <c r="D63">
-        <v>267.6708028440609</v>
+        <v>268.4684556510779</v>
       </c>
       <c r="E63">
-        <v>-15.52199999999999</v>
+        <v>-13.42400000000001</v>
       </c>
       <c r="F63">
-        <v>127.978</v>
+        <v>130.076</v>
       </c>
       <c r="G63">
         <v>6.14</v>
@@ -6584,28 +6584,28 @@
         <v>45</v>
       </c>
       <c r="M63">
-        <v>6.9492054</v>
+        <v>7.0631268</v>
       </c>
       <c r="N63">
-        <v>38.0507946</v>
+        <v>37.9368732</v>
       </c>
       <c r="O63">
-        <v>8.561428785</v>
+        <v>8.535796470000001</v>
       </c>
       <c r="P63">
-        <v>29.489365815</v>
+        <v>29.40107673</v>
       </c>
       <c r="Q63">
-        <v>32.88936581500001</v>
+        <v>32.80107673</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3558259959260651</v>
+        <v>0.3631547685729775</v>
       </c>
       <c r="T63">
-        <v>2.161638447103451</v>
+        <v>2.212737893381575</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.475560500773225</v>
+        <v>6.371115976567205</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1640899620577314</v>
+        <v>0.1637374607042975</v>
       </c>
       <c r="C64">
-        <v>144.5324556510779</v>
+        <v>143.2368766410345</v>
       </c>
       <c r="D64">
-        <v>268.4684556510779</v>
+        <v>269.2708766410345</v>
       </c>
       <c r="E64">
-        <v>-13.42400000000001</v>
+        <v>-11.32599999999999</v>
       </c>
       <c r="F64">
-        <v>130.076</v>
+        <v>132.174</v>
       </c>
       <c r="G64">
         <v>6.14</v>
@@ -6666,28 +6666,28 @@
         <v>45</v>
       </c>
       <c r="M64">
-        <v>7.0631268</v>
+        <v>7.177048200000001</v>
       </c>
       <c r="N64">
-        <v>37.9368732</v>
+        <v>37.8229518</v>
       </c>
       <c r="O64">
-        <v>8.535796470000001</v>
+        <v>8.510164155</v>
       </c>
       <c r="P64">
-        <v>29.40107673</v>
+        <v>29.312787645</v>
       </c>
       <c r="Q64">
-        <v>32.80107673</v>
+        <v>32.712787645</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3631547685729775</v>
+        <v>0.370879691092696</v>
       </c>
       <c r="T64">
-        <v>2.212737893381575</v>
+        <v>2.26659947189095</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.371115976567205</v>
+        <v>6.269987151542328</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1637374607042975</v>
+        <v>0.1633849593508636</v>
       </c>
       <c r="C65">
-        <v>143.2368766410345</v>
+        <v>141.9461086967354</v>
       </c>
       <c r="D65">
-        <v>269.2708766410345</v>
+        <v>270.0781086967354</v>
       </c>
       <c r="E65">
-        <v>-11.32599999999999</v>
+        <v>-9.22799999999998</v>
       </c>
       <c r="F65">
-        <v>132.174</v>
+        <v>134.272</v>
       </c>
       <c r="G65">
         <v>6.14</v>
@@ -6748,28 +6748,28 @@
         <v>45</v>
       </c>
       <c r="M65">
-        <v>7.177048200000001</v>
+        <v>7.290969600000001</v>
       </c>
       <c r="N65">
-        <v>37.8229518</v>
+        <v>37.7090304</v>
       </c>
       <c r="O65">
-        <v>8.510164155</v>
+        <v>8.484531839999999</v>
       </c>
       <c r="P65">
-        <v>29.312787645</v>
+        <v>29.22449856</v>
       </c>
       <c r="Q65">
-        <v>32.712787645</v>
+        <v>32.62449855999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.370879691092696</v>
+        <v>0.3790337759746211</v>
       </c>
       <c r="T65">
-        <v>2.26659947189095</v>
+        <v>2.323453360317512</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.269987151542328</v>
+        <v>6.172018602299478</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1633849593508636</v>
+        <v>0.1635362079974297</v>
       </c>
       <c r="C66">
-        <v>141.9461086967354</v>
+        <v>139.5011555452597</v>
       </c>
       <c r="D66">
-        <v>270.0781086967354</v>
+        <v>269.7311555452598</v>
       </c>
       <c r="E66">
-        <v>-9.22799999999998</v>
+        <v>-7.129999999999995</v>
       </c>
       <c r="F66">
-        <v>134.272</v>
+        <v>136.37</v>
       </c>
       <c r="G66">
         <v>6.14</v>
@@ -6830,45 +6830,45 @@
         <v>45</v>
       </c>
       <c r="M66">
-        <v>7.290969600000001</v>
+        <v>7.541261</v>
       </c>
       <c r="N66">
-        <v>37.7090304</v>
+        <v>37.458739</v>
       </c>
       <c r="O66">
-        <v>8.484531839999999</v>
+        <v>8.428216275</v>
       </c>
       <c r="P66">
-        <v>29.22449856</v>
+        <v>29.030522725</v>
       </c>
       <c r="Q66">
-        <v>32.62449855999999</v>
+        <v>32.430522725</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3790337759746211</v>
+        <v>0.3876538085640848</v>
       </c>
       <c r="T66">
-        <v>2.323453360317512</v>
+        <v>2.383556042368449</v>
       </c>
       <c r="U66">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V66">
         <v>0.225</v>
       </c>
       <c r="W66">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>6.172018602299478</v>
+        <v>5.967171803230255</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1635362079974297</v>
+        <v>0.1631914566439957</v>
       </c>
       <c r="C67">
-        <v>139.5011555452597</v>
+        <v>138.1952930959465</v>
       </c>
       <c r="D67">
-        <v>269.7311555452598</v>
+        <v>270.5232930959465</v>
       </c>
       <c r="E67">
-        <v>-7.129999999999995</v>
+        <v>-5.031999999999982</v>
       </c>
       <c r="F67">
-        <v>136.37</v>
+        <v>138.468</v>
       </c>
       <c r="G67">
         <v>6.14</v>
@@ -6912,28 +6912,28 @@
         <v>45</v>
       </c>
       <c r="M67">
-        <v>7.541261</v>
+        <v>7.657280400000001</v>
       </c>
       <c r="N67">
-        <v>37.458739</v>
+        <v>37.3427196</v>
       </c>
       <c r="O67">
-        <v>8.428216275</v>
+        <v>8.402111909999999</v>
       </c>
       <c r="P67">
-        <v>29.030522725</v>
+        <v>28.94060769</v>
       </c>
       <c r="Q67">
-        <v>32.430522725</v>
+        <v>32.34060769</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3876538085640848</v>
+        <v>0.3967809018941051</v>
       </c>
       <c r="T67">
-        <v>2.383556042368449</v>
+        <v>2.447194176304735</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.967171803230255</v>
+        <v>5.876760109241917</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1631914566439957</v>
+        <v>0.1628467052905618</v>
       </c>
       <c r="C68">
-        <v>138.1952930959465</v>
+        <v>136.8940969974207</v>
       </c>
       <c r="D68">
-        <v>270.5232930959465</v>
+        <v>271.3200969974207</v>
       </c>
       <c r="E68">
-        <v>-5.031999999999982</v>
+        <v>-2.933999999999997</v>
       </c>
       <c r="F68">
-        <v>138.468</v>
+        <v>140.566</v>
       </c>
       <c r="G68">
         <v>6.14</v>
@@ -6994,28 +6994,28 @@
         <v>45</v>
       </c>
       <c r="M68">
-        <v>7.657280400000001</v>
+        <v>7.7732998</v>
       </c>
       <c r="N68">
-        <v>37.3427196</v>
+        <v>37.2267002</v>
       </c>
       <c r="O68">
-        <v>8.402111909999999</v>
+        <v>8.376007545</v>
       </c>
       <c r="P68">
-        <v>28.94060769</v>
+        <v>28.850692655</v>
       </c>
       <c r="Q68">
-        <v>32.34060769</v>
+        <v>32.25069265499999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3967809018941051</v>
+        <v>0.406461152395642</v>
       </c>
       <c r="T68">
-        <v>2.447194176304735</v>
+        <v>2.514689166843221</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.876760109241917</v>
+        <v>5.789047271790546</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1628467052905618</v>
+        <v>0.1625019539371279</v>
       </c>
       <c r="C69">
-        <v>136.8940969974207</v>
+        <v>135.5976086045364</v>
       </c>
       <c r="D69">
-        <v>271.3200969974207</v>
+        <v>272.1216086045364</v>
       </c>
       <c r="E69">
-        <v>-2.933999999999997</v>
+        <v>-0.8359999999999843</v>
       </c>
       <c r="F69">
-        <v>140.566</v>
+        <v>142.664</v>
       </c>
       <c r="G69">
         <v>6.14</v>
@@ -7076,28 +7076,28 @@
         <v>45</v>
       </c>
       <c r="M69">
-        <v>7.7732998</v>
+        <v>7.889319200000001</v>
       </c>
       <c r="N69">
-        <v>37.2267002</v>
+        <v>37.1106808</v>
       </c>
       <c r="O69">
-        <v>8.376007545</v>
+        <v>8.34990318</v>
       </c>
       <c r="P69">
-        <v>28.850692655</v>
+        <v>28.76077762</v>
       </c>
       <c r="Q69">
-        <v>32.25069265499999</v>
+        <v>32.16077762</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.406461152395642</v>
+        <v>0.4167464185535247</v>
       </c>
       <c r="T69">
-        <v>2.514689166843221</v>
+        <v>2.586402594290361</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.789047271790546</v>
+        <v>5.703914223675978</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1625019539371279</v>
+        <v>0.162157202583694</v>
       </c>
       <c r="C70">
-        <v>135.5976086045364</v>
+        <v>134.3058697622636</v>
       </c>
       <c r="D70">
-        <v>272.1216086045364</v>
+        <v>272.9278697622636</v>
       </c>
       <c r="E70">
-        <v>-0.8359999999999843</v>
+        <v>1.262000000000029</v>
       </c>
       <c r="F70">
-        <v>142.664</v>
+        <v>144.762</v>
       </c>
       <c r="G70">
         <v>6.14</v>
@@ -7158,28 +7158,28 @@
         <v>45</v>
       </c>
       <c r="M70">
-        <v>7.889319200000001</v>
+        <v>8.005338600000002</v>
       </c>
       <c r="N70">
-        <v>37.1106808</v>
+        <v>36.9946614</v>
       </c>
       <c r="O70">
-        <v>8.34990318</v>
+        <v>8.323798815</v>
       </c>
       <c r="P70">
-        <v>28.76077762</v>
+        <v>28.670862585</v>
       </c>
       <c r="Q70">
-        <v>32.16077762</v>
+        <v>32.070862585</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4167464185535247</v>
+        <v>0.4276952502699806</v>
       </c>
       <c r="T70">
-        <v>2.586402594290361</v>
+        <v>2.662742694476028</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.703914223675978</v>
+        <v>5.621248800144443</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.162157202583694</v>
+        <v>0.16181245123026</v>
       </c>
       <c r="C71">
-        <v>134.3058697622636</v>
+        <v>133.0189228129714</v>
       </c>
       <c r="D71">
-        <v>272.9278697622636</v>
+        <v>273.7389228129714</v>
       </c>
       <c r="E71">
-        <v>1.262000000000029</v>
+        <v>3.360000000000014</v>
       </c>
       <c r="F71">
-        <v>144.762</v>
+        <v>146.86</v>
       </c>
       <c r="G71">
         <v>6.14</v>
@@ -7240,28 +7240,28 @@
         <v>45</v>
       </c>
       <c r="M71">
-        <v>8.005338600000002</v>
+        <v>8.121358000000001</v>
       </c>
       <c r="N71">
-        <v>36.9946614</v>
+        <v>36.878642</v>
       </c>
       <c r="O71">
-        <v>8.323798815</v>
+        <v>8.29769445</v>
       </c>
       <c r="P71">
-        <v>28.670862585</v>
+        <v>28.58094755</v>
       </c>
       <c r="Q71">
-        <v>32.070862585</v>
+        <v>31.98094755</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4276952502699806</v>
+        <v>0.4393740041008667</v>
       </c>
       <c r="T71">
-        <v>2.662742694476028</v>
+        <v>2.744172134674071</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.621248800144443</v>
+        <v>5.540945245856665</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.16181245123026</v>
+        <v>0.1614676998768261</v>
       </c>
       <c r="C72">
-        <v>133.0189228129714</v>
+        <v>131.7368106038396</v>
       </c>
       <c r="D72">
-        <v>273.7389228129714</v>
+        <v>274.5548106038397</v>
       </c>
       <c r="E72">
-        <v>3.360000000000014</v>
+        <v>5.458000000000027</v>
       </c>
       <c r="F72">
-        <v>146.86</v>
+        <v>148.958</v>
       </c>
       <c r="G72">
         <v>6.14</v>
@@ -7322,28 +7322,28 @@
         <v>45</v>
       </c>
       <c r="M72">
-        <v>8.121358000000001</v>
+        <v>8.237377400000002</v>
       </c>
       <c r="N72">
-        <v>36.878642</v>
+        <v>36.7626226</v>
       </c>
       <c r="O72">
-        <v>8.29769445</v>
+        <v>8.271590085</v>
       </c>
       <c r="P72">
-        <v>28.58094755</v>
+        <v>28.491032515</v>
       </c>
       <c r="Q72">
-        <v>31.98094755</v>
+        <v>31.891032515</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4393740041008667</v>
+        <v>0.4518581892304349</v>
       </c>
       <c r="T72">
-        <v>2.744172134674071</v>
+        <v>2.831217398334049</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.540945245856665</v>
+        <v>5.462903763520655</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1614676998768261</v>
+        <v>0.1611229485233922</v>
       </c>
       <c r="C73">
-        <v>131.7368106038396</v>
+        <v>130.4595764944053</v>
       </c>
       <c r="D73">
-        <v>274.5548106038397</v>
+        <v>275.3755764944053</v>
       </c>
       <c r="E73">
-        <v>5.457999999999998</v>
+        <v>7.556000000000012</v>
       </c>
       <c r="F73">
-        <v>148.958</v>
+        <v>151.056</v>
       </c>
       <c r="G73">
         <v>6.14</v>
@@ -7404,28 +7404,28 @@
         <v>45</v>
       </c>
       <c r="M73">
-        <v>8.2373774</v>
+        <v>8.353396800000001</v>
       </c>
       <c r="N73">
-        <v>36.7626226</v>
+        <v>36.6466032</v>
       </c>
       <c r="O73">
-        <v>8.271590085</v>
+        <v>8.245485720000001</v>
       </c>
       <c r="P73">
-        <v>28.491032515</v>
+        <v>28.40111748</v>
       </c>
       <c r="Q73">
-        <v>31.891032515</v>
+        <v>31.80111748</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4518581892304347</v>
+        <v>0.4652341018692577</v>
       </c>
       <c r="T73">
-        <v>2.831217398334048</v>
+        <v>2.924480180826881</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.462903763520656</v>
+        <v>5.387030100138425</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1611229485233922</v>
+        <v>0.1607781971699582</v>
       </c>
       <c r="C74">
-        <v>130.4595764944053</v>
+        <v>129.1872643642436</v>
       </c>
       <c r="D74">
-        <v>275.3755764944053</v>
+        <v>276.2012643642436</v>
       </c>
       <c r="E74">
-        <v>7.556000000000012</v>
+        <v>9.653999999999996</v>
       </c>
       <c r="F74">
-        <v>151.056</v>
+        <v>153.154</v>
       </c>
       <c r="G74">
         <v>6.14</v>
@@ -7486,28 +7486,28 @@
         <v>45</v>
       </c>
       <c r="M74">
-        <v>8.353396800000001</v>
+        <v>8.4694162</v>
       </c>
       <c r="N74">
-        <v>36.6466032</v>
+        <v>36.5305838</v>
       </c>
       <c r="O74">
-        <v>8.245485720000001</v>
+        <v>8.219381355000001</v>
       </c>
       <c r="P74">
-        <v>28.40111748</v>
+        <v>28.311202445</v>
       </c>
       <c r="Q74">
-        <v>31.80111748</v>
+        <v>31.711202445</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4652341018692577</v>
+        <v>0.4796008228516971</v>
       </c>
       <c r="T74">
-        <v>2.924480180826881</v>
+        <v>3.024651317578443</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.387030100138425</v>
+        <v>5.313235167259817</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1607781971699582</v>
+        <v>0.1604334458165243</v>
       </c>
       <c r="C75">
-        <v>129.1872643642436</v>
+        <v>127.9199186207869</v>
       </c>
       <c r="D75">
-        <v>276.2012643642436</v>
+        <v>277.0319186207869</v>
       </c>
       <c r="E75">
-        <v>9.653999999999996</v>
+        <v>11.75200000000001</v>
       </c>
       <c r="F75">
-        <v>153.154</v>
+        <v>155.252</v>
       </c>
       <c r="G75">
         <v>6.14</v>
@@ -7568,28 +7568,28 @@
         <v>45</v>
       </c>
       <c r="M75">
-        <v>8.4694162</v>
+        <v>8.5854356</v>
       </c>
       <c r="N75">
-        <v>36.5305838</v>
+        <v>36.4145644</v>
       </c>
       <c r="O75">
-        <v>8.219381355000001</v>
+        <v>8.193276990000001</v>
       </c>
       <c r="P75">
-        <v>28.311202445</v>
+        <v>28.22128741</v>
       </c>
       <c r="Q75">
-        <v>31.711202445</v>
+        <v>31.62128741</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4796008228516971</v>
+        <v>0.4950726762174011</v>
       </c>
       <c r="T75">
-        <v>3.024651317578443</v>
+        <v>3.132527926387817</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.313235167259817</v>
+        <v>5.241434692026576</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1604334458165243</v>
+        <v>0.1600886944630904</v>
       </c>
       <c r="C76">
-        <v>127.9199186207869</v>
+        <v>126.6575842072878</v>
       </c>
       <c r="D76">
-        <v>277.0319186207869</v>
+        <v>277.8675842072878</v>
       </c>
       <c r="E76">
-        <v>11.75200000000001</v>
+        <v>13.85000000000002</v>
       </c>
       <c r="F76">
-        <v>155.252</v>
+        <v>157.35</v>
       </c>
       <c r="G76">
         <v>6.14</v>
@@ -7650,28 +7650,28 @@
         <v>45</v>
       </c>
       <c r="M76">
-        <v>8.5854356</v>
+        <v>8.701455000000001</v>
       </c>
       <c r="N76">
-        <v>36.4145644</v>
+        <v>36.298545</v>
       </c>
       <c r="O76">
-        <v>8.193276990000001</v>
+        <v>8.167172624999999</v>
       </c>
       <c r="P76">
-        <v>28.22128741</v>
+        <v>28.131372375</v>
       </c>
       <c r="Q76">
-        <v>31.62128741</v>
+        <v>31.531372375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4950726762174011</v>
+        <v>0.5117822778523615</v>
       </c>
       <c r="T76">
-        <v>3.132527926387817</v>
+        <v>3.249034663901941</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.241434692026576</v>
+        <v>5.171548896132887</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1600886944630904</v>
+        <v>0.1597439431096564</v>
       </c>
       <c r="C77">
-        <v>126.6575842072878</v>
+        <v>125.4003066109235</v>
       </c>
       <c r="D77">
-        <v>277.8675842072878</v>
+        <v>278.7083066109235</v>
       </c>
       <c r="E77">
-        <v>13.85000000000002</v>
+        <v>15.94800000000001</v>
       </c>
       <c r="F77">
-        <v>157.35</v>
+        <v>159.448</v>
       </c>
       <c r="G77">
         <v>6.14</v>
@@ -7732,28 +7732,28 @@
         <v>45</v>
       </c>
       <c r="M77">
-        <v>8.701455000000001</v>
+        <v>8.8174744</v>
       </c>
       <c r="N77">
-        <v>36.298545</v>
+        <v>36.1825256</v>
       </c>
       <c r="O77">
-        <v>8.167172624999999</v>
+        <v>8.141068259999999</v>
       </c>
       <c r="P77">
-        <v>28.131372375</v>
+        <v>28.04145734</v>
       </c>
       <c r="Q77">
-        <v>31.531372375</v>
+        <v>31.44145734</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5117822778523615</v>
+        <v>0.5298843462902352</v>
       </c>
       <c r="T77">
-        <v>3.249034663901941</v>
+        <v>3.375250296208909</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.171548896132887</v>
+        <v>5.103502200131139</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1597439431096564</v>
+        <v>0.1593991917562225</v>
       </c>
       <c r="C78">
-        <v>125.4003066109235</v>
+        <v>124.1481318710503</v>
       </c>
       <c r="D78">
-        <v>278.7083066109235</v>
+        <v>279.5541318710503</v>
       </c>
       <c r="E78">
-        <v>15.94800000000001</v>
+        <v>18.04600000000002</v>
       </c>
       <c r="F78">
-        <v>159.448</v>
+        <v>161.546</v>
       </c>
       <c r="G78">
         <v>6.14</v>
@@ -7814,28 +7814,28 @@
         <v>45</v>
       </c>
       <c r="M78">
-        <v>8.8174744</v>
+        <v>8.933493800000001</v>
       </c>
       <c r="N78">
-        <v>36.1825256</v>
+        <v>36.0665062</v>
       </c>
       <c r="O78">
-        <v>8.141068259999999</v>
+        <v>8.114963895000001</v>
       </c>
       <c r="P78">
-        <v>28.04145734</v>
+        <v>27.951542305</v>
       </c>
       <c r="Q78">
-        <v>31.44145734</v>
+        <v>31.351542305</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5298843462902352</v>
+        <v>0.54956050763575</v>
       </c>
       <c r="T78">
-        <v>3.375250296208909</v>
+        <v>3.512441200890396</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.103502200131139</v>
+        <v>5.037222950778786</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1593991917562225</v>
+        <v>0.1590544404027886</v>
       </c>
       <c r="C79">
-        <v>124.1481318710503</v>
+        <v>122.9011065876073</v>
       </c>
       <c r="D79">
-        <v>279.5541318710503</v>
+        <v>280.4051065876073</v>
       </c>
       <c r="E79">
-        <v>18.04600000000002</v>
+        <v>20.14400000000001</v>
       </c>
       <c r="F79">
-        <v>161.546</v>
+        <v>163.644</v>
       </c>
       <c r="G79">
         <v>6.14</v>
@@ -7896,28 +7896,28 @@
         <v>45</v>
       </c>
       <c r="M79">
-        <v>8.933493800000001</v>
+        <v>9.0495132</v>
       </c>
       <c r="N79">
-        <v>36.0665062</v>
+        <v>35.9504868</v>
       </c>
       <c r="O79">
-        <v>8.114963895000001</v>
+        <v>8.088859530000001</v>
       </c>
       <c r="P79">
-        <v>27.951542305</v>
+        <v>27.86162727</v>
       </c>
       <c r="Q79">
-        <v>31.351542305</v>
+        <v>31.26162727</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.54956050763575</v>
+        <v>0.5710254109217663</v>
       </c>
       <c r="T79">
-        <v>3.512441200890396</v>
+        <v>3.662104005997472</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.037222950778786</v>
+        <v>4.972643169358546</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1590544404027886</v>
+        <v>0.1587096890493546</v>
       </c>
       <c r="C80">
-        <v>122.9011065876073</v>
+        <v>121.6592779296753</v>
       </c>
       <c r="D80">
-        <v>280.4051065876073</v>
+        <v>281.2612779296753</v>
       </c>
       <c r="E80">
-        <v>20.14400000000001</v>
+        <v>22.24200000000002</v>
       </c>
       <c r="F80">
-        <v>163.644</v>
+        <v>165.742</v>
       </c>
       <c r="G80">
         <v>6.14</v>
@@ -7978,28 +7978,28 @@
         <v>45</v>
       </c>
       <c r="M80">
-        <v>9.0495132</v>
+        <v>9.165532600000001</v>
       </c>
       <c r="N80">
-        <v>35.9504868</v>
+        <v>35.8344674</v>
       </c>
       <c r="O80">
-        <v>8.088859530000001</v>
+        <v>8.062755165</v>
       </c>
       <c r="P80">
-        <v>27.86162727</v>
+        <v>27.771712235</v>
       </c>
       <c r="Q80">
-        <v>31.26162727</v>
+        <v>31.171712235</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5710254109217663</v>
+        <v>0.5945345907112127</v>
       </c>
       <c r="T80">
-        <v>3.662104005997472</v>
+        <v>3.826020411590937</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.972643169358546</v>
+        <v>4.909698319113501</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1587096890493546</v>
+        <v>0.1583649376959207</v>
       </c>
       <c r="C81">
-        <v>121.6592779296753</v>
+        <v>120.4226936441915</v>
       </c>
       <c r="D81">
-        <v>281.2612779296753</v>
+        <v>282.1226936441915</v>
       </c>
       <c r="E81">
-        <v>22.24200000000002</v>
+        <v>24.34000000000003</v>
       </c>
       <c r="F81">
-        <v>165.742</v>
+        <v>167.84</v>
       </c>
       <c r="G81">
         <v>6.14</v>
@@ -8060,28 +8060,28 @@
         <v>45</v>
       </c>
       <c r="M81">
-        <v>9.165532600000001</v>
+        <v>9.281552000000001</v>
       </c>
       <c r="N81">
-        <v>35.8344674</v>
+        <v>35.718448</v>
       </c>
       <c r="O81">
-        <v>8.062755165</v>
+        <v>8.036650799999999</v>
       </c>
       <c r="P81">
-        <v>27.771712235</v>
+        <v>27.6817972</v>
       </c>
       <c r="Q81">
-        <v>31.171712235</v>
+        <v>31.0817972</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5945345907112127</v>
+        <v>0.6203946884796038</v>
       </c>
       <c r="T81">
-        <v>3.826020411590937</v>
+        <v>4.006328457743749</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.909698319113501</v>
+        <v>4.848327090124581</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1583649376959207</v>
+        <v>0.1580201863424868</v>
       </c>
       <c r="C82">
-        <v>120.4226936441915</v>
+        <v>119.1914020648265</v>
       </c>
       <c r="D82">
-        <v>282.1226936441915</v>
+        <v>282.9894020648265</v>
       </c>
       <c r="E82">
-        <v>24.34000000000003</v>
+        <v>26.43800000000002</v>
       </c>
       <c r="F82">
-        <v>167.84</v>
+        <v>169.938</v>
       </c>
       <c r="G82">
         <v>6.14</v>
@@ -8142,28 +8142,28 @@
         <v>45</v>
       </c>
       <c r="M82">
-        <v>9.281552000000001</v>
+        <v>9.397571400000002</v>
       </c>
       <c r="N82">
-        <v>35.718448</v>
+        <v>35.6024286</v>
       </c>
       <c r="O82">
-        <v>8.036650799999999</v>
+        <v>8.010546435</v>
       </c>
       <c r="P82">
-        <v>27.6817972</v>
+        <v>27.59188216499999</v>
       </c>
       <c r="Q82">
-        <v>31.0817972</v>
+        <v>30.99188216499999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6203946884796038</v>
+        <v>0.6489769018025622</v>
       </c>
       <c r="T82">
-        <v>4.006328457743749</v>
+        <v>4.205616298228434</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.848327090124581</v>
+        <v>4.788471200123043</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1580201863424868</v>
+        <v>0.1576754349890528</v>
       </c>
       <c r="C83">
-        <v>119.1914020648265</v>
+        <v>117.9654521210239</v>
       </c>
       <c r="D83">
-        <v>282.9894020648265</v>
+        <v>283.8614521210239</v>
       </c>
       <c r="E83">
-        <v>26.43800000000002</v>
+        <v>28.53600000000003</v>
       </c>
       <c r="F83">
-        <v>169.938</v>
+        <v>172.036</v>
       </c>
       <c r="G83">
         <v>6.14</v>
@@ -8224,28 +8224,28 @@
         <v>45</v>
       </c>
       <c r="M83">
-        <v>9.397571400000002</v>
+        <v>9.513590800000001</v>
       </c>
       <c r="N83">
-        <v>35.6024286</v>
+        <v>35.4864092</v>
       </c>
       <c r="O83">
-        <v>8.010546435</v>
+        <v>7.984442069999999</v>
       </c>
       <c r="P83">
-        <v>27.59188216499999</v>
+        <v>27.50196713</v>
       </c>
       <c r="Q83">
-        <v>30.99188216499999</v>
+        <v>30.90196713</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6489769018025622</v>
+        <v>0.6807349166058494</v>
       </c>
       <c r="T83">
-        <v>4.205616298228434</v>
+        <v>4.427047232100307</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.788471200123043</v>
+        <v>4.730075209877641</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1576754349890528</v>
+        <v>0.1573306836356189</v>
       </c>
       <c r="C84">
-        <v>117.9654521210239</v>
+        <v>116.7448933472085</v>
       </c>
       <c r="D84">
-        <v>283.8614521210239</v>
+        <v>284.7388933472085</v>
       </c>
       <c r="E84">
-        <v>28.53600000000003</v>
+        <v>30.63400000000001</v>
       </c>
       <c r="F84">
-        <v>172.036</v>
+        <v>174.134</v>
       </c>
       <c r="G84">
         <v>6.14</v>
@@ -8306,28 +8306,28 @@
         <v>45</v>
       </c>
       <c r="M84">
-        <v>9.513590800000001</v>
+        <v>9.629610200000002</v>
       </c>
       <c r="N84">
-        <v>35.4864092</v>
+        <v>35.3703898</v>
       </c>
       <c r="O84">
-        <v>7.984442069999999</v>
+        <v>7.958337705</v>
       </c>
       <c r="P84">
-        <v>27.50196713</v>
+        <v>27.412052095</v>
       </c>
       <c r="Q84">
-        <v>30.90196713</v>
+        <v>30.812052095</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6807349166058494</v>
+        <v>0.7162291684448174</v>
       </c>
       <c r="T84">
-        <v>4.427047232100307</v>
+        <v>4.674528864074754</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.730075209877641</v>
+        <v>4.673086351927308</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1573306836356189</v>
+        <v>0.156985932282185</v>
       </c>
       <c r="C85">
-        <v>116.7448933472085</v>
+        <v>115.5297758921656</v>
       </c>
       <c r="D85">
-        <v>284.7388933472085</v>
+        <v>285.6217758921656</v>
       </c>
       <c r="E85">
-        <v>30.63400000000001</v>
+        <v>32.73200000000003</v>
       </c>
       <c r="F85">
-        <v>174.134</v>
+        <v>176.232</v>
       </c>
       <c r="G85">
         <v>6.14</v>
@@ -8388,28 +8388,28 @@
         <v>45</v>
       </c>
       <c r="M85">
-        <v>9.629610200000002</v>
+        <v>9.745629600000003</v>
       </c>
       <c r="N85">
-        <v>35.3703898</v>
+        <v>35.2543704</v>
       </c>
       <c r="O85">
-        <v>7.958337705</v>
+        <v>7.93223334</v>
       </c>
       <c r="P85">
-        <v>27.412052095</v>
+        <v>27.32213706</v>
       </c>
       <c r="Q85">
-        <v>30.812052095</v>
+        <v>30.72213706</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7162291684448174</v>
+        <v>0.7561602017636567</v>
       </c>
       <c r="T85">
-        <v>4.674528864074754</v>
+        <v>4.952945700046008</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.673086351927308</v>
+        <v>4.61745437154722</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.156985932282185</v>
+        <v>0.1566411809287511</v>
       </c>
       <c r="C86">
-        <v>115.5297758921655</v>
+        <v>114.3201505285954</v>
       </c>
       <c r="D86">
-        <v>285.6217758921655</v>
+        <v>286.5101505285954</v>
       </c>
       <c r="E86">
-        <v>32.732</v>
+        <v>34.83000000000001</v>
       </c>
       <c r="F86">
-        <v>176.232</v>
+        <v>178.33</v>
       </c>
       <c r="G86">
         <v>6.14</v>
@@ -8470,28 +8470,28 @@
         <v>45</v>
       </c>
       <c r="M86">
-        <v>9.745629600000001</v>
+        <v>9.861649000000002</v>
       </c>
       <c r="N86">
-        <v>35.2543704</v>
+        <v>35.138351</v>
       </c>
       <c r="O86">
-        <v>7.93223334</v>
+        <v>7.906128975000001</v>
       </c>
       <c r="P86">
-        <v>27.32213706</v>
+        <v>27.232222025</v>
       </c>
       <c r="Q86">
-        <v>30.72213706</v>
+        <v>30.632222025</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7561602017636563</v>
+        <v>0.8014153728583405</v>
       </c>
       <c r="T86">
-        <v>4.952945700046004</v>
+        <v>5.268484780813424</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.617454371547221</v>
+        <v>4.563131378940783</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1566411809287511</v>
+        <v>0.1562964295753171</v>
       </c>
       <c r="C87">
-        <v>114.3201505285954</v>
+        <v>113.1160686628458</v>
       </c>
       <c r="D87">
-        <v>286.5101505285954</v>
+        <v>287.4040686628458</v>
       </c>
       <c r="E87">
-        <v>34.83000000000001</v>
+        <v>36.928</v>
       </c>
       <c r="F87">
-        <v>178.33</v>
+        <v>180.428</v>
       </c>
       <c r="G87">
         <v>6.14</v>
@@ -8552,28 +8552,28 @@
         <v>45</v>
       </c>
       <c r="M87">
-        <v>9.861649000000002</v>
+        <v>9.977668400000001</v>
       </c>
       <c r="N87">
-        <v>35.138351</v>
+        <v>35.0223316</v>
       </c>
       <c r="O87">
-        <v>7.906128975000001</v>
+        <v>7.88002461</v>
       </c>
       <c r="P87">
-        <v>27.232222025</v>
+        <v>27.14230699</v>
       </c>
       <c r="Q87">
-        <v>30.632222025</v>
+        <v>30.54230699</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8014153728583405</v>
+        <v>0.8531355683951224</v>
       </c>
       <c r="T87">
-        <v>5.268484780813424</v>
+        <v>5.629100873119045</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.563131378940783</v>
+        <v>4.510071711743798</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1562964295753171</v>
+        <v>0.1576373032218832</v>
       </c>
       <c r="C88">
-        <v>113.1160686628458</v>
+        <v>107.5722368117209</v>
       </c>
       <c r="D88">
-        <v>287.4040686628458</v>
+        <v>283.958236811721</v>
       </c>
       <c r="E88">
-        <v>36.928</v>
+        <v>39.02600000000001</v>
       </c>
       <c r="F88">
-        <v>180.428</v>
+        <v>182.526</v>
       </c>
       <c r="G88">
         <v>6.14</v>
@@ -8634,45 +8634,45 @@
         <v>45</v>
       </c>
       <c r="M88">
-        <v>9.977668400000001</v>
+        <v>10.5500028</v>
       </c>
       <c r="N88">
-        <v>35.0223316</v>
+        <v>34.4499972</v>
       </c>
       <c r="O88">
-        <v>7.88002461</v>
+        <v>7.75124937</v>
       </c>
       <c r="P88">
-        <v>27.14230699</v>
+        <v>26.69874783</v>
       </c>
       <c r="Q88">
-        <v>30.54230699</v>
+        <v>30.09874783</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8531355683951224</v>
+        <v>0.9128127170914093</v>
       </c>
       <c r="T88">
-        <v>5.629100873119045</v>
+        <v>6.045196364240916</v>
       </c>
       <c r="U88">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V88">
         <v>0.225</v>
       </c>
       <c r="W88">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>4.510071711743798</v>
+        <v>4.265401711552151</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1576373032218832</v>
+        <v>0.1573119268684493</v>
       </c>
       <c r="C89">
-        <v>107.5722368117209</v>
+        <v>106.3027876063845</v>
       </c>
       <c r="D89">
-        <v>283.958236811721</v>
+        <v>284.7867876063846</v>
       </c>
       <c r="E89">
-        <v>39.02600000000001</v>
+        <v>41.12400000000002</v>
       </c>
       <c r="F89">
-        <v>182.526</v>
+        <v>184.624</v>
       </c>
       <c r="G89">
         <v>6.14</v>
@@ -8716,28 +8716,28 @@
         <v>45</v>
       </c>
       <c r="M89">
-        <v>10.5500028</v>
+        <v>10.6712672</v>
       </c>
       <c r="N89">
-        <v>34.4499972</v>
+        <v>34.3287328</v>
       </c>
       <c r="O89">
-        <v>7.75124937</v>
+        <v>7.72396488</v>
       </c>
       <c r="P89">
-        <v>26.69874783</v>
+        <v>26.60476792</v>
       </c>
       <c r="Q89">
-        <v>30.09874783</v>
+        <v>30.00476792</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9128127170914093</v>
+        <v>0.9824360572370774</v>
       </c>
       <c r="T89">
-        <v>6.045196364240916</v>
+        <v>6.5306411038831</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.265401711552151</v>
+        <v>4.21693123755724</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1573119268684493</v>
+        <v>0.1569865505150154</v>
       </c>
       <c r="C90">
-        <v>106.3027876063845</v>
+        <v>105.0381877436161</v>
       </c>
       <c r="D90">
-        <v>284.7867876063846</v>
+        <v>285.6201877436162</v>
       </c>
       <c r="E90">
-        <v>41.12400000000002</v>
+        <v>43.22200000000001</v>
       </c>
       <c r="F90">
-        <v>184.624</v>
+        <v>186.722</v>
       </c>
       <c r="G90">
         <v>6.14</v>
@@ -8798,28 +8798,28 @@
         <v>45</v>
       </c>
       <c r="M90">
-        <v>10.6712672</v>
+        <v>10.7925316</v>
       </c>
       <c r="N90">
-        <v>34.3287328</v>
+        <v>34.2074684</v>
       </c>
       <c r="O90">
-        <v>7.72396488</v>
+        <v>7.696680389999999</v>
       </c>
       <c r="P90">
-        <v>26.60476792</v>
+        <v>26.51078801</v>
       </c>
       <c r="Q90">
-        <v>30.00476792</v>
+        <v>29.91078801</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9824360572370774</v>
+        <v>1.06471818650014</v>
       </c>
       <c r="T90">
-        <v>6.5306411038831</v>
+        <v>7.104348523460226</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.21693123755724</v>
+        <v>4.169549987697047</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1569865505150154</v>
+        <v>0.1566611741615814</v>
       </c>
       <c r="C91">
-        <v>105.0381877436161</v>
+        <v>103.7784799217206</v>
       </c>
       <c r="D91">
-        <v>285.6201877436162</v>
+        <v>286.4584799217207</v>
       </c>
       <c r="E91">
-        <v>43.22200000000001</v>
+        <v>45.32000000000002</v>
       </c>
       <c r="F91">
-        <v>186.722</v>
+        <v>188.82</v>
       </c>
       <c r="G91">
         <v>6.14</v>
@@ -8880,28 +8880,28 @@
         <v>45</v>
       </c>
       <c r="M91">
-        <v>10.7925316</v>
+        <v>10.913796</v>
       </c>
       <c r="N91">
-        <v>34.2074684</v>
+        <v>34.086204</v>
       </c>
       <c r="O91">
-        <v>7.696680389999999</v>
+        <v>7.669395899999999</v>
       </c>
       <c r="P91">
-        <v>26.51078801</v>
+        <v>26.4168081</v>
       </c>
       <c r="Q91">
-        <v>29.91078801</v>
+        <v>29.8168081</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.06471818650014</v>
+        <v>1.163456741615815</v>
       </c>
       <c r="T91">
-        <v>7.104348523460226</v>
+        <v>7.792797426952777</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.169549987697047</v>
+        <v>4.123221654500413</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1566611741615814</v>
+        <v>0.1563357978081475</v>
       </c>
       <c r="C92">
-        <v>103.7784799217206</v>
+        <v>102.5237073417546</v>
       </c>
       <c r="D92">
-        <v>286.4584799217207</v>
+        <v>287.3017073417546</v>
       </c>
       <c r="E92">
-        <v>45.32000000000002</v>
+        <v>47.41800000000001</v>
       </c>
       <c r="F92">
-        <v>188.82</v>
+        <v>190.918</v>
       </c>
       <c r="G92">
         <v>6.14</v>
@@ -8962,28 +8962,28 @@
         <v>45</v>
       </c>
       <c r="M92">
-        <v>10.913796</v>
+        <v>11.0350604</v>
       </c>
       <c r="N92">
-        <v>34.086204</v>
+        <v>33.9649396</v>
       </c>
       <c r="O92">
-        <v>7.669395899999999</v>
+        <v>7.64211141</v>
       </c>
       <c r="P92">
-        <v>26.4168081</v>
+        <v>26.32282819</v>
       </c>
       <c r="Q92">
-        <v>29.8168081</v>
+        <v>29.72282819</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.163456741615815</v>
+        <v>1.284137197868306</v>
       </c>
       <c r="T92">
-        <v>7.792797426952777</v>
+        <v>8.634234975665896</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.123221654500413</v>
+        <v>4.077911526428981</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1563357978081475</v>
+        <v>0.1560104214547136</v>
       </c>
       <c r="C93">
-        <v>102.5237073417546</v>
+        <v>101.2739137149478</v>
       </c>
       <c r="D93">
-        <v>287.3017073417546</v>
+        <v>288.1499137149478</v>
       </c>
       <c r="E93">
-        <v>47.41800000000001</v>
+        <v>49.51600000000002</v>
       </c>
       <c r="F93">
-        <v>190.918</v>
+        <v>193.016</v>
       </c>
       <c r="G93">
         <v>6.14</v>
@@ -9044,28 +9044,28 @@
         <v>45</v>
       </c>
       <c r="M93">
-        <v>11.0350604</v>
+        <v>11.1563248</v>
       </c>
       <c r="N93">
-        <v>33.9649396</v>
+        <v>33.8436752</v>
       </c>
       <c r="O93">
-        <v>7.64211141</v>
+        <v>7.61482692</v>
       </c>
       <c r="P93">
-        <v>26.32282819</v>
+        <v>26.22884828</v>
       </c>
       <c r="Q93">
-        <v>29.72282819</v>
+        <v>29.62884828</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.284137197868306</v>
+        <v>1.43498776818392</v>
       </c>
       <c r="T93">
-        <v>8.634234975665896</v>
+        <v>9.686031911557295</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.077911526428981</v>
+        <v>4.033586401141709</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1560104214547136</v>
+        <v>0.1582076701012797</v>
       </c>
       <c r="C94">
-        <v>101.2739137149478</v>
+        <v>93.54340654397049</v>
       </c>
       <c r="D94">
-        <v>288.1499137149478</v>
+        <v>282.5174065439705</v>
       </c>
       <c r="E94">
-        <v>49.51600000000002</v>
+        <v>51.61400000000003</v>
       </c>
       <c r="F94">
-        <v>193.016</v>
+        <v>195.114</v>
       </c>
       <c r="G94">
         <v>6.14</v>
@@ -9126,45 +9126,45 @@
         <v>45</v>
       </c>
       <c r="M94">
-        <v>11.1563248</v>
+        <v>11.9604882</v>
       </c>
       <c r="N94">
-        <v>33.8436752</v>
+        <v>33.0395118</v>
       </c>
       <c r="O94">
-        <v>7.61482692</v>
+        <v>7.433890155</v>
       </c>
       <c r="P94">
-        <v>26.22884828</v>
+        <v>25.605621645</v>
       </c>
       <c r="Q94">
-        <v>29.62884828</v>
+        <v>29.005621645</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.43498776818392</v>
+        <v>1.628938501446853</v>
       </c>
       <c r="T94">
-        <v>9.686031911557295</v>
+        <v>11.03834225770338</v>
       </c>
       <c r="U94">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V94">
         <v>0.225</v>
       </c>
       <c r="W94">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>4.033586401141709</v>
+        <v>3.762388227597599</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1582076701012797</v>
+        <v>0.1579094187478457</v>
       </c>
       <c r="C95">
-        <v>93.54340654397049</v>
+        <v>92.19700440088124</v>
       </c>
       <c r="D95">
-        <v>282.5174065439705</v>
+        <v>283.2690044008813</v>
       </c>
       <c r="E95">
-        <v>51.61400000000003</v>
+        <v>53.71200000000002</v>
       </c>
       <c r="F95">
-        <v>195.114</v>
+        <v>197.212</v>
       </c>
       <c r="G95">
         <v>6.14</v>
@@ -9208,28 +9208,28 @@
         <v>45</v>
       </c>
       <c r="M95">
-        <v>11.9604882</v>
+        <v>12.0890956</v>
       </c>
       <c r="N95">
-        <v>33.0395118</v>
+        <v>32.9109044</v>
       </c>
       <c r="O95">
-        <v>7.433890155</v>
+        <v>7.40495349</v>
       </c>
       <c r="P95">
-        <v>25.605621645</v>
+        <v>25.50595091</v>
       </c>
       <c r="Q95">
-        <v>29.005621645</v>
+        <v>28.90595091</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.628938501446853</v>
+        <v>1.887539479130764</v>
       </c>
       <c r="T95">
-        <v>11.03834225770338</v>
+        <v>12.84142271923149</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.762388227597599</v>
+        <v>3.722362820921029</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1579094187478457</v>
+        <v>0.1576111673944118</v>
       </c>
       <c r="C96">
-        <v>92.19700440088124</v>
+        <v>90.85461196600423</v>
       </c>
       <c r="D96">
-        <v>283.2690044008813</v>
+        <v>284.0246119660043</v>
       </c>
       <c r="E96">
-        <v>53.71200000000002</v>
+        <v>55.81000000000003</v>
       </c>
       <c r="F96">
-        <v>197.212</v>
+        <v>199.31</v>
       </c>
       <c r="G96">
         <v>6.14</v>
@@ -9290,28 +9290,28 @@
         <v>45</v>
       </c>
       <c r="M96">
-        <v>12.0890956</v>
+        <v>12.217703</v>
       </c>
       <c r="N96">
-        <v>32.9109044</v>
+        <v>32.782297</v>
       </c>
       <c r="O96">
-        <v>7.40495349</v>
+        <v>7.376016825</v>
       </c>
       <c r="P96">
-        <v>25.50595091</v>
+        <v>25.406280175</v>
       </c>
       <c r="Q96">
-        <v>28.90595091</v>
+        <v>28.806280175</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.887539479130764</v>
+        <v>2.249580847888239</v>
       </c>
       <c r="T96">
-        <v>12.84142271923149</v>
+        <v>15.36573536537086</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.722362820921029</v>
+        <v>3.683180054385018</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1576111673944118</v>
+        <v>0.1573129160409779</v>
       </c>
       <c r="C97">
-        <v>90.85461196600423</v>
+        <v>89.51626141231839</v>
       </c>
       <c r="D97">
-        <v>284.0246119660043</v>
+        <v>284.7842614123184</v>
       </c>
       <c r="E97">
-        <v>55.81000000000003</v>
+        <v>57.90800000000002</v>
       </c>
       <c r="F97">
-        <v>199.31</v>
+        <v>201.408</v>
       </c>
       <c r="G97">
         <v>6.14</v>
@@ -9372,28 +9372,28 @@
         <v>45</v>
       </c>
       <c r="M97">
-        <v>12.217703</v>
+        <v>12.3463104</v>
       </c>
       <c r="N97">
-        <v>32.782297</v>
+        <v>32.6536896</v>
       </c>
       <c r="O97">
-        <v>7.376016825</v>
+        <v>7.34708016</v>
       </c>
       <c r="P97">
-        <v>25.406280175</v>
+        <v>25.30660944</v>
       </c>
       <c r="Q97">
-        <v>28.806280175</v>
+        <v>28.70660944</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.249580847888239</v>
+        <v>2.792642901024452</v>
       </c>
       <c r="T97">
-        <v>15.36573536537086</v>
+        <v>19.1522043345799</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.683180054385018</v>
+        <v>3.644813595485174</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1573129160409779</v>
+        <v>0.1570146646875439</v>
       </c>
       <c r="C98">
-        <v>89.51626141231839</v>
+        <v>88.18198525792397</v>
       </c>
       <c r="D98">
-        <v>284.7842614123184</v>
+        <v>285.547985257924</v>
       </c>
       <c r="E98">
-        <v>57.90800000000002</v>
+        <v>60.006</v>
       </c>
       <c r="F98">
-        <v>201.408</v>
+        <v>203.506</v>
       </c>
       <c r="G98">
         <v>6.14</v>
@@ -9454,28 +9454,28 @@
         <v>45</v>
       </c>
       <c r="M98">
-        <v>12.3463104</v>
+        <v>12.4749178</v>
       </c>
       <c r="N98">
-        <v>32.6536896</v>
+        <v>32.5250822</v>
       </c>
       <c r="O98">
-        <v>7.34708016</v>
+        <v>7.318143495</v>
       </c>
       <c r="P98">
-        <v>25.30660944</v>
+        <v>25.206938705</v>
       </c>
       <c r="Q98">
-        <v>28.70660944</v>
+        <v>28.606938705</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.792642901024444</v>
+        <v>3.697746322918128</v>
       </c>
       <c r="T98">
-        <v>19.15220433457985</v>
+        <v>25.46298594992822</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.644813595485174</v>
+        <v>3.607238197593575</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1570146646875439</v>
+        <v>0.15671641333411</v>
       </c>
       <c r="C99">
-        <v>88.18198525792397</v>
+        <v>86.85181637068237</v>
       </c>
       <c r="D99">
-        <v>285.547985257924</v>
+        <v>286.3158163706824</v>
       </c>
       <c r="E99">
-        <v>60.006</v>
+        <v>62.10400000000001</v>
       </c>
       <c r="F99">
-        <v>203.506</v>
+        <v>205.604</v>
       </c>
       <c r="G99">
         <v>6.14</v>
@@ -9536,28 +9536,28 @@
         <v>45</v>
       </c>
       <c r="M99">
-        <v>12.4749178</v>
+        <v>12.6035252</v>
       </c>
       <c r="N99">
-        <v>32.5250822</v>
+        <v>32.3964748</v>
       </c>
       <c r="O99">
-        <v>7.318143495</v>
+        <v>7.28920683</v>
       </c>
       <c r="P99">
-        <v>25.206938705</v>
+        <v>25.10726797</v>
       </c>
       <c r="Q99">
-        <v>28.606938705</v>
+        <v>28.50726797</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.697746322918128</v>
+        <v>5.507953166705495</v>
       </c>
       <c r="T99">
-        <v>25.46298594992822</v>
+        <v>38.08454918062498</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.607238197593575</v>
+        <v>3.570429644556905</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.15671641333411</v>
+        <v>0.1564181619806761</v>
       </c>
       <c r="C100">
-        <v>86.85181637068237</v>
+        <v>85.52578797293165</v>
       </c>
       <c r="D100">
-        <v>286.3158163706824</v>
+        <v>287.0877879729317</v>
       </c>
       <c r="E100">
-        <v>62.10400000000001</v>
+        <v>64.202</v>
       </c>
       <c r="F100">
-        <v>205.604</v>
+        <v>207.702</v>
       </c>
       <c r="G100">
         <v>6.14</v>
@@ -9618,28 +9618,28 @@
         <v>45</v>
       </c>
       <c r="M100">
-        <v>12.6035252</v>
+        <v>12.7321326</v>
       </c>
       <c r="N100">
-        <v>32.3964748</v>
+        <v>32.2678674</v>
       </c>
       <c r="O100">
-        <v>7.28920683</v>
+        <v>7.260270165000001</v>
       </c>
       <c r="P100">
-        <v>25.10726797</v>
+        <v>25.007597235</v>
       </c>
       <c r="Q100">
-        <v>28.50726797</v>
+        <v>28.407597235</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.507953166705495</v>
+        <v>10.9385736980676</v>
       </c>
       <c r="T100">
-        <v>38.08454918062498</v>
+        <v>75.94923887271524</v>
       </c>
       <c r="U100">
         <v>0.0613</v>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.570429644556905</v>
+        <v>3.53436469865229</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1564181619806761</v>
-      </c>
-      <c r="C101">
-        <v>85.52578797293165</v>
-      </c>
-      <c r="D101">
-        <v>287.0877879729317</v>
-      </c>
-      <c r="E101">
-        <v>64.202</v>
-      </c>
-      <c r="F101">
-        <v>207.702</v>
-      </c>
-      <c r="G101">
-        <v>6.14</v>
-      </c>
-      <c r="H101">
-        <v>66.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>48.4</v>
-      </c>
-      <c r="K101">
-        <v>3.399999999999999</v>
-      </c>
-      <c r="L101">
-        <v>45</v>
-      </c>
-      <c r="M101">
-        <v>12.7321326</v>
-      </c>
-      <c r="N101">
-        <v>32.2678674</v>
-      </c>
-      <c r="O101">
-        <v>7.260270165000001</v>
-      </c>
-      <c r="P101">
-        <v>25.007597235</v>
-      </c>
-      <c r="Q101">
-        <v>28.407597235</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.9385736980676</v>
-      </c>
-      <c r="T101">
-        <v>75.94923887271524</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.225</v>
-      </c>
-      <c r="W101">
-        <v>0.0475075</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.53436469865229</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
